--- a/lessons/sorting/excels/remarks_ro_star.xlsx
+++ b/lessons/sorting/excels/remarks_ro_star.xlsx
@@ -162,12 +162,12 @@
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:17:21.139), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), -align (10:57:30.272), -- (10:57:30.282), -items (10:57:30.332), -: (10:57:30.342), -flex (10:57:30.392), -- (10:57:30.402), -end (10:57:30.432), -; (10:57:30.442), +justify (00:00:00), +- (00:00:00), +content (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+        <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:17:21.139) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596) ~1.00, -items (10:24:13.500) ~1.00, +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), -align (10:57:30.272), -- (10:57:30.282), -items (10:57:30.332), -: (10:57:30.342), -flex (10:57:30.392), -- (10:57:30.402), -end (10:57:30.432), -; (10:57:30.442), +justify (00:00:00), +- (00:00:00), +content (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <t>-i (10:38:53.739), -array (10:38:55.446), -createElement (10:39:45.021), -function (10:57:37.492), -bubbleSort (10:57:42.836), -( (10:57:43.053), -arr (10:57:49.140), -) (10:57:49.861), -{ (10:57:54.715), -do (10:58:33.576), -{ (10:58:34.903), -} (10:58:35.895), -var (10:59:12.196), -swapped (10:59:20.551), -= (10:59:21.101), -false (10:59:23.105), -; (10:59:24.221), -for (10:59:26.374), -( (10:59:26.727), -let (10:59:27.295), -i (10:59:27.677), -= (10:59:27.952), -1 (10:59:28.458), -; (10:59:28.738), -i (10:59:29.253), -&lt; (10:59:29.652), -arr (10:59:30.525), -. (10:59:30.766), -length (10:59:32.061), -; (10:59:32.305), -i (10:59:32.661), -+ (10:59:32.869), -+ (10:59:33.126), -) (10:59:33.350), -{ (10:59:35.506), -} (10:59:37.396), -if (10:59:41.288), -( (10:59:41.708), -arr (10:59:42.652), -[ (10:59:42.917), -i (10:59:43.246), -- (10:59:44.058), -1 (10:59:44.656), -] (10:59:44.854), -&gt; (10:59:45.546), -arr (10:59:46.616), -[ (10:59:46.969), -i (10:59:47.212), -] (10:59:47.751), -) (10:59:48.230), -{ (10:59:49.302), -const (11:00:57.203), -aux (11:00:58.458), -= (11:01:01.660), -arr (11:01:02.684), -[ (11:01:02.941), -i (11:01:03.128), -- (11:01:03.607), -1 (11:01:04.198), -] (11:01:04.697), -; (11:01:05.017), -arr (11:01:06.389), -[ (11:01:06.650), -i (11:01:06.835), -- (11:01:07.252), -1 (11:01:07.757), -] (11:01:08.184), -= (11:01:08.961), -arr (11:01:09.861), -[ (11:01:10.052), -i (11:01:10.368), -] (11:01:10.513), -; (11:01:10.683), -arr (11:01:12.501), -[ (11:01:12.714), -i (11:01:12.894), -] (11:01:13.102), -= (11:01:13.537), -aux (11:01:14.449), -; (11:01:14.856), -swapped (11:02:15.877), -= (11:02:16.203), -true (11:02:17.158), -; (11:02:17.463), -while (11:02:23.923), -( (11:02:24.360), -swapped (11:02:25.916), -) (11:02:26.084), -; (11:02:26.436), -( (11:09:55.956), -let (11:09:56.455), -i (11:09:56.677), -= (11:09:57.008), -0 (11:09:57.490), -; (11:09:57.512), -i (11:09:57.854), -&lt; (11:09:58.223), -bars (11:09:58.993), -. (11:09:59.214), -length (11:10:00.426), -; (11:10:00.634), -i (11:10:01.376), -+ (11:10:01.600), -+ (11:10:01.789), -) (11:10:01.880), -{ (11:10:02.609), -} (11:10:03.305), -bars (11:10:05.954), -[ (11:10:06.083), -i (11:10:06.207), -] (11:10:06.517), -. (11:10:06.753), -style (11:10:08.322), -. (11:10:08.474), -height (11:10:09.606), -= (11:10:12.868), -array (11:10:13.726), -[ (11:10:13.999), -i (11:10:14.138), -] (11:10:14.279), -* (11:10:14.846), -100 (11:10:15.517), -+ (11:10:16.137), -" (11:10:16.502), -% (11:10:16.625), -" (11:10:16.705), -; (11:10:17.104), -updateBars (11:12:30.664), -( (11:12:30.752), -) (11:12:30.906), -; (11:12:31.204), -await (11:13:47.348), -new (11:13:53.570), -Promise (11:13:54.982), -( (11:13:55.301), -resolve (11:13:59.055), -= (11:14:16.118), -&gt; (11:14:16.408), -setTimeout (11:14:18.857), -( (11:14:19.066), -resolve (11:14:23.324), -, (11:14:23.491), -100 (11:14:24.924), -) (11:14:31.103), -) (11:14:31.475), -; (11:14:32.118), -async (11:15:16.100), +1 (00:00:00), +arry (00:00:00), +cretaeElement (00:00:00), +function (00:00:00), +bubbleSort (00:00:00), +( (00:00:00), +arr (00:00:00), +) (00:00:00), +{ (00:00:00), +do (00:00:00), +{ (00:00:00), +var (00:00:00), +swapped (00:00:00), += (00:00:00), +false (00:00:00), +; (00:00:00), +for (00:00:00), +( (00:00:00), +i (00:00:00), += (00:00:00), +1 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +arr (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +if (00:00:00), +( (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +- (00:00:00), +1 (00:00:00), +] (00:00:00), +&gt; (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +aux (00:00:00), += (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +- (00:00:00), +1 (00:00:00), +] (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), += (00:00:00), +aux (00:00:00), +; (00:00:00), +swapped (00:00:00), += (00:00:00), +true (00:00:00), +; (00:00:00), +updateBars (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +await (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +100 (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +while (00:00:00), +( (00:00:00), +swapped (00:00:00), +) (00:00:00), +; (00:00:00)</t>
+        <t>-i (10:38:53.739), -array (10:38:55.446) ~0.80, -createElement (10:39:45.021) ~0.85, -function (10:57:37.492) ~1.00, -bubbleSort (10:57:42.836) ~1.00, -( (10:57:43.053) ~1.00, -arr (10:57:49.140) ~1.00, -) (10:57:49.861) ~1.00, -{ (10:57:54.715) ~1.00, -do (10:58:33.576) ~1.00, -{ (10:58:34.903) ~1.00, -} (10:58:35.895), -var (10:59:12.196) ~1.00, -swapped (10:59:20.551) ~1.00, -= (10:59:21.101) ~1.00, -false (10:59:23.105) ~1.00, -; (10:59:24.221) ~1.00, -for (10:59:26.374) ~1.00, -( (10:59:26.727) ~1.00, -let (10:59:27.295), -i (10:59:27.677) ~1.00, -= (10:59:27.952) ~1.00, -1 (10:59:28.458) ~1.00, -; (10:59:28.738) ~1.00, -i (10:59:29.253) ~1.00, -&lt; (10:59:29.652) ~1.00, -arr (10:59:30.525) ~1.00, -. (10:59:30.766) ~1.00, -length (10:59:32.061) ~1.00, -; (10:59:32.305) ~1.00, -i (10:59:32.661) ~1.00, -+ (10:59:32.869) ~1.00, -+ (10:59:33.126) ~1.00, -) (10:59:33.350) ~1.00, -{ (10:59:35.506) ~1.00, -} (10:59:37.396), -if (10:59:41.288) ~1.00, -( (10:59:41.708) ~1.00, -arr (10:59:42.652) ~1.00, -[ (10:59:42.917) ~1.00, -i (10:59:43.246) ~1.00, -- (10:59:44.058) ~1.00, -1 (10:59:44.656) ~1.00, -] (10:59:44.854) ~1.00, -&gt; (10:59:45.546) ~1.00, -arr (10:59:46.616) ~1.00, -[ (10:59:46.969) ~1.00, -i (10:59:47.212) ~1.00, -] (10:59:47.751) ~1.00, -) (10:59:48.230) ~1.00, -{ (10:59:49.302) ~1.00, -const (11:00:57.203) ~1.00, -aux (11:00:58.458) ~1.00, -= (11:01:01.660) ~1.00, -arr (11:01:02.684) ~1.00, -[ (11:01:02.941) ~1.00, -i (11:01:03.128) ~1.00, -- (11:01:03.607) ~1.00, -1 (11:01:04.198) ~1.00, -] (11:01:04.697) ~1.00, -; (11:01:05.017), -arr (11:01:06.389), -[ (11:01:06.650), -i (11:01:06.835), -- (11:01:07.252), -1 (11:01:07.757), -] (11:01:08.184), -= (11:01:08.961), -arr (11:01:09.861), -[ (11:01:10.052), -i (11:01:10.368), -] (11:01:10.513), -; (11:01:10.683), -arr (11:01:12.501) ~1.00, -[ (11:01:12.714) ~1.00, -i (11:01:12.894) ~1.00, -] (11:01:13.102) ~1.00, -= (11:01:13.537) ~1.00, -aux (11:01:14.449) ~1.00, -; (11:01:14.856) ~1.00, -swapped (11:02:15.877) ~1.00, -= (11:02:16.203) ~1.00, -true (11:02:17.158) ~1.00, -; (11:02:17.463) ~1.00, -while (11:02:23.923) ~1.00, -( (11:02:24.360) ~1.00, -swapped (11:02:25.916) ~1.00, -) (11:02:26.084) ~1.00, -; (11:02:26.436) ~1.00, -( (11:09:55.956), -let (11:09:56.455), -i (11:09:56.677), -= (11:09:57.008), -0 (11:09:57.490), -; (11:09:57.512), -i (11:09:57.854) ~0.00, -&lt; (11:09:58.223), -bars (11:09:58.993), -. (11:09:59.214), -length (11:10:00.426), -; (11:10:00.634), -i (11:10:01.376), -+ (11:10:01.600), -+ (11:10:01.789), -) (11:10:01.880), -{ (11:10:02.609), -} (11:10:03.305), -bars (11:10:05.954), -[ (11:10:06.083), -i (11:10:06.207), -] (11:10:06.517), -. (11:10:06.753), -style (11:10:08.322), -. (11:10:08.474), -height (11:10:09.606), -= (11:10:12.868), -array (11:10:13.726), -[ (11:10:13.999), -i (11:10:14.138), -] (11:10:14.279), -* (11:10:14.846), -100 (11:10:15.517), -+ (11:10:16.137), -" (11:10:16.502), -% (11:10:16.625), -" (11:10:16.705), -; (11:10:17.104), -updateBars (11:12:30.664) ~1.00, -( (11:12:30.752) ~1.00, -) (11:12:30.906) ~1.00, -; (11:12:31.204) ~1.00, -await (11:13:47.348) ~1.00, -new (11:13:53.570) ~1.00, -Promise (11:13:54.982) ~1.00, -( (11:13:55.301) ~1.00, -resolve (11:13:59.055) ~1.00, -= (11:14:16.118) ~1.00, -&gt; (11:14:16.408) ~1.00, -setTimeout (11:14:18.857) ~1.00, -( (11:14:19.066) ~1.00, -resolve (11:14:23.324) ~1.00, -, (11:14:23.491) ~1.00, -100 (11:14:24.924) ~1.00, -) (11:14:31.103) ~1.00, -) (11:14:31.475) ~1.00, -; (11:14:32.118) ~1.00, -async (11:15:16.100), +1 (00:00:00), +arry (00:00:00), +cretaeElement (00:00:00), +function (00:00:00), +bubbleSort (00:00:00), +( (00:00:00), +arr (00:00:00), +) (00:00:00), +{ (00:00:00), +do (00:00:00), +{ (00:00:00), +var (00:00:00), +swapped (00:00:00), += (00:00:00), +false (00:00:00), +; (00:00:00), +for (00:00:00), +( (00:00:00), +i (00:00:00), += (00:00:00), +1 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +arr (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +if (00:00:00), +( (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +- (00:00:00), +1 (00:00:00), +] (00:00:00), +&gt; (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +aux (00:00:00), += (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +- (00:00:00), +1 (00:00:00), +] (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), += (00:00:00), +aux (00:00:00), +; (00:00:00), +swapped (00:00:00), += (00:00:00), +true (00:00:00), +; (00:00:00), +updateBars (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +await (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +100 (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +while (00:00:00), +( (00:00:00), +swapped (00:00:00), +) (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E5" authorId="0" shapeId="0">
@@ -187,12 +187,12 @@
     </comment>
     <comment ref="O5" authorId="0" shapeId="0">
       <text>
-        <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:17:21.139), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+        <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:17:21.139) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q5" authorId="0" shapeId="0">
       <text>
-        <t>-for (10:30:13.868), -( (10:30:14.352), -let (10:30:15.164), -i (10:30:15.672), -= (10:30:16.329), -0 (10:30:16.771), -; (10:30:17.011), -i (10:30:17.443), -&lt; (10:30:18.073), -count (10:30:20.284), -; (10:30:20.584), -i (10:30:47.713), -+ (10:30:48.171), -+ (10:30:48.660), -) (10:30:49.210), -{ (10:31:12.723), -array (10:31:16.948), -[ (10:31:17.188), -] (10:31:22.021), -Math (10:31:30.068), -. (10:31:30.292), -random (10:31:31.871), -( (10:31:32.250), -; (10:31:32.818), -var (10:59:12.196), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -} (11:10:03.305), +for (00:00:00), +( (00:00:00), +let (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +count (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +{ (00:00:00), +array (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), += (00:00:00), +Math (00:00:00), +. (00:00:00), +random (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +let (00:00:00)</t>
+        <t>-for (10:30:13.868) ~1.00, -( (10:30:14.352) ~1.00, -let (10:30:15.164) ~1.00, -i (10:30:15.672), -= (10:30:16.329), -0 (10:30:16.771) ~1.00, -; (10:30:17.011) ~1.00, -i (10:30:17.443) ~1.00, -&lt; (10:30:18.073) ~1.00, -count (10:30:20.284) ~1.00, -; (10:30:20.584) ~1.00, -i (10:30:47.713) ~1.00, -+ (10:30:48.171) ~1.00, -+ (10:30:48.660) ~1.00, -) (10:30:49.210), -{ (10:31:12.723) ~1.00, -array (10:31:16.948) ~1.00, -[ (10:31:17.188) ~1.00, -] (10:31:22.021) ~1.00, -Math (10:31:30.068) ~1.00, -. (10:31:30.292) ~1.00, -random (10:31:31.871) ~1.00, -( (10:31:32.250) ~1.00, -; (10:31:32.818) ~1.00, -var (10:59:12.196) ~0.00, +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -} (11:10:03.305), +for (00:00:00), +( (00:00:00), +let (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +count (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +{ (00:00:00), +array (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), += (00:00:00), +Math (00:00:00), +. (00:00:00), +random (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +let (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E9" authorId="0" shapeId="0">
@@ -212,17 +212,17 @@
     </comment>
     <comment ref="M9" authorId="0" shapeId="0">
       <text>
-        <t>-&lt; (10:12:37.377), -/ (10:12:37.545), -head (10:12:38.381), -&gt; (10:12:38.657), -Visualizer (10:12:47.677), -&lt; (10:12:59.962), -body (10:13:00.878), -&gt; (10:13:01.096), -&lt; (10:13:08.462), -h1 (10:13:08.883), -&gt; (10:13:09.312), -Sorting (10:13:13.802), -Visualizer (10:13:16.993), -&lt; (10:13:17.335), -/ (10:13:17.789), -h1 (10:13:18.123), -&gt; (10:13:18.254), -&lt; (10:17:05.513), -/ (10:17:05.729), -style (10:17:06.766), -&gt; (10:17:06.867), -&lt; (10:18:29.900), -div (10:18:30.558), -id (10:18:31.498), -= (10:18:31.631), -" (10:18:33.349), -vis (10:18:34.420), -- (10:18:37.062), -123456 (10:18:40.665), -" (10:18:40.947), -&gt; (10:18:43.208), -&lt; (10:18:44.230), -/ (10:18:44.552), -div (10:18:45.086), -&gt; (10:18:45.251), -&lt; (10:27:13.253), -script (10:27:14.426), -&gt; (10:27:14.698), +visualizer (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +style (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +head (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +body (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +h1 (00:00:00), +&gt; (00:00:00), +Sorting (00:00:00), +visualizer (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +h1 (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +script (00:00:00), +&gt; (00:00:00)</t>
+        <t>-&lt; (10:12:37.377) ~1.00, -/ (10:12:37.545) ~1.00, -head (10:12:38.381) ~1.00, -&gt; (10:12:38.657) ~1.00, -Visualizer (10:12:47.677) ~0.90, -&lt; (10:12:59.962) ~1.00, -body (10:13:00.878) ~1.00, -&gt; (10:13:01.096) ~1.00, -&lt; (10:13:08.462) ~1.00, -h1 (10:13:08.883) ~1.00, -&gt; (10:13:09.312) ~1.00, -Sorting (10:13:13.802) ~1.00, -Visualizer (10:13:16.993) ~0.90, -&lt; (10:13:17.335) ~1.00, -/ (10:13:17.789) ~1.00, -h1 (10:13:18.123) ~1.00, -&gt; (10:13:18.254) ~1.00, -&lt; (10:17:05.513) ~1.00, -/ (10:17:05.729) ~1.00, -style (10:17:06.766) ~1.00, -&gt; (10:17:06.867) ~1.00, -&lt; (10:18:29.900) ~1.00, -div (10:18:30.558) ~1.00, -id (10:18:31.498) ~1.00, -= (10:18:31.631) ~1.00, -" (10:18:33.349) ~1.00, -vis (10:18:34.420) ~1.00, -- (10:18:37.062) ~1.00, -123456 (10:18:40.665) ~1.00, -" (10:18:40.947) ~1.00, -&gt; (10:18:43.208) ~1.00, -&lt; (10:18:44.230) ~1.00, -/ (10:18:44.552) ~1.00, -div (10:18:45.086) ~1.00, -&gt; (10:18:45.251) ~1.00, -&lt; (10:27:13.253) ~1.00, -script (10:27:14.426) ~1.00, -&gt; (10:27:14.698) ~1.00, +visualizer (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +style (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +head (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +body (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +h1 (00:00:00), +&gt; (00:00:00), +Sorting (00:00:00), +visualizer (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +h1 (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +script (00:00:00), +&gt; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O9" authorId="0" shapeId="0">
       <text>
-        <t>-center (10:17:20.707), -# (10:19:53.296), -vis (10:19:54.003), -- (10:19:54.226), -123456 (10:19:55.544), -height (10:20:07.891), -: (10:20:07.983), -200px (10:20:09.051), -; (10:20:09.451), -flex (10:21:58.800), -direction (10:22:01.758), -column (10:22:03.223), -align (10:24:12.446), -items (10:24:13.500), -. (10:43:24.242), -bar (10:43:31.288), -{ (10:43:32.996), -width (10:43:37.644), -: (10:43:37.716), -7px (10:43:39.527), -; (10:43:40.239), -height (10:43:47.504), -: (10:43:47.683), -100 (10:43:48.485), -% (10:43:48.586), -; (10:43:48.809), -background (10:44:24.231), -- (10:44:24.311), -color (10:44:25.031), -: (10:44:25.154), -black (10:44:26.271), -; (10:44:26.592), -display (10:47:38.305), -: (10:47:38.437), -flex (10:47:39.551), -; (10:47:39.811), -margin (10:48:02.482), -: (10:48:02.549), -0px (10:48:03.827), -1px (10:48:07.241), +;* (10:50:09.333), -align (10:57:30.272), -- (10:57:30.282), -items (10:57:30.332), -: (10:57:30.342), -flex (10:57:30.392), -- (10:57:30.402), -end (10:57:30.432), +align (00:00:00), +items (00:00:00), +center (00:00:00), +flex (00:00:00), +direction (00:00:00), +column (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +{ (00:00:00), +height (00:00:00), +: (00:00:00), +200px (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +flex (00:00:00), +- (00:00:00), +end (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +bar (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +7px (00:00:00), +; (00:00:00), +height (00:00:00), +: (00:00:00), +100 (00:00:00), +% (00:00:00), +; (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +black (00:00:00), +; (00:00:00), +margin (00:00:00), +: (00:00:00), +0px (00:00:00), +1px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        <t>-center (10:17:20.707) ~0.17, -# (10:19:53.296) ~1.00, -vis (10:19:54.003) ~1.00, -- (10:19:54.226) ~1.00, -123456 (10:19:55.544) ~1.00, -height (10:20:07.891) ~1.00, -: (10:20:07.983) ~1.00, -200px (10:20:09.051) ~1.00, -; (10:20:09.451), -flex (10:21:58.800) ~0.20, -direction (10:22:01.758) ~0.22, -column (10:22:03.223) ~1.00, -align (10:24:12.446) ~0.00, -items (10:24:13.500) ~0.14, -. (10:43:24.242) ~1.00, -bar (10:43:31.288) ~1.00, -{ (10:43:32.996) ~1.00, -width (10:43:37.644) ~1.00, -: (10:43:37.716) ~1.00, -7px (10:43:39.527) ~1.00, -; (10:43:40.239) ~1.00, -height (10:43:47.504) ~1.00, -: (10:43:47.683) ~1.00, -100 (10:43:48.485) ~1.00, -% (10:43:48.586) ~1.00, -; (10:43:48.809) ~1.00, -background (10:44:24.231) ~1.00, -- (10:44:24.311) ~1.00, -color (10:44:25.031) ~1.00, -: (10:44:25.154) ~1.00, -black (10:44:26.271) ~1.00, -; (10:44:26.592) ~1.00, -display (10:47:38.305) ~1.00, -: (10:47:38.437) ~1.00, -flex (10:47:39.551) ~1.00, -; (10:47:39.811) ~1.00, -margin (10:48:02.482) ~1.00, -: (10:48:02.549) ~1.00, -0px (10:48:03.827) ~1.00, -1px (10:48:07.241) ~1.00, +;* (10:50:09.333), -align (10:57:30.272) ~1.00, -- (10:57:30.282) ~1.00, -items (10:57:30.332) ~1.00, -: (10:57:30.342) ~1.00, -flex (10:57:30.392) ~1.00, -- (10:57:30.402) ~1.00, -end (10:57:30.432) ~1.00, +align (00:00:00), +items (00:00:00), +center (00:00:00), +flex (00:00:00), +direction (00:00:00), +column (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +{ (00:00:00), +height (00:00:00), +: (00:00:00), +200px (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +flex (00:00:00), +- (00:00:00), +end (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +bar (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +7px (00:00:00), +; (00:00:00), +height (00:00:00), +: (00:00:00), +100 (00:00:00), +% (00:00:00), +; (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +black (00:00:00), +; (00:00:00), +margin (00:00:00), +: (00:00:00), +0px (00:00:00), +1px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q9" authorId="0" shapeId="0">
       <text>
-        <t>-const (10:27:46.114), -count (10:27:47.499), -= (10:27:48.489), -50 (10:27:50.527), -; (10:27:51.439), -const (10:28:42.502), -array (10:28:45.898), -= (10:28:48.193), -new (10:28:49.261), -Array (10:28:50.400), -( (10:28:50.634), -count (10:28:52.202), -) (10:28:52.450), -; (10:28:52.802), -for (10:30:13.868), -( (10:30:14.352), -let (10:30:15.164), -i (10:30:15.672), -= (10:30:16.329), -0 (10:30:16.771), -; (10:30:17.011), -i (10:30:17.443), -&lt; (10:30:18.073), -count (10:30:20.284), -; (10:30:20.584), -i (10:30:47.713), -+ (10:30:48.171), -+ (10:30:48.660), -) (10:30:49.210), -{ (10:31:12.723), -array (10:31:16.948), -[ (10:31:17.188), -i (10:31:18.211), -] (10:31:22.021), -= (10:31:23.399), -Math (10:31:30.068), -. (10:31:30.292), -random (10:31:31.871), -( (10:31:32.250), -) (10:31:32.537), -; (10:31:32.818), -const (10:37:42.386), -visualizer (10:37:44.631), -= (10:37:45.082), -document (10:37:47.323), -. (10:37:47.760), -getElementById (10:38:03.158), -( (10:38:03.433), -" (10:38:19.019), -vis (10:38:19.926), -- (10:38:20.217), -123456 (10:38:22.251), -" (10:38:22.629), -) (10:38:22.754), -; (10:38:23.727), -for (10:38:50.477), -( (10:38:50.999), -let (10:38:51.733), -i (10:38:52.267), -= (10:38:52.612), -0 (10:38:53.033), -; (10:38:53.257), -i (10:38:53.739), -&lt; (10:38:54.145), -array (10:38:55.446), -. (10:38:55.684), -length (10:38:57.372), -; (10:38:57.593), -i (10:38:58.029), -+ (10:38:58.280), -+ (10:38:58.511), -) (10:38:58.809), -{ (10:39:16.312), -const (10:39:36.638), -bar (10:39:37.346), -= (10:39:37.875), -document (10:39:42.722), -. (10:39:42.888), -createElement (10:39:45.021), -( (10:39:45.078), -" (10:39:45.883), -div (10:39:48.709), -" (10:39:48.892), -) (10:39:49.655), -; (10:39:49.907), -visualizer (10:40:27.992), -. (10:40:28.151), -appendChild (10:40:30.229), -( (10:40:30.435), -bar (10:40:31.317), -) (10:40:31.505), -; (10:40:32.101), -bar (10:42:30.607), -. (10:42:30.785), -classList (10:42:32.670), -. (10:42:32.869), -add (10:42:33.487), -( (10:42:33.684), -" (10:42:33.916), -bar (10:42:35.380), -" (10:42:35.625), -) (10:42:36.061), -; (10:42:36.565), -bar (10:50:10.577), -. (10:50:10.720), -style (10:50:11.842), -. (10:50:12.547), -height (10:50:14.172), -= (10:50:15.244), -array (10:50:17.753), -[ (10:50:17.905), -i (10:50:18.168), -] (10:50:18.460), -* (10:50:28.020), -100 (10:50:29.694), -+ (10:50:38.934), -" (10:50:40.368), -% (10:50:40.883), -" (10:50:41.432), -; (10:50:48.660), -function (10:57:37.492), -bubbleSort (10:57:42.836), -( (10:57:43.053), -arr (10:57:49.140), -) (10:57:49.861), -{ (10:57:54.715), -} (10:57:57.644), -do (10:58:33.576), -{ (10:58:34.903), -} (10:58:35.895), -var (10:59:12.196), -swapped (10:59:20.551), -= (10:59:21.101), -false (10:59:23.105), -; (10:59:24.221), -for (10:59:26.374), -( (10:59:26.727), -let (10:59:27.295), -i (10:59:27.677), -= (10:59:27.952), -1 (10:59:28.458), -; (10:59:28.738), -i (10:59:29.253), -&lt; (10:59:29.652), -arr (10:59:30.525), -. (10:59:30.766), -length (10:59:32.061), -; (10:59:32.305), -i (10:59:32.661), -+ (10:59:32.869), -+ (10:59:33.126), -) (10:59:33.350), -{ (10:59:35.506), -} (10:59:37.396), -if (10:59:41.288), -( (10:59:41.708), -arr (10:59:42.652), -[ (10:59:42.917), -i (10:59:43.246), -- (10:59:44.058), -1 (10:59:44.656), -] (10:59:44.854), -&gt; (10:59:45.546), -arr (10:59:46.616), -[ (10:59:46.969), -i (10:59:47.212), -] (10:59:47.751), -) (10:59:48.230), -{ (10:59:49.302), -} (10:59:50.413), -const (11:00:57.203), -aux (11:00:58.458), -= (11:01:01.660), -arr (11:01:02.684), -[ (11:01:02.941), -i (11:01:03.128), -- (11:01:03.607), -1 (11:01:04.198), -] (11:01:04.697), -; (11:01:05.017), -arr (11:01:06.389), -[ (11:01:06.650), -i (11:01:06.835), -- (11:01:07.252), -1 (11:01:07.757), -] (11:01:08.184), -= (11:01:08.961), -arr (11:01:09.861), -[ (11:01:10.052), -i (11:01:10.368), -] (11:01:10.513), -; (11:01:10.683), -arr (11:01:12.501), -[ (11:01:12.714), -i (11:01:12.894), -] (11:01:13.102), -= (11:01:13.537), -aux (11:01:14.449), -; (11:01:14.856), -swapped (11:02:15.877), -= (11:02:16.203), -true (11:02:17.158), -; (11:02:17.463), -while (11:02:23.923), -( (11:02:24.360), -swapped (11:02:25.916), -) (11:02:26.084), -; (11:02:26.436), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -function (11:08:36.630), -updateBars (11:08:38.342), -( (11:08:38.511), -) (11:08:38.687), -{ (11:08:39.319), -} (11:08:40.006), -const (11:09:21.850), -bars (11:09:22.876), -= (11:09:23.405), -document (11:09:24.920), -. (11:09:25.072), -getElementsByClassName (11:09:28.891), -( (11:09:28.949), -" (11:09:29.056), -bar (11:09:29.764), -" (11:09:29.897), -) (11:09:29.998), -; (11:09:30.476), -for (11:09:55.616), -( (11:09:55.956), -let (11:09:56.455), -i (11:09:56.677), -= (11:09:57.008), -0 (11:09:57.490), -; (11:09:57.512), -i (11:09:57.854), -&lt; (11:09:58.223), -bars (11:09:58.993), -. (11:09:59.214), -length (11:10:00.426), -; (11:10:00.634), -i (11:10:01.376), -+ (11:10:01.600), -+ (11:10:01.789), -) (11:10:01.880), -{ (11:10:02.609), -} (11:10:03.305), -bars (11:10:05.954), -[ (11:10:06.083), -i (11:10:06.207), -] (11:10:06.517), -. (11:10:06.753), -style (11:10:08.322), -. (11:10:08.474), -height (11:10:09.606), -= (11:10:12.868), -array (11:10:13.726), -[ (11:10:13.999), -i (11:10:14.138), -] (11:10:14.279), -* (11:10:14.846), -100 (11:10:15.517), -+ (11:10:16.137), -" (11:10:16.502), -% (11:10:16.625), -" (11:10:16.705), -; (11:10:17.104), -updateBars (11:12:30.664), -( (11:12:30.752), -) (11:12:30.906), -; (11:12:31.204), -await (11:13:47.348), -new (11:13:53.570), -Promise (11:13:54.982), -( (11:13:55.301), -resolve (11:13:59.055), -= (11:14:16.118), -&gt; (11:14:16.408), -setTimeout (11:14:18.857), -( (11:14:19.066), -resolve (11:14:23.324), -, (11:14:23.491), -100 (11:14:24.924), -) (11:14:31.103), -) (11:14:31.475), -; (11:14:32.118), -async (11:15:16.100), +const (00:00:00), +count (00:00:00), += (00:00:00), +50 (00:00:00), +; (00:00:00), +const (00:00:00), +array (00:00:00), += (00:00:00), +new (00:00:00), +Array (00:00:00), +( (00:00:00), +count (00:00:00), +) (00:00:00), +; (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +count (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +array (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), += (00:00:00), +Math (00:00:00), +. (00:00:00), +random (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +const (00:00:00), +visualizer (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +array (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bar (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +createElement (00:00:00), +( (00:00:00), +" (00:00:00), +div (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +visualizer (00:00:00), +. (00:00:00), +appendChild (00:00:00), +( (00:00:00), +bar (00:00:00), +) (00:00:00), +; (00:00:00), +bar (00:00:00), +. (00:00:00), +classList (00:00:00), +. (00:00:00), +add (00:00:00), +( (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +bar (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +height (00:00:00), += (00:00:00), +array (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +* (00:00:00), +100 (00:00:00), ++ (00:00:00), +" (00:00:00), +% (00:00:00), +" (00:00:00), +; (00:00:00), +function (00:00:00), +bubbleSort (00:00:00), +( (00:00:00), +array (00:00:00), +) (00:00:00), +function (00:00:00), +updatebars (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bars (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementByClassName (00:00:00), +( (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +) (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +bars (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +height (00:00:00), += (00:00:00), +array (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +* (00:00:00), +100 (00:00:00), ++ (00:00:00), +" (00:00:00), +% (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00), +async (00:00:00), +function (00:00:00), +bubbleSort (00:00:00), +( (00:00:00), +arr (00:00:00), +) (00:00:00), +{ (00:00:00), +do (00:00:00), +{ (00:00:00), +var (00:00:00), +swapped (00:00:00), += (00:00:00), +false (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +1 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +arr (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +if (00:00:00), +( (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +- (00:00:00), +1 (00:00:00), +] (00:00:00), +&gt; (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +aux (00:00:00), += (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +- (00:00:00), +1 (00:00:00), +] (00:00:00), +; (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +- (00:00:00), +1 (00:00:00), +] (00:00:00), += (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +; (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), += (00:00:00), +aux (00:00:00), +; (00:00:00), +swapped (00:00:00), += (00:00:00), +true (00:00:00), +; (00:00:00), +updateBars (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +await (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +100 (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +while (00:00:00), +( (00:00:00), +swapped (00:00:00), +) (00:00:00), +; (00:00:00)</t>
+        <t>-const (10:27:46.114) ~1.00, -count (10:27:47.499) ~1.00, -= (10:27:48.489) ~1.00, -50 (10:27:50.527) ~1.00, -; (10:27:51.439) ~1.00, -const (10:28:42.502) ~1.00, -array (10:28:45.898) ~1.00, -= (10:28:48.193) ~1.00, -new (10:28:49.261) ~1.00, -Array (10:28:50.400) ~1.00, -( (10:28:50.634) ~1.00, -count (10:28:52.202) ~1.00, -) (10:28:52.450) ~1.00, -; (10:28:52.802) ~1.00, -for (10:30:13.868) ~1.00, -( (10:30:14.352) ~1.00, -let (10:30:15.164) ~1.00, -i (10:30:15.672) ~1.00, -= (10:30:16.329) ~1.00, -0 (10:30:16.771) ~1.00, -; (10:30:17.011) ~1.00, -i (10:30:17.443) ~1.00, -&lt; (10:30:18.073) ~1.00, -count (10:30:20.284) ~1.00, -; (10:30:20.584) ~1.00, -i (10:30:47.713) ~1.00, -+ (10:30:48.171) ~1.00, -+ (10:30:48.660) ~1.00, -) (10:30:49.210) ~1.00, -{ (10:31:12.723) ~1.00, -array (10:31:16.948) ~1.00, -[ (10:31:17.188) ~1.00, -i (10:31:18.211) ~1.00, -] (10:31:22.021) ~1.00, -= (10:31:23.399) ~1.00, -Math (10:31:30.068) ~1.00, -. (10:31:30.292) ~1.00, -random (10:31:31.871) ~1.00, -( (10:31:32.250) ~1.00, -) (10:31:32.537) ~1.00, -; (10:31:32.818) ~1.00, -const (10:37:42.386) ~1.00, -visualizer (10:37:44.631) ~1.00, -= (10:37:45.082) ~1.00, -document (10:37:47.323) ~1.00, -. (10:37:47.760) ~1.00, -getElementById (10:38:03.158) ~1.00, -( (10:38:03.433) ~1.00, -" (10:38:19.019) ~1.00, -vis (10:38:19.926) ~1.00, -- (10:38:20.217) ~1.00, -123456 (10:38:22.251) ~1.00, -" (10:38:22.629) ~1.00, -) (10:38:22.754) ~1.00, -; (10:38:23.727) ~1.00, -for (10:38:50.477) ~1.00, -( (10:38:50.999) ~1.00, -let (10:38:51.733) ~1.00, -i (10:38:52.267) ~1.00, -= (10:38:52.612) ~1.00, -0 (10:38:53.033) ~1.00, -; (10:38:53.257) ~1.00, -i (10:38:53.739) ~1.00, -&lt; (10:38:54.145) ~1.00, -array (10:38:55.446) ~1.00, -. (10:38:55.684) ~1.00, -length (10:38:57.372) ~1.00, -; (10:38:57.593) ~1.00, -i (10:38:58.029) ~1.00, -+ (10:38:58.280) ~1.00, -+ (10:38:58.511) ~1.00, -) (10:38:58.809) ~1.00, -{ (10:39:16.312) ~1.00, -const (10:39:36.638) ~1.00, -bar (10:39:37.346) ~1.00, -= (10:39:37.875) ~1.00, -document (10:39:42.722) ~1.00, -. (10:39:42.888) ~1.00, -createElement (10:39:45.021) ~1.00, -( (10:39:45.078) ~1.00, -" (10:39:45.883) ~1.00, -div (10:39:48.709) ~1.00, -" (10:39:48.892) ~1.00, -) (10:39:49.655) ~1.00, -; (10:39:49.907) ~1.00, -visualizer (10:40:27.992) ~1.00, -. (10:40:28.151) ~1.00, -appendChild (10:40:30.229) ~1.00, -( (10:40:30.435) ~1.00, -bar (10:40:31.317) ~1.00, -) (10:40:31.505) ~1.00, -; (10:40:32.101) ~1.00, -bar (10:42:30.607) ~1.00, -. (10:42:30.785) ~1.00, -classList (10:42:32.670) ~1.00, -. (10:42:32.869) ~1.00, -add (10:42:33.487) ~1.00, -( (10:42:33.684) ~1.00, -" (10:42:33.916) ~1.00, -bar (10:42:35.380) ~1.00, -" (10:42:35.625) ~1.00, -) (10:42:36.061) ~1.00, -; (10:42:36.565) ~1.00, -bar (10:50:10.577) ~1.00, -. (10:50:10.720) ~1.00, -style (10:50:11.842) ~1.00, -. (10:50:12.547) ~1.00, -height (10:50:14.172) ~1.00, -= (10:50:15.244) ~1.00, -array (10:50:17.753) ~1.00, -[ (10:50:17.905) ~1.00, -i (10:50:18.168) ~1.00, -] (10:50:18.460) ~1.00, -* (10:50:28.020) ~1.00, -100 (10:50:29.694) ~1.00, -+ (10:50:38.934) ~1.00, -" (10:50:40.368) ~1.00, -% (10:50:40.883) ~1.00, -" (10:50:41.432) ~1.00, -; (10:50:48.660) ~1.00, -function (10:57:37.492) ~1.00, -bubbleSort (10:57:42.836) ~1.00, -( (10:57:43.053) ~1.00, -arr (10:57:49.140) ~1.00, -) (10:57:49.861) ~1.00, -{ (10:57:54.715) ~1.00, -} (10:57:57.644) ~1.00, -do (10:58:33.576) ~1.00, -{ (10:58:34.903) ~1.00, -} (10:58:35.895) ~1.00, -var (10:59:12.196) ~1.00, -swapped (10:59:20.551) ~1.00, -= (10:59:21.101) ~1.00, -false (10:59:23.105) ~1.00, -; (10:59:24.221), -for (10:59:26.374) ~1.00, -( (10:59:26.727) ~1.00, -let (10:59:27.295) ~1.00, -i (10:59:27.677) ~1.00, -= (10:59:27.952) ~1.00, -1 (10:59:28.458) ~1.00, -; (10:59:28.738) ~1.00, -i (10:59:29.253) ~1.00, -&lt; (10:59:29.652) ~1.00, -arr (10:59:30.525) ~1.00, -. (10:59:30.766) ~1.00, -length (10:59:32.061) ~1.00, -; (10:59:32.305) ~1.00, -i (10:59:32.661) ~1.00, -+ (10:59:32.869) ~1.00, -+ (10:59:33.126) ~1.00, -) (10:59:33.350) ~1.00, -{ (10:59:35.506) ~1.00, -} (10:59:37.396), -if (10:59:41.288) ~1.00, -( (10:59:41.708) ~1.00, -arr (10:59:42.652) ~1.00, -[ (10:59:42.917) ~1.00, -i (10:59:43.246) ~1.00, -- (10:59:44.058) ~1.00, -1 (10:59:44.656) ~1.00, -] (10:59:44.854) ~1.00, -&gt; (10:59:45.546) ~1.00, -arr (10:59:46.616) ~1.00, -[ (10:59:46.969) ~1.00, -i (10:59:47.212) ~1.00, -] (10:59:47.751) ~1.00, -) (10:59:48.230) ~1.00, -{ (10:59:49.302) ~1.00, -} (10:59:50.413), -const (11:00:57.203) ~1.00, -aux (11:00:58.458) ~1.00, -= (11:01:01.660) ~1.00, -arr (11:01:02.684) ~1.00, -[ (11:01:02.941) ~1.00, -i (11:01:03.128) ~1.00, -- (11:01:03.607) ~1.00, -1 (11:01:04.198) ~1.00, -] (11:01:04.697) ~1.00, -; (11:01:05.017) ~1.00, -arr (11:01:06.389) ~1.00, -[ (11:01:06.650) ~1.00, -i (11:01:06.835) ~1.00, -- (11:01:07.252) ~1.00, -1 (11:01:07.757) ~1.00, -] (11:01:08.184) ~1.00, -= (11:01:08.961) ~1.00, -arr (11:01:09.861) ~1.00, -[ (11:01:10.052) ~1.00, -i (11:01:10.368) ~1.00, -] (11:01:10.513) ~1.00, -; (11:01:10.683) ~1.00, -arr (11:01:12.501) ~1.00, -[ (11:01:12.714) ~1.00, -i (11:01:12.894) ~1.00, -] (11:01:13.102) ~1.00, -= (11:01:13.537) ~1.00, -aux (11:01:14.449) ~1.00, -; (11:01:14.856) ~1.00, -swapped (11:02:15.877) ~1.00, -= (11:02:16.203) ~1.00, -true (11:02:17.158) ~1.00, -; (11:02:17.463) ~1.00, -while (11:02:23.923) ~1.00, -( (11:02:24.360) ~1.00, -swapped (11:02:25.916) ~1.00, -) (11:02:26.084) ~1.00, -; (11:02:26.436) ~1.00, +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118) ~1.00, -( (11:08:34.128) ~1.00, -array (11:08:34.178) ~1.00, -) (11:08:34.188) ~1.00, -; (11:08:34.198), -function (11:08:36.630) ~1.00, -updateBars (11:08:38.342) ~0.90, -( (11:08:38.511) ~1.00, -) (11:08:38.687) ~1.00, -{ (11:08:39.319) ~1.00, -} (11:08:40.006) ~1.00, -const (11:09:21.850) ~1.00, -bars (11:09:22.876) ~1.00, -= (11:09:23.405) ~1.00, -document (11:09:24.920) ~1.00, -. (11:09:25.072) ~1.00, -getElementsByClassName (11:09:28.891) ~0.95, -( (11:09:28.949) ~1.00, -" (11:09:29.056) ~1.00, -bar (11:09:29.764) ~1.00, -" (11:09:29.897) ~1.00, -) (11:09:29.998) ~1.00, -; (11:09:30.476), -for (11:09:55.616) ~1.00, -( (11:09:55.956) ~1.00, -let (11:09:56.455) ~1.00, -i (11:09:56.677) ~1.00, -= (11:09:57.008) ~1.00, -0 (11:09:57.490) ~1.00, -; (11:09:57.512) ~1.00, -i (11:09:57.854) ~1.00, -&lt; (11:09:58.223) ~1.00, -bars (11:09:58.993) ~1.00, -. (11:09:59.214) ~1.00, -length (11:10:00.426) ~1.00, -; (11:10:00.634) ~1.00, -i (11:10:01.376) ~1.00, -+ (11:10:01.600) ~1.00, -+ (11:10:01.789) ~1.00, -) (11:10:01.880) ~1.00, -{ (11:10:02.609) ~1.00, -} (11:10:03.305) ~1.00, -bars (11:10:05.954) ~1.00, -[ (11:10:06.083) ~1.00, -i (11:10:06.207) ~1.00, -] (11:10:06.517) ~1.00, -. (11:10:06.753) ~1.00, -style (11:10:08.322) ~1.00, -. (11:10:08.474) ~1.00, -height (11:10:09.606) ~1.00, -= (11:10:12.868) ~1.00, -array (11:10:13.726) ~1.00, -[ (11:10:13.999) ~1.00, -i (11:10:14.138) ~1.00, -] (11:10:14.279) ~1.00, -* (11:10:14.846) ~1.00, -100 (11:10:15.517) ~1.00, -+ (11:10:16.137) ~1.00, -" (11:10:16.502) ~1.00, -% (11:10:16.625) ~1.00, -" (11:10:16.705) ~1.00, -; (11:10:17.104) ~1.00, -updateBars (11:12:30.664) ~1.00, -( (11:12:30.752) ~1.00, -) (11:12:30.906) ~1.00, -; (11:12:31.204) ~1.00, -await (11:13:47.348) ~1.00, -new (11:13:53.570) ~1.00, -Promise (11:13:54.982) ~1.00, -( (11:13:55.301) ~1.00, -resolve (11:13:59.055) ~1.00, -= (11:14:16.118) ~1.00, -&gt; (11:14:16.408) ~1.00, -setTimeout (11:14:18.857) ~1.00, -( (11:14:19.066) ~1.00, -resolve (11:14:23.324) ~1.00, -, (11:14:23.491) ~1.00, -100 (11:14:24.924) ~1.00, -) (11:14:31.103) ~1.00, -) (11:14:31.475) ~1.00, -; (11:14:32.118) ~1.00, -async (11:15:16.100) ~1.00, +const (00:00:00), +count (00:00:00), += (00:00:00), +50 (00:00:00), +; (00:00:00), +const (00:00:00), +array (00:00:00), += (00:00:00), +new (00:00:00), +Array (00:00:00), +( (00:00:00), +count (00:00:00), +) (00:00:00), +; (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +count (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +array (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), += (00:00:00), +Math (00:00:00), +. (00:00:00), +random (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +const (00:00:00), +visualizer (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +array (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bar (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +createElement (00:00:00), +( (00:00:00), +" (00:00:00), +div (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +visualizer (00:00:00), +. (00:00:00), +appendChild (00:00:00), +( (00:00:00), +bar (00:00:00), +) (00:00:00), +; (00:00:00), +bar (00:00:00), +. (00:00:00), +classList (00:00:00), +. (00:00:00), +add (00:00:00), +( (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +bar (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +height (00:00:00), += (00:00:00), +array (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +* (00:00:00), +100 (00:00:00), ++ (00:00:00), +" (00:00:00), +% (00:00:00), +" (00:00:00), +; (00:00:00), +function (00:00:00), +bubbleSort (00:00:00), +( (00:00:00), +array (00:00:00), +) (00:00:00), +function (00:00:00), +updatebars (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bars (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementByClassName (00:00:00), +( (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +) (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +bars (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +height (00:00:00), += (00:00:00), +array (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +* (00:00:00), +100 (00:00:00), ++ (00:00:00), +" (00:00:00), +% (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00), +async (00:00:00), +function (00:00:00), +bubbleSort (00:00:00), +( (00:00:00), +arr (00:00:00), +) (00:00:00), +{ (00:00:00), +do (00:00:00), +{ (00:00:00), +var (00:00:00), +swapped (00:00:00), += (00:00:00), +false (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +1 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +arr (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +if (00:00:00), +( (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +- (00:00:00), +1 (00:00:00), +] (00:00:00), +&gt; (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +aux (00:00:00), += (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +- (00:00:00), +1 (00:00:00), +] (00:00:00), +; (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +- (00:00:00), +1 (00:00:00), +] (00:00:00), += (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +; (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), += (00:00:00), +aux (00:00:00), +; (00:00:00), +swapped (00:00:00), += (00:00:00), +true (00:00:00), +; (00:00:00), +updateBars (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +await (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +100 (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +while (00:00:00), +( (00:00:00), +swapped (00:00:00), +) (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E12" authorId="0" shapeId="0">
@@ -247,7 +247,7 @@
     </comment>
     <comment ref="O12" authorId="0" shapeId="0">
       <text>
-        <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:17:21.139), -# (10:19:53.296), -vis (10:19:54.003), -- (10:19:54.226), -123456 (10:19:55.544), -{ (10:20:02.452), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +{ (00:00:00)</t>
+        <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:17:21.139) ~1.00, -# (10:19:53.296) ~1.00, -vis (10:19:54.003) ~1.00, -- (10:19:54.226) ~1.00, -123456 (10:19:55.544) ~1.00, -{ (10:20:02.452) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +{ (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E19" authorId="0" shapeId="0">
@@ -262,17 +262,17 @@
     </comment>
     <comment ref="M19" authorId="0" shapeId="0">
       <text>
-        <t>-&lt; (10:12:43.632), -title (10:12:44.512), -&gt; (10:12:44.622), -Sorting (10:12:45.778), -Visualizer (10:12:47.677), -&lt; (10:12:47.904), -/ (10:12:48.260), -title (10:12:49.434), -&gt; (10:12:49.841), +&lt; (00:00:00), +title (00:00:00), +&gt; (00:00:00), +Sorting (00:00:00), +Visualizer (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +title (00:00:00), +&gt; (00:00:00)</t>
+        <t>-&lt; (10:12:43.632) ~1.00, -title (10:12:44.512) ~1.00, -&gt; (10:12:44.622) ~1.00, -Sorting (10:12:45.778) ~1.00, -Visualizer (10:12:47.677) ~1.00, -&lt; (10:12:47.904) ~1.00, -/ (10:12:48.260) ~1.00, -title (10:12:49.434) ~1.00, -&gt; (10:12:49.841) ~1.00, +&lt; (00:00:00), +title (00:00:00), +&gt; (00:00:00), +Sorting (00:00:00), +Visualizer (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +title (00:00:00), +&gt; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O19" authorId="0" shapeId="0">
       <text>
-        <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:17:21.139), -# (10:19:53.296), -vis (10:19:54.003), -- (10:19:54.226), -123456 (10:19:55.544), -{ (10:20:02.452), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +{ (00:00:00)</t>
+        <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:17:21.139) ~1.00, -# (10:19:53.296) ~1.00, -vis (10:19:54.003) ~1.00, -- (10:19:54.226) ~1.00, -123456 (10:19:55.544) ~1.00, -{ (10:20:02.452) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +{ (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q19" authorId="0" shapeId="0">
       <text>
-        <t>+bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -updateBars (11:12:30.664), -( (11:12:30.752), -) (11:12:30.906), -; (11:12:31.204), -await (11:13:47.348), -new (11:13:53.570), -Promise (11:13:54.982), -( (11:13:55.301), -resolve (11:13:59.055), -= (11:14:16.118), -&gt; (11:14:16.408), -setTimeout (11:14:18.857), -( (11:14:19.066), -resolve (11:14:23.324), -, (11:14:23.491), -100 (11:14:24.924), -) (11:14:31.103), -) (11:14:31.475), -; (11:14:32.118), +bubbleSort (00:00:00), +( (00:00:00), +array (00:00:00), +) (00:00:00), +; (00:00:00), +updateBars (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +await (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +100 (00:00:00), +) (00:00:00), +) (00:00:00)</t>
+        <t>+bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118) ~1.00, -( (11:08:34.128) ~1.00, -array (11:08:34.178) ~1.00, -) (11:08:34.188) ~1.00, -; (11:08:34.198) ~1.00, -updateBars (11:12:30.664) ~1.00, -( (11:12:30.752) ~1.00, -) (11:12:30.906) ~1.00, -; (11:12:31.204) ~1.00, -await (11:13:47.348) ~1.00, -new (11:13:53.570) ~1.00, -Promise (11:13:54.982) ~1.00, -( (11:13:55.301) ~1.00, -resolve (11:13:59.055) ~1.00, -= (11:14:16.118) ~1.00, -&gt; (11:14:16.408) ~1.00, -setTimeout (11:14:18.857) ~1.00, -( (11:14:19.066) ~1.00, -resolve (11:14:23.324) ~1.00, -, (11:14:23.491) ~1.00, -100 (11:14:24.924) ~1.00, -) (11:14:31.103) ~1.00, -) (11:14:31.475) ~1.00, -; (11:14:32.118), +bubbleSort (00:00:00), +( (00:00:00), +array (00:00:00), +) (00:00:00), +; (00:00:00), +updateBars (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +await (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +100 (00:00:00), +) (00:00:00), +) (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E21" authorId="0" shapeId="0">
@@ -292,17 +292,17 @@
     </comment>
     <comment ref="M21" authorId="0" shapeId="0">
       <text>
-        <t>-Visualizer (10:12:47.677), +Visualiser (00:00:00)</t>
+        <t>-Visualizer (10:12:47.677) ~0.90, +Visualiser (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O21" authorId="0" shapeId="0">
       <text>
-        <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:17:21.139), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), -0px (10:48:03.827), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +0 (00:00:00)</t>
+        <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:17:21.139) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, -0px (10:48:03.827) ~0.33, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +0 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q21" authorId="0" shapeId="0">
       <text>
-        <t>-getElementsByClassName (11:09:28.891), -bars (11:09:58.993), -100 (11:14:24.924), +querySelectorAll (00:00:00), +. (00:00:00), +array (00:00:00), +10 (00:00:00)</t>
+        <t>-getElementsByClassName (11:09:28.891) ~0.18, -bars (11:09:58.993) ~0.20, -100 (11:14:24.924) ~0.67, +querySelectorAll (00:00:00), +. (00:00:00), +array (00:00:00), +10 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E24" authorId="0" shapeId="0">
@@ -322,7 +322,7 @@
     </comment>
     <comment ref="O24" authorId="0" shapeId="0">
       <text>
-        <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:17:21.139), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), -. (10:43:24.242), -bar (10:43:31.288), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +. (00:00:00), +bar (00:00:00)</t>
+        <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:17:21.139) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, -. (10:43:24.242) ~1.00, -bar (10:43:31.288) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +. (00:00:00), +bar (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q24" authorId="0" shapeId="0">
@@ -347,12 +347,12 @@
     </comment>
     <comment ref="O25" authorId="0" shapeId="0">
       <text>
-        <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:17:21.139), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+        <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:17:21.139) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q25" authorId="0" shapeId="0">
       <text>
-        <t>-length (10:38:57.372), -classList (10:42:32.670), -length (10:59:32.061), -getElementsByClassName (11:09:28.891), -length (11:10:00.426), -Promise (11:13:54.982), +lenght (00:00:00), +ClassList (00:00:00), +getElementByClassName (00:00:00), +lenght (00:00:00), +lenght (00:00:00), +promise (00:00:00)</t>
+        <t>-length (10:38:57.372) ~0.67, -classList (10:42:32.670) ~0.89, -length (10:59:32.061) ~0.67, -getElementsByClassName (11:09:28.891) ~0.95, -length (11:10:00.426) ~0.67, -Promise (11:13:54.982) ~0.86, +lenght (00:00:00), +ClassList (00:00:00), +getElementByClassName (00:00:00), +lenght (00:00:00), +lenght (00:00:00), +promise (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E30" authorId="0" shapeId="0">
@@ -372,12 +372,12 @@
     </comment>
     <comment ref="O30" authorId="0" shapeId="0">
       <text>
-        <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:17:21.139), -# (10:19:53.296), -vis (10:19:54.003), -- (10:19:54.226), -123456 (10:19:55.544), -{ (10:20:02.452), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +{ (00:00:00)</t>
+        <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:17:21.139) ~1.00, -# (10:19:53.296) ~1.00, -vis (10:19:54.003) ~1.00, -- (10:19:54.226) ~1.00, -123456 (10:19:55.544) ~1.00, -{ (10:20:02.452) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +{ (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q30" authorId="0" shapeId="0">
       <text>
-        <t>-function (10:57:37.492), -bubbleSort (10:57:42.836), -( (10:57:43.053), -arr (10:57:49.140), -) (10:57:49.861), -{ (10:57:54.715), -async (11:15:16.100), +async (00:00:00), +function (00:00:00), +bubbleSort (00:00:00), +( (00:00:00), +arr (00:00:00), +) (00:00:00), +{ (00:00:00)</t>
+        <t>-function (10:57:37.492) ~1.00, -bubbleSort (10:57:42.836) ~1.00, -( (10:57:43.053) ~1.00, -arr (10:57:49.140) ~1.00, -) (10:57:49.861) ~1.00, -{ (10:57:54.715) ~1.00, -async (11:15:16.100) ~1.00, +async (00:00:00), +function (00:00:00), +bubbleSort (00:00:00), +( (00:00:00), +arr (00:00:00), +) (00:00:00), +{ (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E31" authorId="0" shapeId="0">
@@ -397,17 +397,17 @@
     </comment>
     <comment ref="M31" authorId="0" shapeId="0">
       <text>
-        <t>-Sorting (10:12:45.778), +sorting (00:00:00)</t>
+        <t>-Sorting (10:12:45.778) ~0.86, +sorting (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O31" authorId="0" shapeId="0">
       <text>
-        <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:17:21.139), -# (10:19:53.296), -vis (10:19:54.003), -- (10:19:54.226), -123456 (10:19:55.544), -{ (10:20:02.452), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), -. (10:43:24.242), -bar (10:43:31.288), -{ (10:43:32.996), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +{ (00:00:00), +. (00:00:00), +bar (00:00:00), +{ (00:00:00)</t>
+        <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:17:21.139) ~1.00, -# (10:19:53.296) ~1.00, -vis (10:19:54.003) ~1.00, -- (10:19:54.226) ~1.00, -123456 (10:19:55.544) ~1.00, -{ (10:20:02.452) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, -. (10:43:24.242) ~1.00, -bar (10:43:31.288) ~1.00, -{ (10:43:32.996) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +{ (00:00:00), +. (00:00:00), +bar (00:00:00), +{ (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q31" authorId="0" shapeId="0">
       <text>
-        <t>-for (10:59:26.374), -( (10:59:26.727), -let (10:59:27.295), -i (10:59:27.677), -= (10:59:27.952), -1 (10:59:28.458), -; (10:59:28.738), -i (10:59:29.253), -&lt; (10:59:29.652), -arr (10:59:30.525), -. (10:59:30.766), -length (10:59:32.061), -; (10:59:32.305), -i (10:59:32.661), -+ (10:59:32.869), -+ (10:59:33.126), -) (10:59:33.350), -{ (10:59:35.506), -if (10:59:41.288), -( (10:59:41.708), -arr (10:59:42.652), -[ (10:59:42.917), -i (10:59:43.246), -- (10:59:44.058), -1 (10:59:44.656), -] (10:59:44.854), -&gt; (10:59:45.546), -arr (10:59:46.616), -[ (10:59:46.969), -i (10:59:47.212), -] (10:59:47.751), -) (10:59:48.230), -{ (10:59:49.302), -const (11:00:57.203), -aux (11:00:58.458), -= (11:01:01.660), -arr (11:01:02.684), -[ (11:01:02.941), -i (11:01:03.128), -- (11:01:03.607), -1 (11:01:04.198), -] (11:01:04.697), -; (11:01:05.017), -arr (11:01:06.389), -[ (11:01:06.650), -i (11:01:06.835), -- (11:01:07.252), -1 (11:01:07.757), -] (11:01:08.184), -= (11:01:08.961), -arr (11:01:09.861), -[ (11:01:10.052), -i (11:01:10.368), -] (11:01:10.513), -; (11:01:10.683), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +arr (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +if (00:00:00), +( (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +- (00:00:00), +1 (00:00:00), +] (00:00:00), +&gt; (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +aux (00:00:00), += (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +- (00:00:00), +1 (00:00:00), +] (00:00:00), +; (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +- (00:00:00), +1 (00:00:00), +] (00:00:00), += (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +; (00:00:00)</t>
+        <t>-for (10:59:26.374) ~1.00, -( (10:59:26.727) ~1.00, -let (10:59:27.295) ~1.00, -i (10:59:27.677) ~1.00, -= (10:59:27.952) ~1.00, -1 (10:59:28.458) ~0.00, -; (10:59:28.738) ~1.00, -i (10:59:29.253) ~1.00, -&lt; (10:59:29.652) ~1.00, -arr (10:59:30.525) ~1.00, -. (10:59:30.766) ~1.00, -length (10:59:32.061) ~1.00, -; (10:59:32.305) ~1.00, -i (10:59:32.661) ~1.00, -+ (10:59:32.869) ~1.00, -+ (10:59:33.126) ~1.00, -) (10:59:33.350) ~1.00, -{ (10:59:35.506) ~1.00, -if (10:59:41.288) ~1.00, -( (10:59:41.708) ~1.00, -arr (10:59:42.652) ~1.00, -[ (10:59:42.917) ~1.00, -i (10:59:43.246) ~1.00, -- (10:59:44.058) ~1.00, -1 (10:59:44.656) ~1.00, -] (10:59:44.854) ~1.00, -&gt; (10:59:45.546) ~1.00, -arr (10:59:46.616) ~1.00, -[ (10:59:46.969) ~1.00, -i (10:59:47.212) ~1.00, -] (10:59:47.751) ~1.00, -) (10:59:48.230) ~1.00, -{ (10:59:49.302) ~1.00, -const (11:00:57.203) ~1.00, -aux (11:00:58.458) ~1.00, -= (11:01:01.660) ~1.00, -arr (11:01:02.684) ~1.00, -[ (11:01:02.941) ~1.00, -i (11:01:03.128) ~1.00, -- (11:01:03.607) ~1.00, -1 (11:01:04.198) ~1.00, -] (11:01:04.697) ~1.00, -; (11:01:05.017) ~1.00, -arr (11:01:06.389) ~1.00, -[ (11:01:06.650) ~1.00, -i (11:01:06.835) ~1.00, -- (11:01:07.252) ~1.00, -1 (11:01:07.757) ~1.00, -] (11:01:08.184) ~1.00, -= (11:01:08.961) ~1.00, -arr (11:01:09.861) ~1.00, -[ (11:01:10.052) ~1.00, -i (11:01:10.368) ~1.00, -] (11:01:10.513) ~1.00, -; (11:01:10.683) ~1.00, +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +arr (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +if (00:00:00), +( (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +- (00:00:00), +1 (00:00:00), +] (00:00:00), +&gt; (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +aux (00:00:00), += (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +- (00:00:00), +1 (00:00:00), +] (00:00:00), +; (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +- (00:00:00), +1 (00:00:00), +] (00:00:00), += (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E36" authorId="0" shapeId="0">
@@ -427,17 +427,17 @@
     </comment>
     <comment ref="M36" authorId="0" shapeId="0">
       <text>
-        <t>-Sorting (10:13:13.802), +/ (00:00:00), +sorting (00:00:00)</t>
+        <t>-Sorting (10:13:13.802) ~0.86, +/ (00:00:00), +sorting (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O36" authorId="0" shapeId="0">
       <text>
-        <t>-center (10:17:20.707), -# (10:19:53.296), -vis (10:19:54.003), -- (10:19:54.226), -123456 (10:19:55.544), -{ (10:20:02.452), -height (10:20:07.891), -200px (10:20:09.051), -flex (10:21:58.800), -direction (10:22:01.758), -column (10:22:03.223), -align (10:24:12.446), -items (10:24:13.500), -. (10:43:24.242), -bar (10:43:31.288), -{ (10:43:32.996), -width (10:43:37.644), -7px (10:43:39.527), -height (10:43:47.504), -100 (10:43:48.485), -% (10:43:48.586), -background (10:44:24.231), -- (10:44:24.311), -color (10:44:25.031), -: (10:44:25.154), -black (10:44:26.271), -; (10:44:26.592), +200px* (10:50:08.740), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +red* (10:50:09.332), +align (00:00:00), +items (00:00:00), +center (00:00:00), +flex (00:00:00), +direction (00:00:00), +column (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +{ (00:00:00), +height (00:00:00), +: (00:00:00), +; (00:00:00), +. (00:00:00), +bar (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +7px (00:00:00), +; (00:00:00), +height (00:00:00), +100 (00:00:00), +% (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +black (00:00:00)</t>
+        <t>-center (10:17:20.707) ~0.17, -# (10:19:53.296) ~1.00, -vis (10:19:54.003) ~1.00, -- (10:19:54.226) ~1.00, -123456 (10:19:55.544) ~1.00, -{ (10:20:02.452) ~1.00, -height (10:20:07.891) ~1.00, -200px (10:20:09.051) ~0.00, -flex (10:21:58.800) ~0.20, -direction (10:22:01.758) ~0.22, -column (10:22:03.223) ~0.17, -align (10:24:12.446) ~0.20, -items (10:24:13.500) ~0.22, -. (10:43:24.242) ~1.00, -bar (10:43:31.288) ~1.00, -{ (10:43:32.996) ~1.00, -width (10:43:37.644) ~1.00, -7px (10:43:39.527) ~1.00, -height (10:43:47.504) ~1.00, -100 (10:43:48.485) ~1.00, -% (10:43:48.586) ~1.00, -background (10:44:24.231) ~1.00, -- (10:44:24.311) ~1.00, -color (10:44:25.031) ~1.00, -: (10:44:25.154), -black (10:44:26.271) ~1.00, -; (10:44:26.592), +200px* (10:50:08.740), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +red* (10:50:09.332), +align (00:00:00), +items (00:00:00), +center (00:00:00), +flex (00:00:00), +direction (00:00:00), +column (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +{ (00:00:00), +height (00:00:00), +: (00:00:00), +; (00:00:00), +. (00:00:00), +bar (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +7px (00:00:00), +; (00:00:00), +height (00:00:00), +100 (00:00:00), +% (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +black (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q36" authorId="0" shapeId="0">
       <text>
-        <t>-50 (10:27:50.527), -. (10:31:30.292), -. (10:38:55.684), -. (10:40:28.151), -arr (11:01:09.861), -; (11:01:10.683), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -array (11:08:34.178), -function (11:08:36.630), -updateBars (11:08:38.342), -( (11:08:38.511), -) (11:08:38.687), -{ (11:08:39.319), -const (11:09:21.850), -bars (11:09:22.876), -= (11:09:23.405), -document (11:09:24.920), -. (11:09:25.072), -getElementsByClassName (11:09:28.891), -( (11:09:28.949), -" (11:09:29.056), -bar (11:09:29.764), -" (11:09:29.897), -) (11:09:29.998), -; (11:09:30.476), -for (11:09:55.616), -( (11:09:55.956), -let (11:09:56.455), -i (11:09:56.677), -= (11:09:57.008), -0 (11:09:57.490), -; (11:09:57.512), -i (11:09:57.854), -&lt; (11:09:58.223), -bars (11:09:58.993), -. (11:09:59.214), -length (11:10:00.426), -; (11:10:00.634), -i (11:10:01.376), -+ (11:10:01.600), -+ (11:10:01.789), -) (11:10:01.880), -{ (11:10:02.609), -bars (11:10:05.954), -[ (11:10:06.083), -i (11:10:06.207), -] (11:10:06.517), -. (11:10:06.753), -style (11:10:08.322), -. (11:10:08.474), -height (11:10:09.606), -= (11:10:12.868), -array (11:10:13.726), -[ (11:10:13.999), -i (11:10:14.138), -] (11:10:14.279), -* (11:10:14.846), -100 (11:10:15.517), -+ (11:10:16.137), -" (11:10:16.502), -% (11:10:16.625), -" (11:10:16.705), -; (11:10:17.104), -Promise (11:13:54.982), +20 (00:00:00), +, (00:00:00), +bubblesort (00:00:00), +, (00:00:00), +, (00:00:00), +function (00:00:00), +updateBars (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bars (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementsByClassName (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +bars (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +height (00:00:00), += (00:00:00), +array (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +* (00:00:00), +100 (00:00:00), ++ (00:00:00), +" (00:00:00), +% (00:00:00), +" (00:00:00), +aee (00:00:00), +promise (00:00:00)</t>
+        <t>-50 (10:27:50.527) ~0.50, -. (10:31:30.292) ~0.00, -. (10:38:55.684) ~0.00, -. (10:40:28.151) ~0.00, -arr (11:01:09.861) ~0.33, -; (11:01:10.683), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -array (11:08:34.178), -function (11:08:36.630) ~1.00, -updateBars (11:08:38.342) ~1.00, -( (11:08:38.511) ~1.00, -) (11:08:38.687) ~1.00, -{ (11:08:39.319) ~1.00, -const (11:09:21.850) ~1.00, -bars (11:09:22.876) ~1.00, -= (11:09:23.405) ~1.00, -document (11:09:24.920) ~1.00, -. (11:09:25.072) ~1.00, -getElementsByClassName (11:09:28.891) ~1.00, -( (11:09:28.949), -" (11:09:29.056) ~1.00, -bar (11:09:29.764) ~1.00, -" (11:09:29.897) ~1.00, -) (11:09:29.998), -; (11:09:30.476), -for (11:09:55.616) ~1.00, -( (11:09:55.956) ~1.00, -let (11:09:56.455) ~1.00, -i (11:09:56.677) ~1.00, -= (11:09:57.008) ~1.00, -0 (11:09:57.490) ~1.00, -; (11:09:57.512) ~1.00, -i (11:09:57.854) ~1.00, -&lt; (11:09:58.223) ~1.00, -bars (11:09:58.993) ~1.00, -. (11:09:59.214) ~1.00, -length (11:10:00.426) ~1.00, -; (11:10:00.634) ~1.00, -i (11:10:01.376) ~1.00, -+ (11:10:01.600) ~1.00, -+ (11:10:01.789) ~1.00, -) (11:10:01.880) ~1.00, -{ (11:10:02.609) ~1.00, -bars (11:10:05.954) ~1.00, -[ (11:10:06.083) ~1.00, -i (11:10:06.207) ~1.00, -] (11:10:06.517) ~1.00, -. (11:10:06.753) ~1.00, -style (11:10:08.322) ~1.00, -. (11:10:08.474) ~1.00, -height (11:10:09.606) ~1.00, -= (11:10:12.868) ~1.00, -array (11:10:13.726) ~1.00, -[ (11:10:13.999) ~1.00, -i (11:10:14.138) ~1.00, -] (11:10:14.279) ~1.00, -* (11:10:14.846) ~1.00, -100 (11:10:15.517) ~1.00, -+ (11:10:16.137) ~1.00, -" (11:10:16.502) ~1.00, -% (11:10:16.625) ~1.00, -" (11:10:16.705) ~1.00, -; (11:10:17.104), -Promise (11:13:54.982) ~0.86, +20 (00:00:00), +, (00:00:00), +bubblesort (00:00:00), +, (00:00:00), +, (00:00:00), +function (00:00:00), +updateBars (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bars (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementsByClassName (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +bars (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +height (00:00:00), += (00:00:00), +array (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +* (00:00:00), +100 (00:00:00), ++ (00:00:00), +" (00:00:00), +% (00:00:00), +" (00:00:00), +aee (00:00:00), +promise (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E42" authorId="0" shapeId="0">
@@ -457,12 +457,12 @@
     </comment>
     <comment ref="O42" authorId="0" shapeId="0">
       <text>
-        <t>-# (10:19:53.296), -vis (10:19:54.003), -- (10:19:54.226), -123456 (10:19:55.544), -{ (10:20:02.452), -height (10:20:07.891), -: (10:20:07.983), -200px (10:20:09.051), -; (10:20:09.451), -flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223), -; (10:22:03.455), +;* (10:50:09.333), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +coloumn (00:00:00), +; (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +{ (00:00:00), +height (00:00:00), +: (00:00:00), +200px (00:00:00)</t>
+        <t>-# (10:19:53.296) ~1.00, -vis (10:19:54.003) ~1.00, -- (10:19:54.226) ~1.00, -123456 (10:19:55.544) ~1.00, -{ (10:20:02.452) ~1.00, -height (10:20:07.891) ~1.00, -: (10:20:07.983) ~1.00, -200px (10:20:09.051) ~1.00, -; (10:20:09.451), -flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758) ~1.00, -: (10:22:01.952), -column (10:22:03.223) ~0.86, -; (10:22:03.455) ~1.00, +;* (10:50:09.333), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +coloumn (00:00:00), +; (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +{ (00:00:00), +height (00:00:00), +: (00:00:00), +200px (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q42" authorId="0" shapeId="0">
       <text>
-        <t>-let (10:38:51.733), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -let (11:09:56.455), -bars (11:09:58.993), -bars (11:10:05.954), -[ (11:10:06.083), -i (11:10:06.207), -] (11:10:06.517), -. (11:10:06.753), -style (11:10:08.322), -. (11:10:08.474), -height (11:10:09.606), -= (11:10:12.868), -array (11:10:13.726), -[ (11:10:13.999), -i (11:10:14.138), -] (11:10:14.279), -* (11:10:14.846), -100 (11:10:15.517), -+ (11:10:16.137), -" (11:10:16.502), -% (11:10:16.625), -" (11:10:16.705), -; (11:10:17.104), -updateBars (11:12:30.664), -( (11:12:30.752), -) (11:12:30.906), -; (11:12:31.204), -await (11:13:47.348), -new (11:13:53.570), -Promise (11:13:54.982), -( (11:13:55.301), -resolve (11:13:59.055), -= (11:14:16.118), -&gt; (11:14:16.408), -setTimeout (11:14:18.857), -( (11:14:19.066), -resolve (11:14:23.324), -, (11:14:23.491), -100 (11:14:24.924), -) (11:14:31.103), -) (11:14:31.475), -; (11:14:32.118), -async (11:15:16.100), +array (00:00:00)</t>
+        <t>-let (10:38:51.733), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -let (11:09:56.455), -bars (11:09:58.993) ~0.20, -bars (11:10:05.954), -[ (11:10:06.083), -i (11:10:06.207), -] (11:10:06.517), -. (11:10:06.753), -style (11:10:08.322), -. (11:10:08.474), -height (11:10:09.606), -= (11:10:12.868), -array (11:10:13.726), -[ (11:10:13.999), -i (11:10:14.138), -] (11:10:14.279), -* (11:10:14.846), -100 (11:10:15.517), -+ (11:10:16.137), -" (11:10:16.502), -% (11:10:16.625), -" (11:10:16.705), -; (11:10:17.104), -updateBars (11:12:30.664), -( (11:12:30.752), -) (11:12:30.906), -; (11:12:31.204), -await (11:13:47.348), -new (11:13:53.570), -Promise (11:13:54.982), -( (11:13:55.301), -resolve (11:13:59.055), -= (11:14:16.118), -&gt; (11:14:16.408), -setTimeout (11:14:18.857), -( (11:14:19.066), -resolve (11:14:23.324), -, (11:14:23.491), -100 (11:14:24.924), -) (11:14:31.103), -) (11:14:31.475), -; (11:14:32.118), -async (11:15:16.100), +array (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D45" authorId="0" shapeId="0">
@@ -487,7 +487,7 @@
     </comment>
     <comment ref="O45" authorId="0" shapeId="0">
       <text>
-        <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:17:21.139), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), -. (10:43:24.242), -bar (10:43:31.288), -{ (10:43:32.996), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +. (00:00:00), +bar (00:00:00), +{ (00:00:00)</t>
+        <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:17:21.139) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, -. (10:43:24.242) ~1.00, -bar (10:43:31.288) ~1.00, -{ (10:43:32.996) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +. (00:00:00), +bar (00:00:00), +{ (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q45" authorId="0" shapeId="0">
@@ -512,7 +512,7 @@
     </comment>
     <comment ref="O46" authorId="0" shapeId="0">
       <text>
-        <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:17:21.139), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), -display (10:47:38.305), -flex (10:47:39.551), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +red* (10:50:09.332), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+        <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:17:21.139) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, -display (10:47:38.305), -flex (10:47:39.551), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +red* (10:50:09.332), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E48" authorId="0" shapeId="0">
@@ -527,17 +527,17 @@
     </comment>
     <comment ref="M48" authorId="0" shapeId="0">
       <text>
-        <t>-title (10:12:49.434), -Visualizer (10:13:16.993), +tittle (00:00:00), +visualizer (00:00:00)</t>
+        <t>-title (10:12:49.434) ~0.83, -Visualizer (10:13:16.993) ~0.90, +tittle (00:00:00), +visualizer (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O48" authorId="0" shapeId="0">
       <text>
-        <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:17:21.139), -# (10:19:53.296), -vis (10:19:54.003), -- (10:19:54.226), -123456 (10:19:55.544), -{ (10:20:02.452), -height (10:20:07.891), -: (10:20:07.983), -200px (10:20:09.051), -; (10:20:09.451), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), -display (10:47:38.305), -: (10:47:38.437), -flex (10:47:39.551), -; (10:47:39.811), -margin (10:48:02.482), -: (10:48:02.549), -0px (10:48:03.827), -1px (10:48:07.241), -; (10:48:07.569), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), -align (10:57:30.272), -- (10:57:30.282), -items (10:57:30.332), -: (10:57:30.342), -flex (10:57:30.392), -- (10:57:30.402), -end (10:57:30.432), -; (10:57:30.442), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +{ (00:00:00), +height (00:00:00), +: (00:00:00), +200px (00:00:00), +; (00:00:00)</t>
+        <t>-: (10:17:19.374), -center (10:17:20.707) ~1.00, -; (10:17:21.139) ~1.00, -# (10:19:53.296) ~1.00, -vis (10:19:54.003) ~1.00, -- (10:19:54.226) ~1.00, -123456 (10:19:55.544) ~1.00, -{ (10:20:02.452) ~1.00, -height (10:20:07.891) ~1.00, -: (10:20:07.983), -200px (10:20:09.051), -; (10:20:09.451), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), -display (10:47:38.305), -: (10:47:38.437) ~1.00, -flex (10:47:39.551) ~0.20, -; (10:47:39.811) ~1.00, -margin (10:48:02.482), -: (10:48:02.549), -0px (10:48:03.827), -1px (10:48:07.241), -; (10:48:07.569), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), -align (10:57:30.272) ~1.00, -- (10:57:30.282) ~1.00, -items (10:57:30.332) ~1.00, -: (10:57:30.342) ~1.00, -flex (10:57:30.392), -- (10:57:30.402), -end (10:57:30.432), -; (10:57:30.442), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +{ (00:00:00), +height (00:00:00), +: (00:00:00), +200px (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q48" authorId="0" shapeId="0">
       <text>
-        <t>-array (10:28:45.898), -const (10:37:42.386), -visualizer (10:37:44.631), -= (10:37:45.082), -document (10:37:47.323), -. (10:37:47.760), -getElementById (10:38:03.158), -" (10:38:19.019), -vis (10:38:19.926), -- (10:38:20.217), -123456 (10:38:22.251), -" (10:38:22.629), +bubbleSort* (11:08:31.581), -array (11:08:34.178), -getElementsByClassName (11:09:28.891), +arry (00:00:00), +arry (00:00:00), +const (00:00:00), +visualizer (00:00:00), += (00:00:00), +documnet (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +arry (00:00:00), +getElementByClassName (00:00:00)</t>
+        <t>-array (10:28:45.898) ~0.80, -const (10:37:42.386) ~1.00, -visualizer (10:37:44.631) ~1.00, -= (10:37:45.082) ~1.00, -document (10:37:47.323) ~0.75, -. (10:37:47.760) ~1.00, -getElementById (10:38:03.158) ~1.00, -" (10:38:19.019) ~1.00, -vis (10:38:19.926) ~1.00, -- (10:38:20.217) ~1.00, -123456 (10:38:22.251) ~1.00, -" (10:38:22.629) ~1.00, +bubbleSort* (11:08:31.581), -array (11:08:34.178) ~0.80, -getElementsByClassName (11:09:28.891) ~0.95, +arry (00:00:00), +arry (00:00:00), +const (00:00:00), +visualizer (00:00:00), += (00:00:00), +documnet (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +arry (00:00:00), +getElementByClassName (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E50" authorId="0" shapeId="0">
@@ -557,17 +557,17 @@
     </comment>
     <comment ref="M50" authorId="0" shapeId="0">
       <text>
-        <t>-html (10:12:23.484), +htm (00:00:00)</t>
+        <t>-html (10:12:23.484) ~0.75, +htm (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O50" authorId="0" shapeId="0">
       <text>
-        <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:17:21.139), -# (10:19:53.296), -vis (10:19:54.003), -- (10:19:54.226), -123456 (10:19:55.544), -{ (10:20:02.452), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), -. (10:43:24.242), -bar (10:43:31.288), -{ (10:43:32.996), -- (10:57:30.402), -end (10:57:30.432), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +{ (00:00:00), +. (00:00:00), +bar (00:00:00), +{ (00:00:00)</t>
+        <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:17:21.139) ~1.00, -# (10:19:53.296) ~1.00, -vis (10:19:54.003) ~1.00, -- (10:19:54.226) ~1.00, -123456 (10:19:55.544) ~1.00, -{ (10:20:02.452) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, -. (10:43:24.242) ~1.00, -bar (10:43:31.288) ~1.00, -{ (10:43:32.996) ~1.00, -- (10:57:30.402), -end (10:57:30.432), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +{ (00:00:00), +. (00:00:00), +bar (00:00:00), +{ (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q50" authorId="0" shapeId="0">
       <text>
-        <t>-for (10:30:13.868), -( (10:30:14.352), -let (10:30:15.164), -i (10:30:15.672), -= (10:30:16.329), -0 (10:30:16.771), -; (10:30:17.011), -i (10:30:17.443), -&lt; (10:30:18.073), -count (10:30:20.284), -; (10:30:20.584), -i (10:30:47.713), -+ (10:30:48.171), -+ (10:30:48.660), -) (10:30:49.210), -{ (10:31:12.723), -function (10:57:37.492), -bubbleSort (10:57:42.836), -( (10:57:43.053), -arr (10:57:49.140), -) (10:57:49.861), -{ (10:57:54.715), -bubbleSort (11:08:34.118), -array (11:08:34.178), -function (11:08:36.630), -updateBars (11:08:38.342), -( (11:08:38.511), -) (11:08:38.687), -{ (11:08:39.319), -const (11:09:21.850), -bars (11:09:22.876), -= (11:09:23.405), -document (11:09:24.920), -. (11:09:25.072), -getElementsByClassName (11:09:28.891), -( (11:09:28.949), -" (11:09:29.056), -bar (11:09:29.764), -" (11:09:29.897), -) (11:09:29.998), -; (11:09:30.476), -for (11:09:55.616), -( (11:09:55.956), -let (11:09:56.455), -i (11:09:56.677), -= (11:09:57.008), -0 (11:09:57.490), -; (11:09:57.512), -i (11:09:57.854), -&lt; (11:09:58.223), -bars (11:09:58.993), -. (11:09:59.214), -length (11:10:00.426), -; (11:10:00.634), -i (11:10:01.376), -+ (11:10:01.600), -+ (11:10:01.789), -) (11:10:01.880), -{ (11:10:02.609), -bars (11:10:05.954), -[ (11:10:06.083), -i (11:10:06.207), -] (11:10:06.517), -. (11:10:06.753), -style (11:10:08.322), -. (11:10:08.474), -height (11:10:09.606), -= (11:10:12.868), -array (11:10:13.726), -[ (11:10:13.999), -i (11:10:14.138), -] (11:10:14.279), -* (11:10:14.846), -100 (11:10:15.517), -+ (11:10:16.137), -" (11:10:16.502), -% (11:10:16.625), -" (11:10:16.705), -; (11:10:17.104), -100 (11:14:24.924), -async (11:15:16.100), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +count (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +function (00:00:00), +updateBars (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bars (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementsByClassname (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +bars (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +height (00:00:00), += (00:00:00), +array (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +* (00:00:00), +100 (00:00:00), ++ (00:00:00), +" (00:00:00), +% (00:00:00), +" (00:00:00), +; (00:00:00), +async (00:00:00), +function (00:00:00), +bubbleSort (00:00:00), +( (00:00:00), +arr (00:00:00), +) (00:00:00), +{ (00:00:00), +10 (00:00:00)</t>
+        <t>-for (10:30:13.868) ~1.00, -( (10:30:14.352) ~1.00, -let (10:30:15.164) ~1.00, -i (10:30:15.672) ~1.00, -= (10:30:16.329) ~1.00, -0 (10:30:16.771) ~1.00, -; (10:30:17.011) ~1.00, -i (10:30:17.443) ~1.00, -&lt; (10:30:18.073) ~1.00, -count (10:30:20.284) ~1.00, -; (10:30:20.584) ~1.00, -i (10:30:47.713) ~1.00, -+ (10:30:48.171) ~1.00, -+ (10:30:48.660) ~1.00, -) (10:30:49.210) ~1.00, -{ (10:31:12.723) ~1.00, -function (10:57:37.492) ~1.00, -bubbleSort (10:57:42.836) ~1.00, -( (10:57:43.053) ~1.00, -arr (10:57:49.140) ~1.00, -) (10:57:49.861) ~1.00, -{ (10:57:54.715) ~1.00, -bubbleSort (11:08:34.118), -array (11:08:34.178), -function (11:08:36.630) ~1.00, -updateBars (11:08:38.342) ~1.00, -( (11:08:38.511) ~1.00, -) (11:08:38.687) ~1.00, -{ (11:08:39.319) ~1.00, -const (11:09:21.850) ~1.00, -bars (11:09:22.876) ~1.00, -= (11:09:23.405) ~1.00, -document (11:09:24.920) ~1.00, -. (11:09:25.072) ~1.00, -getElementsByClassName (11:09:28.891) ~0.95, -( (11:09:28.949), -" (11:09:29.056) ~1.00, -bar (11:09:29.764) ~1.00, -" (11:09:29.897) ~1.00, -) (11:09:29.998), -; (11:09:30.476), -for (11:09:55.616) ~1.00, -( (11:09:55.956) ~1.00, -let (11:09:56.455) ~1.00, -i (11:09:56.677) ~1.00, -= (11:09:57.008) ~1.00, -0 (11:09:57.490) ~1.00, -; (11:09:57.512) ~1.00, -i (11:09:57.854) ~1.00, -&lt; (11:09:58.223) ~1.00, -bars (11:09:58.993) ~1.00, -. (11:09:59.214) ~1.00, -length (11:10:00.426) ~1.00, -; (11:10:00.634) ~1.00, -i (11:10:01.376) ~1.00, -+ (11:10:01.600) ~1.00, -+ (11:10:01.789) ~1.00, -) (11:10:01.880) ~1.00, -{ (11:10:02.609) ~1.00, -bars (11:10:05.954) ~1.00, -[ (11:10:06.083) ~1.00, -i (11:10:06.207) ~1.00, -] (11:10:06.517) ~1.00, -. (11:10:06.753) ~1.00, -style (11:10:08.322) ~1.00, -. (11:10:08.474) ~1.00, -height (11:10:09.606) ~1.00, -= (11:10:12.868) ~1.00, -array (11:10:13.726) ~1.00, -[ (11:10:13.999) ~1.00, -i (11:10:14.138) ~1.00, -] (11:10:14.279) ~1.00, -* (11:10:14.846) ~1.00, -100 (11:10:15.517) ~1.00, -+ (11:10:16.137) ~1.00, -" (11:10:16.502) ~1.00, -% (11:10:16.625) ~1.00, -" (11:10:16.705) ~1.00, -; (11:10:17.104) ~1.00, -100 (11:14:24.924) ~0.67, -async (11:15:16.100) ~1.00, +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +count (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +function (00:00:00), +updateBars (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bars (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementsByClassname (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +bars (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +height (00:00:00), += (00:00:00), +array (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +* (00:00:00), +100 (00:00:00), ++ (00:00:00), +" (00:00:00), +% (00:00:00), +" (00:00:00), +; (00:00:00), +async (00:00:00), +function (00:00:00), +bubbleSort (00:00:00), +( (00:00:00), +arr (00:00:00), +) (00:00:00), +{ (00:00:00), +10 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E51" authorId="0" shapeId="0">
@@ -587,7 +587,7 @@
     </comment>
     <comment ref="O51" authorId="0" shapeId="0">
       <text>
-        <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:17:21.139), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+        <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:17:21.139) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E56" authorId="0" shapeId="0">
@@ -607,17 +607,17 @@
     </comment>
     <comment ref="M56" authorId="0" shapeId="0">
       <text>
-        <t>-&lt; (10:12:43.632), -title (10:12:44.512), -&gt; (10:12:44.622), -&lt; (10:12:47.904), -/ (10:12:48.260), -title (10:12:49.434), -&gt; (10:12:49.841), -Sorting (10:13:13.802), -Visualizer (10:13:16.993), -&lt; (10:13:17.335), -/ (10:13:17.789), -h1 (10:13:18.123), -&gt; (10:13:18.254), -&lt; (10:18:29.900), -div (10:18:30.558), -id (10:18:31.498), -= (10:18:31.631), -" (10:18:33.349), -vis (10:18:34.420), -- (10:18:37.062), -123456 (10:18:40.665), -" (10:18:40.947), -&gt; (10:18:43.208), -&lt; (10:18:44.230), -/ (10:18:44.552), -div (10:18:45.086), -&gt; (10:18:45.251), +Sorting (00:00:00), +Visualizer (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +h1 (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
+        <t>-&lt; (10:12:43.632), -title (10:12:44.512), -&gt; (10:12:44.622), -&lt; (10:12:47.904), -/ (10:12:48.260), -title (10:12:49.434), -&gt; (10:12:49.841), -Sorting (10:13:13.802) ~1.00, -Visualizer (10:13:16.993) ~1.00, -&lt; (10:13:17.335) ~1.00, -/ (10:13:17.789) ~1.00, -h1 (10:13:18.123) ~1.00, -&gt; (10:13:18.254) ~1.00, -&lt; (10:18:29.900) ~1.00, -div (10:18:30.558) ~1.00, -id (10:18:31.498) ~1.00, -= (10:18:31.631) ~1.00, -" (10:18:33.349) ~1.00, -vis (10:18:34.420) ~1.00, -- (10:18:37.062) ~1.00, -123456 (10:18:40.665) ~1.00, -" (10:18:40.947) ~1.00, -&gt; (10:18:43.208) ~1.00, -&lt; (10:18:44.230) ~1.00, -/ (10:18:44.552) ~1.00, -div (10:18:45.086) ~1.00, -&gt; (10:18:45.251) ~1.00, +Sorting (00:00:00), +Visualizer (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +h1 (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O56" authorId="0" shapeId="0">
       <text>
-        <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:17:21.139), -# (10:19:53.296), -vis (10:19:54.003), -- (10:19:54.226), -123456 (10:19:55.544), -{ (10:20:02.452), -height (10:20:07.891), -: (10:20:07.983), -200px (10:20:09.051), -; (10:20:09.451), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), -. (10:43:24.242), -bar (10:43:31.288), -{ (10:43:32.996), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +{ (00:00:00), +height (00:00:00), +: (00:00:00), +200px (00:00:00), +; (00:00:00), +. (00:00:00), +bar (00:00:00), +{ (00:00:00)</t>
+        <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:17:21.139) ~1.00, -# (10:19:53.296) ~1.00, -vis (10:19:54.003) ~1.00, -- (10:19:54.226) ~1.00, -123456 (10:19:55.544) ~1.00, -{ (10:20:02.452) ~1.00, -height (10:20:07.891) ~1.00, -: (10:20:07.983) ~1.00, -200px (10:20:09.051) ~1.00, -; (10:20:09.451) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, -. (10:43:24.242) ~1.00, -bar (10:43:31.288) ~1.00, -{ (10:43:32.996) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +{ (00:00:00), +height (00:00:00), +: (00:00:00), +200px (00:00:00), +; (00:00:00), +. (00:00:00), +bar (00:00:00), +{ (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q56" authorId="0" shapeId="0">
       <text>
-        <t>-; (10:50:48.660), -100 (11:14:24.924), +10 (00:00:00)</t>
+        <t>-; (10:50:48.660), -100 (11:14:24.924) ~0.67, +10 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E59" authorId="0" shapeId="0">
@@ -637,17 +637,17 @@
     </comment>
     <comment ref="O59" authorId="0" shapeId="0">
       <text>
-        <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:17:21.139), -# (10:19:53.296), -vis (10:19:54.003), -- (10:19:54.226), -123456 (10:19:55.544), -{ (10:20:02.452), -height (10:20:07.891), -: (10:20:07.983), -200px (10:20:09.051), -; (10:20:09.451), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), -align (10:57:30.272), -- (10:57:30.282), -items (10:57:30.332), -: (10:57:30.342), -flex (10:57:30.392), -- (10:57:30.402), -end (10:57:30.432), -; (10:57:30.442), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +{ (00:00:00), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +flex (00:00:00), +- (00:00:00), +end (00:00:00), +; (00:00:00), +height (00:00:00), +: (00:00:00), +200px (00:00:00), +; (00:00:00)</t>
+        <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:17:21.139) ~1.00, -# (10:19:53.296) ~1.00, -vis (10:19:54.003) ~1.00, -- (10:19:54.226) ~1.00, -123456 (10:19:55.544) ~1.00, -{ (10:20:02.452) ~1.00, -height (10:20:07.891) ~1.00, -: (10:20:07.983) ~1.00, -200px (10:20:09.051) ~0.20, -; (10:20:09.451), -align (10:24:12.446) ~1.00, -- (10:24:12.596) ~1.00, -items (10:24:13.500), -align (10:57:30.272) ~1.00, -- (10:57:30.282) ~1.00, -items (10:57:30.332) ~1.00, -: (10:57:30.342) ~1.00, -flex (10:57:30.392), -- (10:57:30.402) ~0.00, -end (10:57:30.432) ~1.00, -; (10:57:30.442) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +{ (00:00:00), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +flex (00:00:00), +- (00:00:00), +end (00:00:00), +; (00:00:00), +height (00:00:00), +: (00:00:00), +200px (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q59" authorId="0" shapeId="0">
       <text>
-        <t>-length (10:38:57.372), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -getElementsByClassName (11:09:28.891), -; (11:14:32.118), +lenght (00:00:00), +getElementsByClassname (00:00:00)</t>
+        <t>-length (10:38:57.372) ~0.67, +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -getElementsByClassName (11:09:28.891) ~0.95, -; (11:14:32.118), +lenght (00:00:00), +getElementsByClassname (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D62" authorId="0" shapeId="0">
       <text>
-        <t>Short name part(s) not auto-redacted (verify manually): De</t>
+        <t>Short name part(s) not auto-redacted</t>
       </text>
     </comment>
     <comment ref="E62" authorId="0" shapeId="0">
@@ -667,7 +667,7 @@
     </comment>
     <comment ref="O62" authorId="0" shapeId="0">
       <text>
-        <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:17:21.139), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+        <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:17:21.139) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E66" authorId="0" shapeId="0">
@@ -687,12 +687,12 @@
     </comment>
     <comment ref="O66" authorId="0" shapeId="0">
       <text>
-        <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:17:21.139), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), -7px (10:43:39.527), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +700px (00:00:00)</t>
+        <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:17:21.139) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, -7px (10:43:39.527) ~0.60, +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +700px (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q66" authorId="0" shapeId="0">
       <text>
-        <t>-for (10:30:13.868), -( (10:30:14.352), -let (10:30:15.164), -i (10:30:15.672), -= (10:30:16.329), -0 (10:30:16.771), -; (10:30:17.011), -i (10:30:17.443), -&lt; (10:30:18.073), -count (10:30:20.284), -; (10:30:20.584), -i (10:30:47.713), -+ (10:30:48.171), -+ (10:30:48.660), -) (10:30:49.210), -{ (10:31:12.723), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +count (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00)</t>
+        <t>-for (10:30:13.868) ~1.00, -( (10:30:14.352) ~1.00, -let (10:30:15.164) ~1.00, -i (10:30:15.672) ~1.00, -= (10:30:16.329) ~1.00, -0 (10:30:16.771) ~1.00, -; (10:30:17.011) ~1.00, -i (10:30:17.443) ~1.00, -&lt; (10:30:18.073) ~1.00, -count (10:30:20.284) ~1.00, -; (10:30:20.584) ~1.00, -i (10:30:47.713) ~1.00, -+ (10:30:48.171) ~1.00, -+ (10:30:48.660) ~1.00, -) (10:30:49.210) ~1.00, -{ (10:31:12.723) ~1.00, -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +count (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E68" authorId="0" shapeId="0">
@@ -712,12 +712,12 @@
     </comment>
     <comment ref="O68" authorId="0" shapeId="0">
       <text>
-        <t>-# (10:19:53.296), -vis (10:19:54.003), -- (10:19:54.226), -123456 (10:19:55.544), -height (10:20:07.891), -200px (10:20:09.051), -. (10:43:24.242), -bar (10:43:31.288), -{ (10:43:32.996), -} (10:43:33.966), -width (10:43:37.644), -: (10:43:37.716), -7px (10:43:39.527), -; (10:43:40.239), -height (10:43:47.504), -: (10:43:47.683), -100 (10:43:48.485), -% (10:43:48.586), -; (10:43:48.809), -background (10:44:24.231), -- (10:44:24.311), -color (10:44:25.031), -: (10:44:25.154), -black (10:44:26.271), -; (10:44:26.592), -display (10:47:38.305), -flex (10:47:39.551), -margin (10:48:02.482), -: (10:48:02.549), -0px (10:48:03.827), -1px (10:48:07.241), -; (10:48:07.569), +:* (10:50:08.734), +;* (10:50:09.333), -align (10:57:30.272), -items (10:57:30.332), -flex (10:57:30.392), -- (10:57:30.402), -end (10:57:30.432), +} (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +{ (00:00:00), +display (00:00:00), +flex (00:00:00), +; (00:00:00), +height (00:00:00), +: (00:00:00), +200px (00:00:00), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +flex (00:00:00), +- (00:00:00), +end (00:00:00), +; (00:00:00), +background (00:00:00), +: (00:00:00), +red (00:00:00), +; (00:00:00), +. (00:00:00), +bar (00:00:00), +width (00:00:00), +7px (00:00:00), +height (00:00:00), +100 (00:00:00), +% (00:00:00), +background (00:00:00), +color (00:00:00), +black (00:00:00), +margin (00:00:00), +: (00:00:00), +0 (00:00:00), +1px (00:00:00), +; (00:00:00)</t>
+        <t>-# (10:19:53.296) ~1.00, -vis (10:19:54.003) ~1.00, -- (10:19:54.226) ~1.00, -123456 (10:19:55.544) ~1.00, -height (10:20:07.891) ~1.00, -200px (10:20:09.051) ~1.00, -. (10:43:24.242) ~1.00, -bar (10:43:31.288) ~1.00, -{ (10:43:32.996) ~1.00, -} (10:43:33.966), -width (10:43:37.644) ~1.00, -: (10:43:37.716), -7px (10:43:39.527) ~1.00, -; (10:43:40.239), -height (10:43:47.504) ~1.00, -: (10:43:47.683), -100 (10:43:48.485) ~1.00, -% (10:43:48.586) ~1.00, -; (10:43:48.809), -background (10:44:24.231) ~1.00, -- (10:44:24.311) ~1.00, -color (10:44:25.031) ~1.00, -: (10:44:25.154), -black (10:44:26.271) ~1.00, -; (10:44:26.592), -display (10:47:38.305) ~1.00, -flex (10:47:39.551) ~1.00, -margin (10:48:02.482) ~1.00, -: (10:48:02.549) ~1.00, -0px (10:48:03.827) ~0.33, -1px (10:48:07.241) ~1.00, -; (10:48:07.569) ~1.00, +:* (10:50:08.734), +;* (10:50:09.333), -align (10:57:30.272) ~1.00, -items (10:57:30.332) ~1.00, -flex (10:57:30.392) ~1.00, -- (10:57:30.402) ~1.00, -end (10:57:30.432) ~0.33, +} (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +{ (00:00:00), +display (00:00:00), +flex (00:00:00), +; (00:00:00), +height (00:00:00), +: (00:00:00), +200px (00:00:00), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +flex (00:00:00), +- (00:00:00), +end (00:00:00), +; (00:00:00), +background (00:00:00), +: (00:00:00), +red (00:00:00), +; (00:00:00), +. (00:00:00), +bar (00:00:00), +width (00:00:00), +7px (00:00:00), +height (00:00:00), +100 (00:00:00), +% (00:00:00), +background (00:00:00), +color (00:00:00), +black (00:00:00), +margin (00:00:00), +: (00:00:00), +0 (00:00:00), +1px (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q68" authorId="0" shapeId="0">
       <text>
-        <t>-function (10:57:37.492), -bubbleSort (10:57:42.836), -( (10:57:43.053), -arr (10:57:49.140), -) (10:57:49.861), -{ (10:57:54.715), -do (10:58:33.576), -{ (10:58:34.903), -var (10:59:12.196), -swapped (10:59:20.551), -= (10:59:21.101), -false (10:59:23.105), -; (10:59:24.221), -for (10:59:26.374), -( (10:59:26.727), -let (10:59:27.295), -i (10:59:27.677), -= (10:59:27.952), -1 (10:59:28.458), -; (10:59:28.738), -i (10:59:29.253), -&lt; (10:59:29.652), -arr (10:59:30.525), -. (10:59:30.766), -length (10:59:32.061), -; (10:59:32.305), -i (10:59:32.661), -+ (10:59:32.869), -+ (10:59:33.126), -) (10:59:33.350), -{ (10:59:35.506), -if (10:59:41.288), -( (10:59:41.708), -arr (10:59:42.652), -[ (10:59:42.917), -i (10:59:43.246), -- (10:59:44.058), -1 (10:59:44.656), -] (10:59:44.854), -&gt; (10:59:45.546), -arr (10:59:46.616), -[ (10:59:46.969), -i (10:59:47.212), -] (10:59:47.751), -) (10:59:48.230), -{ (10:59:49.302), -const (11:00:57.203), -aux (11:00:58.458), -= (11:01:01.660), -arr (11:01:02.684), -[ (11:01:02.941), -i (11:01:03.128), -- (11:01:03.607), -1 (11:01:04.198), -] (11:01:04.697), -; (11:01:05.017), -arr (11:01:06.389), -[ (11:01:06.650), -i (11:01:06.835), -- (11:01:07.252), -1 (11:01:07.757), -] (11:01:08.184), -= (11:01:08.961), -arr (11:01:09.861), -[ (11:01:10.052), -i (11:01:10.368), -] (11:01:10.513), -; (11:01:10.683), -arr (11:01:12.501), -[ (11:01:12.714), -i (11:01:12.894), -] (11:01:13.102), -= (11:01:13.537), -aux (11:01:14.449), -; (11:01:14.856), -swapped (11:02:15.877), -= (11:02:16.203), -true (11:02:17.158), -; (11:02:17.463), -bubbleSort (11:08:34.118), -array (11:08:34.178), -function (11:08:36.630), -updateBars (11:08:38.342), -( (11:08:38.511), -) (11:08:38.687), -{ (11:08:39.319), -const (11:09:21.850), -bars (11:09:22.876), -= (11:09:23.405), -document (11:09:24.920), -. (11:09:25.072), -getElementsByClassName (11:09:28.891), -( (11:09:28.949), -" (11:09:29.056), -bar (11:09:29.764), -" (11:09:29.897), -) (11:09:29.998), -; (11:09:30.476), -for (11:09:55.616), -( (11:09:55.956), -let (11:09:56.455), -i (11:09:56.677), -= (11:09:57.008), -0 (11:09:57.490), -; (11:09:57.512), -i (11:09:57.854), -&lt; (11:09:58.223), -bars (11:09:58.993), -. (11:09:59.214), -length (11:10:00.426), -; (11:10:00.634), -i (11:10:01.376), -+ (11:10:01.600), -+ (11:10:01.789), -) (11:10:01.880), -{ (11:10:02.609), -bars (11:10:05.954), -[ (11:10:06.083), -i (11:10:06.207), -] (11:10:06.517), -. (11:10:06.753), -style (11:10:08.322), -. (11:10:08.474), -height (11:10:09.606), -= (11:10:12.868), -array (11:10:13.726), -[ (11:10:13.999), -i (11:10:14.138), -] (11:10:14.279), -* (11:10:14.846), -100 (11:10:15.517), -+ (11:10:16.137), -" (11:10:16.502), -% (11:10:16.625), -" (11:10:16.705), -; (11:10:17.104), -updateBars (11:12:30.664), -; (11:12:31.204), -await (11:13:47.348), -new (11:13:53.570), -Promise (11:13:54.982), -( (11:13:55.301), -resolve (11:13:59.055), -= (11:14:16.118), -&gt; (11:14:16.408), -setTimeout (11:14:18.857), -( (11:14:19.066), -resolve (11:14:23.324), -, (11:14:23.491), -100 (11:14:24.924), -) (11:14:31.103), -) (11:14:31.475), -; (11:14:32.118), -async (11:15:16.100), +function (00:00:00), +updataBars (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bars (00:00:00), += (00:00:00), +visualizer (00:00:00), +. (00:00:00), +querySelectorAll (00:00:00), +" (00:00:00), +. (00:00:00), +bar (00:00:00), +" (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +array (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +height (00:00:00), += (00:00:00), +array (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +* (00:00:00), +100 (00:00:00), ++ (00:00:00), +" (00:00:00), +% (00:00:00), +" (00:00:00), +; (00:00:00), +async (00:00:00), +function (00:00:00), +bubblesort (00:00:00), +arr (00:00:00), +{ (00:00:00), +do (00:00:00), +{ (00:00:00), +var (00:00:00), +swapped (00:00:00), += (00:00:00), +false (00:00:00), +; (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +arr (00:00:00), +. (00:00:00), +length (00:00:00), +- (00:00:00), +1 (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +if (00:00:00), +( (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +&gt; (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), ++ (00:00:00), +1 (00:00:00), +] (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +aux (00:00:00), += (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +- (00:00:00), +1 (00:00:00), +] (00:00:00), +; (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), += (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), ++ (00:00:00), +1 (00:00:00), +] (00:00:00), +; (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), ++ (00:00:00), +1 (00:00:00), +] (00:00:00), += (00:00:00), +aux (00:00:00), +; (00:00:00), +swapped (00:00:00), += (00:00:00), +true (00:00:00), +; (00:00:00), +updataBars (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +await (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +10 (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00)</t>
+        <t>-function (10:57:37.492) ~1.00, -bubbleSort (10:57:42.836) ~0.90, -( (10:57:43.053), -arr (10:57:49.140) ~1.00, -) (10:57:49.861), -{ (10:57:54.715) ~1.00, -do (10:58:33.576) ~1.00, -{ (10:58:34.903) ~1.00, -var (10:59:12.196) ~1.00, -swapped (10:59:20.551) ~1.00, -= (10:59:21.101) ~1.00, -false (10:59:23.105) ~1.00, -; (10:59:24.221) ~1.00, -for (10:59:26.374) ~1.00, -( (10:59:26.727) ~1.00, -let (10:59:27.295) ~1.00, -i (10:59:27.677) ~1.00, -= (10:59:27.952) ~1.00, -1 (10:59:28.458) ~0.00, -; (10:59:28.738) ~1.00, -i (10:59:29.253) ~1.00, -&lt; (10:59:29.652) ~1.00, -arr (10:59:30.525) ~1.00, -. (10:59:30.766) ~1.00, -length (10:59:32.061) ~1.00, -; (10:59:32.305) ~1.00, -i (10:59:32.661) ~1.00, -+ (10:59:32.869) ~1.00, -+ (10:59:33.126) ~1.00, -) (10:59:33.350) ~1.00, -{ (10:59:35.506) ~1.00, -if (10:59:41.288) ~1.00, -( (10:59:41.708) ~1.00, -arr (10:59:42.652) ~1.00, -[ (10:59:42.917) ~1.00, -i (10:59:43.246) ~1.00, -- (10:59:44.058), -1 (10:59:44.656) ~1.00, -] (10:59:44.854) ~1.00, -&gt; (10:59:45.546) ~1.00, -arr (10:59:46.616) ~1.00, -[ (10:59:46.969) ~1.00, -i (10:59:47.212) ~1.00, -] (10:59:47.751) ~1.00, -) (10:59:48.230) ~1.00, -{ (10:59:49.302) ~1.00, -const (11:00:57.203) ~1.00, -aux (11:00:58.458) ~1.00, -= (11:01:01.660) ~1.00, -arr (11:01:02.684) ~1.00, -[ (11:01:02.941) ~1.00, -i (11:01:03.128) ~1.00, -- (11:01:03.607) ~1.00, -1 (11:01:04.198) ~1.00, -] (11:01:04.697) ~1.00, -; (11:01:05.017) ~1.00, -arr (11:01:06.389) ~1.00, -[ (11:01:06.650) ~1.00, -i (11:01:06.835) ~1.00, -- (11:01:07.252) ~0.00, -1 (11:01:07.757) ~1.00, -] (11:01:08.184) ~1.00, -= (11:01:08.961) ~1.00, -arr (11:01:09.861) ~1.00, -[ (11:01:10.052) ~1.00, -i (11:01:10.368) ~1.00, -] (11:01:10.513) ~1.00, -; (11:01:10.683) ~1.00, -arr (11:01:12.501) ~1.00, -[ (11:01:12.714) ~1.00, -i (11:01:12.894) ~1.00, -] (11:01:13.102) ~1.00, -= (11:01:13.537) ~1.00, -aux (11:01:14.449) ~1.00, -; (11:01:14.856) ~1.00, -swapped (11:02:15.877) ~1.00, -= (11:02:16.203) ~1.00, -true (11:02:17.158) ~1.00, -; (11:02:17.463) ~1.00, -bubbleSort (11:08:34.118) ~0.20, -array (11:08:34.178), -function (11:08:36.630), -updateBars (11:08:38.342) ~0.90, -( (11:08:38.511) ~1.00, -) (11:08:38.687) ~1.00, -{ (11:08:39.319) ~1.00, -const (11:09:21.850) ~1.00, -bars (11:09:22.876) ~1.00, -= (11:09:23.405) ~1.00, -document (11:09:24.920) ~0.10, -. (11:09:25.072) ~1.00, -getElementsByClassName (11:09:28.891) ~0.18, -( (11:09:28.949) ~0.00, -" (11:09:29.056) ~1.00, -bar (11:09:29.764) ~1.00, -" (11:09:29.897) ~1.00, -) (11:09:29.998), -; (11:09:30.476), -for (11:09:55.616) ~1.00, -( (11:09:55.956) ~1.00, -let (11:09:56.455) ~1.00, -i (11:09:56.677) ~1.00, -= (11:09:57.008) ~1.00, -0 (11:09:57.490) ~1.00, -; (11:09:57.512) ~1.00, -i (11:09:57.854) ~1.00, -&lt; (11:09:58.223) ~1.00, -bars (11:09:58.993) ~0.20, -. (11:09:59.214) ~1.00, -length (11:10:00.426) ~1.00, -; (11:10:00.634) ~1.00, -i (11:10:01.376) ~1.00, -+ (11:10:01.600) ~1.00, -+ (11:10:01.789) ~1.00, -) (11:10:01.880) ~1.00, -{ (11:10:02.609) ~1.00, -bars (11:10:05.954) ~1.00, -[ (11:10:06.083) ~1.00, -i (11:10:06.207) ~1.00, -] (11:10:06.517) ~1.00, -. (11:10:06.753) ~1.00, -style (11:10:08.322) ~1.00, -. (11:10:08.474) ~1.00, -height (11:10:09.606) ~1.00, -= (11:10:12.868) ~1.00, -array (11:10:13.726) ~1.00, -[ (11:10:13.999) ~1.00, -i (11:10:14.138) ~1.00, -] (11:10:14.279) ~1.00, -* (11:10:14.846) ~1.00, -100 (11:10:15.517) ~1.00, -+ (11:10:16.137) ~1.00, -" (11:10:16.502) ~1.00, -% (11:10:16.625) ~1.00, -" (11:10:16.705) ~1.00, -; (11:10:17.104) ~1.00, -updateBars (11:12:30.664) ~0.90, -; (11:12:31.204) ~1.00, -await (11:13:47.348) ~1.00, -new (11:13:53.570) ~1.00, -Promise (11:13:54.982) ~1.00, -( (11:13:55.301) ~1.00, -resolve (11:13:59.055) ~1.00, -= (11:14:16.118) ~1.00, -&gt; (11:14:16.408) ~1.00, -setTimeout (11:14:18.857) ~1.00, -( (11:14:19.066) ~1.00, -resolve (11:14:23.324) ~1.00, -, (11:14:23.491) ~1.00, -100 (11:14:24.924) ~0.67, -) (11:14:31.103) ~1.00, -) (11:14:31.475) ~1.00, -; (11:14:32.118) ~1.00, -async (11:15:16.100) ~1.00, +function (00:00:00), +updataBars (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bars (00:00:00), += (00:00:00), +visualizer (00:00:00), +. (00:00:00), +querySelectorAll (00:00:00), +" (00:00:00), +. (00:00:00), +bar (00:00:00), +" (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +array (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +height (00:00:00), += (00:00:00), +array (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +* (00:00:00), +100 (00:00:00), ++ (00:00:00), +" (00:00:00), +% (00:00:00), +" (00:00:00), +; (00:00:00), +async (00:00:00), +function (00:00:00), +bubblesort (00:00:00), +arr (00:00:00), +{ (00:00:00), +do (00:00:00), +{ (00:00:00), +var (00:00:00), +swapped (00:00:00), += (00:00:00), +false (00:00:00), +; (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +arr (00:00:00), +. (00:00:00), +length (00:00:00), +- (00:00:00), +1 (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +if (00:00:00), +( (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +&gt; (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), ++ (00:00:00), +1 (00:00:00), +] (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +aux (00:00:00), += (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +- (00:00:00), +1 (00:00:00), +] (00:00:00), +; (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), += (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), ++ (00:00:00), +1 (00:00:00), +] (00:00:00), +; (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), ++ (00:00:00), +1 (00:00:00), +] (00:00:00), += (00:00:00), +aux (00:00:00), +; (00:00:00), +swapped (00:00:00), += (00:00:00), +true (00:00:00), +; (00:00:00), +updataBars (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +await (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +10 (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E70" authorId="0" shapeId="0">
@@ -737,17 +737,17 @@
     </comment>
     <comment ref="M70" authorId="0" shapeId="0">
       <text>
-        <t>-DOCTYPE (10:12:14.338), -Visualizer (10:12:47.677), -Sorting (10:13:13.802), -Visualizer (10:13:16.993), -&lt; (10:27:15.917), +Doctype (00:00:00), +visualizer (00:00:00), +sorting (00:00:00), +visualizer (00:00:00)</t>
+        <t>-DOCTYPE (10:12:14.338) ~0.14, -Visualizer (10:12:47.677) ~0.90, -Sorting (10:13:13.802) ~0.86, -Visualizer (10:13:16.993) ~0.90, -&lt; (10:27:15.917), +Doctype (00:00:00), +visualizer (00:00:00), +sorting (00:00:00), +visualizer (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O70" authorId="0" shapeId="0">
       <text>
-        <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:17:21.139), -# (10:19:53.296), -vis (10:19:54.003), -- (10:19:54.226), -123456 (10:19:55.544), -{ (10:20:02.452), -height (10:20:07.891), -200px (10:20:09.051), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), -. (10:43:24.242), -bar (10:43:31.288), -{ (10:43:32.996), -width (10:43:37.644), -7px (10:43:39.527), -height (10:43:47.504), -100 (10:43:48.485), -% (10:43:48.586), -background (10:44:24.231), -- (10:44:24.311), -color (10:44:25.031), -black (10:44:26.271), -margin (10:48:02.482), -: (10:48:02.549), -0px (10:48:03.827), -1px (10:48:07.241), -; (10:48:07.569), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +red* (10:50:09.332), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +{ (00:00:00), +height (00:00:00), +: (00:00:00), +500px (00:00:00), +. (00:00:00), +bar (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +7px (00:00:00), +; (00:00:00), +height (00:00:00), +100 (00:00:00), +% (00:00:00), +Background (00:00:00), +- (00:00:00), +color (00:00:00), +black (00:00:00), +margin (00:00:00), +0px (00:00:00), +1px (00:00:00)</t>
+        <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:17:21.139) ~1.00, -# (10:19:53.296) ~1.00, -vis (10:19:54.003) ~1.00, -- (10:19:54.226) ~1.00, -123456 (10:19:55.544) ~1.00, -{ (10:20:02.452) ~1.00, -height (10:20:07.891) ~1.00, -200px (10:20:09.051) ~0.80, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, -. (10:43:24.242) ~1.00, -bar (10:43:31.288) ~1.00, -{ (10:43:32.996) ~1.00, -width (10:43:37.644) ~1.00, -7px (10:43:39.527) ~1.00, -height (10:43:47.504) ~1.00, -100 (10:43:48.485) ~1.00, -% (10:43:48.586) ~1.00, -background (10:44:24.231) ~0.90, -- (10:44:24.311) ~1.00, -color (10:44:25.031) ~1.00, -black (10:44:26.271) ~1.00, -margin (10:48:02.482) ~1.00, -: (10:48:02.549), -0px (10:48:03.827) ~1.00, -1px (10:48:07.241) ~1.00, -; (10:48:07.569), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +red* (10:50:09.332), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +{ (00:00:00), +height (00:00:00), +: (00:00:00), +500px (00:00:00), +. (00:00:00), +bar (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +7px (00:00:00), +; (00:00:00), +height (00:00:00), +100 (00:00:00), +% (00:00:00), +Background (00:00:00), +- (00:00:00), +color (00:00:00), +black (00:00:00), +margin (00:00:00), +0px (00:00:00), +1px (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q70" authorId="0" shapeId="0">
       <text>
-        <t>-bubbleSort (10:57:42.836), -i (10:59:29.253), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -&lt; (11:09:58.223), -bars (11:09:58.993), -i (11:10:01.376), -Promise (11:13:54.982), +&gt; (00:00:00), +bats (00:00:00), +bubblesort (00:00:00), +promise (00:00:00)</t>
+        <t>-bubbleSort (10:57:42.836) ~0.90, -i (10:59:29.253), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -&lt; (11:09:58.223) ~0.00, -bars (11:09:58.993) ~0.75, -i (11:10:01.376), -Promise (11:13:54.982) ~0.86, +&gt; (00:00:00), +bats (00:00:00), +bubblesort (00:00:00), +promise (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E71" authorId="0" shapeId="0">
@@ -762,7 +762,7 @@
     </comment>
     <comment ref="O71" authorId="0" shapeId="0">
       <text>
-        <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:17:21.139), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+        <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:17:21.139) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q71" authorId="0" shapeId="0">
@@ -787,17 +787,17 @@
     </comment>
     <comment ref="M72" authorId="0" shapeId="0">
       <text>
-        <t>-title (10:12:49.434), -Visualizer (10:13:16.993), -123456 (10:18:40.665), +tittle (00:00:00), +visualizer (00:00:00), +654321 (00:00:00)</t>
+        <t>-title (10:12:49.434) ~0.83, -Visualizer (10:13:16.993) ~0.90, -123456 (10:18:40.665) ~0.00, +tittle (00:00:00), +visualizer (00:00:00), +654321 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O72" authorId="0" shapeId="0">
       <text>
-        <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:17:21.139), -# (10:19:53.296), -vis (10:19:54.003), -- (10:19:54.226), -123456 (10:19:55.544), -{ (10:20:02.452), -height (10:20:07.891), -: (10:20:07.983), -200px (10:20:09.051), -; (10:20:09.451), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), -display (10:47:38.305), -: (10:47:38.437), -flex (10:47:39.551), -; (10:47:39.811), -margin (10:48:02.482), -: (10:48:02.549), -0px (10:48:03.827), -1px (10:48:07.241), -; (10:48:07.569), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), -align (10:57:30.272), -- (10:57:30.282), -items (10:57:30.332), -: (10:57:30.342), -flex (10:57:30.392), -- (10:57:30.402), -end (10:57:30.432), -; (10:57:30.442), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +654321 (00:00:00), +{ (00:00:00), +height (00:00:00), +: (00:00:00), +200px (00:00:00), +; (00:00:00)</t>
+        <t>-: (10:17:19.374), -center (10:17:20.707) ~1.00, -; (10:17:21.139) ~1.00, -# (10:19:53.296) ~1.00, -vis (10:19:54.003) ~1.00, -- (10:19:54.226) ~1.00, -123456 (10:19:55.544) ~0.00, -{ (10:20:02.452) ~1.00, -height (10:20:07.891) ~1.00, -: (10:20:07.983), -200px (10:20:09.051), -; (10:20:09.451), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), -display (10:47:38.305), -: (10:47:38.437) ~1.00, -flex (10:47:39.551), -; (10:47:39.811) ~1.00, -margin (10:48:02.482), -: (10:48:02.549), -0px (10:48:03.827), -1px (10:48:07.241), -; (10:48:07.569), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), -align (10:57:30.272) ~1.00, -- (10:57:30.282) ~1.00, -items (10:57:30.332) ~1.00, -: (10:57:30.342) ~1.00, -flex (10:57:30.392), -- (10:57:30.402), -end (10:57:30.432), -; (10:57:30.442), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +654321 (00:00:00), +{ (00:00:00), +height (00:00:00), +: (00:00:00), +200px (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q72" authorId="0" shapeId="0">
       <text>
-        <t>-array (10:28:45.898), -const (10:37:42.386), -visualizer (10:37:44.631), -= (10:37:45.082), -document (10:37:47.323), -. (10:37:47.760), -getElementById (10:38:03.158), -" (10:38:19.019), -vis (10:38:19.926), -- (10:38:20.217), -123456 (10:38:22.251), -" (10:38:22.629), +bubbleSort* (11:08:31.581), -array (11:08:34.178), -getElementsByClassName (11:09:28.891), +arry (00:00:00), +arry (00:00:00), +const (00:00:00), +visualizer (00:00:00), += (00:00:00), +documnet (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +654321 (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +arry (00:00:00), +getElementByClassName (00:00:00)</t>
+        <t>-array (10:28:45.898) ~0.80, -const (10:37:42.386) ~1.00, -visualizer (10:37:44.631) ~1.00, -= (10:37:45.082) ~1.00, -document (10:37:47.323) ~0.75, -. (10:37:47.760) ~1.00, -getElementById (10:38:03.158) ~1.00, -" (10:38:19.019) ~1.00, -vis (10:38:19.926) ~1.00, -- (10:38:20.217) ~1.00, -123456 (10:38:22.251) ~0.00, -" (10:38:22.629) ~1.00, +bubbleSort* (11:08:31.581), -array (11:08:34.178) ~0.80, -getElementsByClassName (11:09:28.891) ~0.95, +arry (00:00:00), +arry (00:00:00), +const (00:00:00), +visualizer (00:00:00), += (00:00:00), +documnet (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +654321 (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +arry (00:00:00), +getElementByClassName (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E73" authorId="0" shapeId="0">
@@ -817,7 +817,7 @@
     </comment>
     <comment ref="O73" authorId="0" shapeId="0">
       <text>
-        <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:17:21.139), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+        <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:17:21.139) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E75" authorId="0" shapeId="0">
@@ -832,12 +832,12 @@
     </comment>
     <comment ref="O75" authorId="0" shapeId="0">
       <text>
-        <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:17:21.139), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), -align (10:57:30.272), -- (10:57:30.282), -items (10:57:30.332), -: (10:57:30.342), -flex (10:57:30.392), -- (10:57:30.402), -end (10:57:30.432), -; (10:57:30.442), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+        <t>-: (10:17:19.374), -center (10:17:20.707) ~1.00, -; (10:17:21.139) ~1.00, -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), -align (10:57:30.272) ~1.00, -- (10:57:30.282) ~1.00, -items (10:57:30.332) ~1.00, -: (10:57:30.342) ~1.00, -flex (10:57:30.392), -- (10:57:30.402), -end (10:57:30.432), -; (10:57:30.442), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q75" authorId="0" shapeId="0">
       <text>
-        <t>-createElement (10:39:45.021), -visualizer (10:40:27.992), -. (10:40:28.151), -appendChild (10:40:30.229), -( (10:40:30.435), -bar (10:40:31.317), -) (10:40:31.505), -; (10:40:32.101), -bubbleSort (10:57:42.836), -} (10:59:37.396), -&gt; (10:59:45.546), -arr (10:59:46.616), -[ (10:59:46.969), -i (10:59:47.212), -] (10:59:47.751), -- (11:01:03.607), -1 (11:01:04.198), -arr (11:01:06.389), -[ (11:01:06.650), -i (11:01:06.835), -- (11:01:07.252), -1 (11:01:07.757), -] (11:01:08.184), -= (11:01:08.961), -arr (11:01:09.861), -[ (11:01:10.052), -i (11:01:10.368), -] (11:01:10.513), -; (11:01:10.683), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -function (11:08:36.630), -updateBars (11:08:38.342), -( (11:08:38.511), -) (11:08:38.687), -{ (11:08:39.319), -const (11:09:21.850), -bars (11:09:22.876), -= (11:09:23.405), -document (11:09:24.920), -. (11:09:25.072), -getElementsByClassName (11:09:28.891), -( (11:09:28.949), -" (11:09:29.056), -bar (11:09:29.764), -" (11:09:29.897), -) (11:09:29.998), -; (11:09:30.476), -for (11:09:55.616), -( (11:09:55.956), -let (11:09:56.455), -i (11:09:56.677), -= (11:09:57.008), -0 (11:09:57.490), -; (11:09:57.512), -i (11:09:57.854), -&lt; (11:09:58.223), -bars (11:09:58.993), -. (11:09:59.214), -length (11:10:00.426), -; (11:10:00.634), -i (11:10:01.376), -+ (11:10:01.600), -+ (11:10:01.789), -) (11:10:01.880), -{ (11:10:02.609), -} (11:10:03.305), -bars (11:10:05.954), -[ (11:10:06.083), -i (11:10:06.207), -] (11:10:06.517), -. (11:10:06.753), -style (11:10:08.322), -. (11:10:08.474), -height (11:10:09.606), -= (11:10:12.868), -array (11:10:13.726), -[ (11:10:13.999), -i (11:10:14.138), -] (11:10:14.279), -* (11:10:14.846), -100 (11:10:15.517), -+ (11:10:16.137), -" (11:10:16.502), -% (11:10:16.625), -" (11:10:16.705), -; (11:10:17.104), -updateBars (11:12:30.664), -( (11:12:30.752), -) (11:12:30.906), -; (11:12:31.204), -await (11:13:47.348), -new (11:13:53.570), -Promise (11:13:54.982), -( (11:13:55.301), -resolve (11:13:59.055), -= (11:14:16.118), -&gt; (11:14:16.408), -setTimeout (11:14:18.857), -( (11:14:19.066), -resolve (11:14:23.324), -, (11:14:23.491), -100 (11:14:24.924), -) (11:14:31.103), -) (11:14:31.475), -; (11:14:32.118), +createrElement (00:00:00), +function (00:00:00), +updatebars (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bars (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +get (00:00:00), +ElementsByClassName (00:00:00), +( (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +&lt; (00:00:00), +array (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +height (00:00:00), += (00:00:00), +array (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +* (00:00:00), +100 (00:00:00), ++ (00:00:00), +" (00:00:00), +% (00:00:00), +" (00:00:00), +; (00:00:00), +bubblesort (00:00:00), +updateBars (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +await (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeOut (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +100 (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        <t>-createElement (10:39:45.021) ~0.93, -visualizer (10:40:27.992), -. (10:40:28.151), -appendChild (10:40:30.229), -( (10:40:30.435), -bar (10:40:31.317), -) (10:40:31.505), -; (10:40:32.101), -bubbleSort (10:57:42.836) ~0.90, -} (10:59:37.396) ~1.00, -&gt; (10:59:45.546), -arr (10:59:46.616), -[ (10:59:46.969), -i (10:59:47.212), -] (10:59:47.751), -- (11:01:03.607), -1 (11:01:04.198), -arr (11:01:06.389), -[ (11:01:06.650), -i (11:01:06.835), -- (11:01:07.252), -1 (11:01:07.757), -] (11:01:08.184), -= (11:01:08.961), -arr (11:01:09.861), -[ (11:01:10.052), -i (11:01:10.368), -] (11:01:10.513), -; (11:01:10.683), -bubbleSort (11:08:34.118), -( (11:08:34.128) ~1.00, -array (11:08:34.178), -) (11:08:34.188) ~1.00, -; (11:08:34.198), -function (11:08:36.630) ~1.00, -updateBars (11:08:38.342) ~0.90, -( (11:08:38.511), -) (11:08:38.687), -{ (11:08:39.319) ~1.00, -const (11:09:21.850) ~1.00, -bars (11:09:22.876) ~1.00, -= (11:09:23.405) ~1.00, -document (11:09:24.920) ~1.00, -. (11:09:25.072) ~1.00, -getElementsByClassName (11:09:28.891) ~0.86, -( (11:09:28.949) ~1.00, -" (11:09:29.056) ~1.00, -bar (11:09:29.764) ~1.00, -" (11:09:29.897) ~1.00, -) (11:09:29.998) ~1.00, -; (11:09:30.476) ~1.00, -for (11:09:55.616) ~1.00, -( (11:09:55.956) ~1.00, -let (11:09:56.455) ~1.00, -i (11:09:56.677) ~1.00, -= (11:09:57.008) ~1.00, -0 (11:09:57.490) ~1.00, -; (11:09:57.512), -i (11:09:57.854), -&lt; (11:09:58.223) ~1.00, -bars (11:09:58.993) ~0.20, -. (11:09:59.214) ~1.00, -length (11:10:00.426) ~1.00, -; (11:10:00.634) ~1.00, -i (11:10:01.376) ~1.00, -+ (11:10:01.600) ~1.00, -+ (11:10:01.789) ~1.00, -) (11:10:01.880) ~1.00, -{ (11:10:02.609) ~1.00, -} (11:10:03.305), -bars (11:10:05.954) ~1.00, -[ (11:10:06.083) ~1.00, -i (11:10:06.207) ~1.00, -] (11:10:06.517) ~1.00, -. (11:10:06.753) ~1.00, -style (11:10:08.322) ~1.00, -. (11:10:08.474) ~1.00, -height (11:10:09.606) ~1.00, -= (11:10:12.868) ~1.00, -array (11:10:13.726) ~1.00, -[ (11:10:13.999) ~1.00, -i (11:10:14.138) ~1.00, -] (11:10:14.279) ~1.00, -* (11:10:14.846) ~1.00, -100 (11:10:15.517) ~1.00, -+ (11:10:16.137) ~1.00, -" (11:10:16.502) ~1.00, -% (11:10:16.625) ~1.00, -" (11:10:16.705) ~1.00, -; (11:10:17.104) ~1.00, -updateBars (11:12:30.664) ~1.00, -( (11:12:30.752) ~1.00, -) (11:12:30.906) ~1.00, -; (11:12:31.204) ~1.00, -await (11:13:47.348) ~1.00, -new (11:13:53.570) ~1.00, -Promise (11:13:54.982) ~1.00, -( (11:13:55.301) ~1.00, -resolve (11:13:59.055) ~1.00, -= (11:14:16.118) ~1.00, -&gt; (11:14:16.408) ~1.00, -setTimeout (11:14:18.857) ~0.90, -( (11:14:19.066) ~1.00, -resolve (11:14:23.324) ~1.00, -, (11:14:23.491) ~1.00, -100 (11:14:24.924) ~1.00, -) (11:14:31.103) ~1.00, -) (11:14:31.475) ~1.00, -; (11:14:32.118) ~1.00, +createrElement (00:00:00), +function (00:00:00), +updatebars (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bars (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +get (00:00:00), +ElementsByClassName (00:00:00), +( (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +&lt; (00:00:00), +array (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +height (00:00:00), += (00:00:00), +array (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +* (00:00:00), +100 (00:00:00), ++ (00:00:00), +" (00:00:00), +% (00:00:00), +" (00:00:00), +; (00:00:00), +bubblesort (00:00:00), +updateBars (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +await (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeOut (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +100 (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E78" authorId="0" shapeId="0">
@@ -857,7 +857,7 @@
     </comment>
     <comment ref="O78" authorId="0" shapeId="0">
       <text>
-        <t>-center (10:17:20.707), -flex (10:21:58.800), -direction (10:22:01.758), -column (10:22:03.223), -align (10:24:12.446), -items (10:24:13.500), +align (00:00:00), +items (00:00:00), +center (00:00:00), +flex (00:00:00), +direction (00:00:00), +column (00:00:00)</t>
+        <t>-center (10:17:20.707) ~0.17, -flex (10:21:58.800) ~0.20, -direction (10:22:01.758) ~0.22, -column (10:22:03.223) ~0.17, -align (10:24:12.446) ~0.20, -items (10:24:13.500) ~0.22, +align (00:00:00), +items (00:00:00), +center (00:00:00), +flex (00:00:00), +direction (00:00:00), +column (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q78" authorId="0" shapeId="0">
@@ -882,12 +882,12 @@
     </comment>
     <comment ref="O79" authorId="0" shapeId="0">
       <text>
-        <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:17:21.139), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+        <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:17:21.139) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q79" authorId="0" shapeId="0">
       <text>
-        <t>-; (10:50:48.660), -; (11:10:17.104), -100 (11:14:24.924), +10 (00:00:00)</t>
+        <t>-; (10:50:48.660), -; (11:10:17.104), -100 (11:14:24.924) ~0.67, +10 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E81" authorId="0" shapeId="0">
@@ -907,7 +907,7 @@
     </comment>
     <comment ref="O81" authorId="0" shapeId="0">
       <text>
-        <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:17:21.139), -# (10:19:53.296), -vis (10:19:54.003), -- (10:19:54.226), -123456 (10:19:55.544), -{ (10:20:02.452), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), -. (10:43:24.242), -bar (10:43:31.288), -{ (10:43:32.996), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +{ (00:00:00), +. (00:00:00), +bar (00:00:00), +{ (00:00:00)</t>
+        <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:17:21.139) ~1.00, -# (10:19:53.296) ~1.00, -vis (10:19:54.003) ~1.00, -- (10:19:54.226) ~1.00, -123456 (10:19:55.544) ~1.00, -{ (10:20:02.452) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, -. (10:43:24.242) ~1.00, -bar (10:43:31.288) ~1.00, -{ (10:43:32.996) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +{ (00:00:00), +. (00:00:00), +bar (00:00:00), +{ (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q81" authorId="0" shapeId="0">
@@ -932,12 +932,12 @@
     </comment>
     <comment ref="M82" authorId="0" shapeId="0">
       <text>
-        <t>-&lt; (10:12:37.377), -/ (10:12:37.545), -head (10:12:38.381), -&gt; (10:12:38.657), +&lt; (00:00:00), +/ (00:00:00), +head (00:00:00), +&gt; (00:00:00)</t>
+        <t>-&lt; (10:12:37.377) ~1.00, -/ (10:12:37.545) ~1.00, -head (10:12:38.381) ~1.00, -&gt; (10:12:38.657) ~1.00, +&lt; (00:00:00), +/ (00:00:00), +head (00:00:00), +&gt; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O82" authorId="0" shapeId="0">
       <text>
-        <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:17:21.139), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+        <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:17:21.139) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E83" authorId="0" shapeId="0">
@@ -957,12 +957,12 @@
     </comment>
     <comment ref="O83" authorId="0" shapeId="0">
       <text>
-        <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:17:21.139), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+        <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:17:21.139) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q83" authorId="0" shapeId="0">
       <text>
-        <t>-; (10:50:48.660), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -array (11:08:34.178), -; (11:08:34.198), -function (11:08:36.630), -updateBars (11:08:38.342), -( (11:08:38.511), -) (11:08:38.687), -{ (11:08:39.319), -; (11:10:17.104), +function (00:00:00), +updateBars (00:00:00), +{ (00:00:00)</t>
+        <t>-; (10:50:48.660), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -array (11:08:34.178), -; (11:08:34.198), -function (11:08:36.630) ~1.00, -updateBars (11:08:38.342) ~1.00, -( (11:08:38.511), -) (11:08:38.687), -{ (11:08:39.319) ~1.00, -; (11:10:17.104), +function (00:00:00), +updateBars (00:00:00), +{ (00:00:00)</t>
       </text>
     </comment>
   </commentList>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:17:21.139), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), -align (10:57:30.272), -- (10:57:30.282), -items (10:57:30.332), -: (10:57:30.342), -flex (10:57:30.392), -- (10:57:30.402), -end (10:57:30.432), -; (10:57:30.442), +justify (00:00:00), +- (00:00:00), +content (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+          <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:17:21.139) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596) ~1.00, -items (10:24:13.500) ~1.00, +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), -align (10:57:30.272), -- (10:57:30.282), -items (10:57:30.332), -: (10:57:30.342), -flex (10:57:30.392), -- (10:57:30.402), -end (10:57:30.432), -; (10:57:30.442), +justify (00:00:00), +- (00:00:00), +content (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>-i (10:38:53.739), -array (10:38:55.446), -createElement (10:39:45.021), -function (10:57:37.492), -bubbleSort (10:57:42.836), -( (10:57:43.053), -arr (10:57:49.140), -) (10:57:49.861), -{ (10:57:54.715), -do (10:58:33.576), -{ (10:58:34.903), -} (10:58:35.895), -var (10:59:12.196), -swapped (10:59:20.551), -= (10:59:21.101), -false (10:59:23.105), -; (10:59:24.221), -for (10:59:26.374), -( (10:59:26.727), -let (10:59:27.295), -i (10:59:27.677), -= (10:59:27.952), -1 (10:59:28.458), -; (10:59:28.738), -i (10:59:29.253), -&lt; (10:59:29.652), -arr (10:59:30.525), -. (10:59:30.766), -length (10:59:32.061), -; (10:59:32.305), -i (10:59:32.661), -+ (10:59:32.869), -+ (10:59:33.126), -) (10:59:33.350), -{ (10:59:35.506), -} (10:59:37.396), -if (10:59:41.288), -( (10:59:41.708), -arr (10:59:42.652), -[ (10:59:42.917), -i (10:59:43.246), -- (10:59:44.058), -1 (10:59:44.656), -] (10:59:44.854), -&gt; (10:59:45.546), -arr (10:59:46.616), -[ (10:59:46.969), -i (10:59:47.212), -] (10:59:47.751), -) (10:59:48.230), -{ (10:59:49.302), -const (11:00:57.203), -aux (11:00:58.458), -= (11:01:01.660), -arr (11:01:02.684), -[ (11:01:02.941), -i (11:01:03.128), -- (11:01:03.607), -1 (11:01:04.198), -] (11:01:04.697), -; (11:01:05.017), -arr (11:01:06.389), -[ (11:01:06.650), -i (11:01:06.835), -- (11:01:07.252), -1 (11:01:07.757), -] (11:01:08.184), -= (11:01:08.961), -arr (11:01:09.861), -[ (11:01:10.052), -i (11:01:10.368), -] (11:01:10.513), -; (11:01:10.683), -arr (11:01:12.501), -[ (11:01:12.714), -i (11:01:12.894), -] (11:01:13.102), -= (11:01:13.537), -aux (11:01:14.449), -; (11:01:14.856), -swapped (11:02:15.877), -= (11:02:16.203), -true (11:02:17.158), -; (11:02:17.463), -while (11:02:23.923), -( (11:02:24.360), -swapped (11:02:25.916), -) (11:02:26.084), -; (11:02:26.436), -( (11:09:55.956), -let (11:09:56.455), -i (11:09:56.677), -= (11:09:57.008), -0 (11:09:57.490), -; (11:09:57.512), -i (11:09:57.854), -&lt; (11:09:58.223), -bars (11:09:58.993), -. (11:09:59.214), -length (11:10:00.426), -; (11:10:00.634), -i (11:10:01.376), -+ (11:10:01.600), -+ (11:10:01.789), -) (11:10:01.880), -{ (11:10:02.609), -} (11:10:03.305), -bars (11:10:05.954), -[ (11:10:06.083), -i (11:10:06.207), -] (11:10:06.517), -. (11:10:06.753), -style (11:10:08.322), -. (11:10:08.474), -height (11:10:09.606), -= (11:10:12.868), -array (11:10:13.726), -[ (11:10:13.999), -i (11:10:14.138), -] (11:10:14.279), -* (11:10:14.846), -100 (11:10:15.517), -+ (11:10:16.137), -" (11:10:16.502), -% (11:10:16.625), -" (11:10:16.705), -; (11:10:17.104), -updateBars (11:12:30.664), -( (11:12:30.752), -) (11:12:30.906), -; (11:12:31.204), -await (11:13:47.348), -new (11:13:53.570), -Promise (11:13:54.982), -( (11:13:55.301), -resolve (11:13:59.055), -= (11:14:16.118), -&gt; (11:14:16.408), -setTimeout (11:14:18.857), -( (11:14:19.066), -resolve (11:14:23.324), -, (11:14:23.491), -100 (11:14:24.924), -) (11:14:31.103), -) (11:14:31.475), -; (11:14:32.118), -async (11:15:16.100), +1 (00:00:00), +arry (00:00:00), +cretaeElement (00:00:00), +function (00:00:00), +bubbleSort (00:00:00), +( (00:00:00), +arr (00:00:00), +) (00:00:00), +{ (00:00:00), +do (00:00:00), +{ (00:00:00), +var (00:00:00), +swapped (00:00:00), += (00:00:00), +false (00:00:00), +; (00:00:00), +for (00:00:00), +( (00:00:00), +i (00:00:00), += (00:00:00), +1 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +arr (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +if (00:00:00), +( (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +- (00:00:00), +1 (00:00:00), +] (00:00:00), +&gt; (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +aux (00:00:00), += (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +- (00:00:00), +1 (00:00:00), +] (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), += (00:00:00), +aux (00:00:00), +; (00:00:00), +swapped (00:00:00), += (00:00:00), +true (00:00:00), +; (00:00:00), +updateBars (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +await (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +100 (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +while (00:00:00), +( (00:00:00), +swapped (00:00:00), +) (00:00:00), +; (00:00:00)</t>
+          <t>-i (10:38:53.739), -array (10:38:55.446) ~0.80, -createElement (10:39:45.021) ~0.85, -function (10:57:37.492) ~1.00, -bubbleSort (10:57:42.836) ~1.00, -( (10:57:43.053) ~1.00, -arr (10:57:49.140) ~1.00, -) (10:57:49.861) ~1.00, -{ (10:57:54.715) ~1.00, -do (10:58:33.576) ~1.00, -{ (10:58:34.903) ~1.00, -} (10:58:35.895), -var (10:59:12.196) ~1.00, -swapped (10:59:20.551) ~1.00, -= (10:59:21.101) ~1.00, -false (10:59:23.105) ~1.00, -; (10:59:24.221) ~1.00, -for (10:59:26.374) ~1.00, -( (10:59:26.727) ~1.00, -let (10:59:27.295), -i (10:59:27.677) ~1.00, -= (10:59:27.952) ~1.00, -1 (10:59:28.458) ~1.00, -; (10:59:28.738) ~1.00, -i (10:59:29.253) ~1.00, -&lt; (10:59:29.652) ~1.00, -arr (10:59:30.525) ~1.00, -. (10:59:30.766) ~1.00, -length (10:59:32.061) ~1.00, -; (10:59:32.305) ~1.00, -i (10:59:32.661) ~1.00, -+ (10:59:32.869) ~1.00, -+ (10:59:33.126) ~1.00, -) (10:59:33.350) ~1.00, -{ (10:59:35.506) ~1.00, -} (10:59:37.396), -if (10:59:41.288) ~1.00, -( (10:59:41.708) ~1.00, -arr (10:59:42.652) ~1.00, -[ (10:59:42.917) ~1.00, -i (10:59:43.246) ~1.00, -- (10:59:44.058) ~1.00, -1 (10:59:44.656) ~1.00, -] (10:59:44.854) ~1.00, -&gt; (10:59:45.546) ~1.00, -arr (10:59:46.616) ~1.00, -[ (10:59:46.969) ~1.00, -i (10:59:47.212) ~1.00, -] (10:59:47.751) ~1.00, -) (10:59:48.230) ~1.00, -{ (10:59:49.302) ~1.00, -const (11:00:57.203) ~1.00, -aux (11:00:58.458) ~1.00, -= (11:01:01.660) ~1.00, -arr (11:01:02.684) ~1.00, -[ (11:01:02.941) ~1.00, -i (11:01:03.128) ~1.00, -- (11:01:03.607) ~1.00, -1 (11:01:04.198) ~1.00, -] (11:01:04.697) ~1.00, -; (11:01:05.017), -arr (11:01:06.389), -[ (11:01:06.650), -i (11:01:06.835), -- (11:01:07.252), -1 (11:01:07.757), -] (11:01:08.184), -= (11:01:08.961), -arr (11:01:09.861), -[ (11:01:10.052), -i (11:01:10.368), -] (11:01:10.513), -; (11:01:10.683), -arr (11:01:12.501) ~1.00, -[ (11:01:12.714) ~1.00, -i (11:01:12.894) ~1.00, -] (11:01:13.102) ~1.00, -= (11:01:13.537) ~1.00, -aux (11:01:14.449) ~1.00, -; (11:01:14.856) ~1.00, -swapped (11:02:15.877) ~1.00, -= (11:02:16.203) ~1.00, -true (11:02:17.158) ~1.00, -; (11:02:17.463) ~1.00, -while (11:02:23.923) ~1.00, -( (11:02:24.360) ~1.00, -swapped (11:02:25.916) ~1.00, -) (11:02:26.084) ~1.00, -; (11:02:26.436) ~1.00, -( (11:09:55.956), -let (11:09:56.455), -i (11:09:56.677), -= (11:09:57.008), -0 (11:09:57.490), -; (11:09:57.512), -i (11:09:57.854) ~0.00, -&lt; (11:09:58.223), -bars (11:09:58.993), -. (11:09:59.214), -length (11:10:00.426), -; (11:10:00.634), -i (11:10:01.376), -+ (11:10:01.600), -+ (11:10:01.789), -) (11:10:01.880), -{ (11:10:02.609), -} (11:10:03.305), -bars (11:10:05.954), -[ (11:10:06.083), -i (11:10:06.207), -] (11:10:06.517), -. (11:10:06.753), -style (11:10:08.322), -. (11:10:08.474), -height (11:10:09.606), -= (11:10:12.868), -array (11:10:13.726), -[ (11:10:13.999), -i (11:10:14.138), -] (11:10:14.279), -* (11:10:14.846), -100 (11:10:15.517), -+ (11:10:16.137), -" (11:10:16.502), -% (11:10:16.625), -" (11:10:16.705), -; (11:10:17.104), -updateBars (11:12:30.664) ~1.00, -( (11:12:30.752) ~1.00, -) (11:12:30.906) ~1.00, -; (11:12:31.204) ~1.00, -await (11:13:47.348) ~1.00, -new (11:13:53.570) ~1.00, -Promise (11:13:54.982) ~1.00, -( (11:13:55.301) ~1.00, -resolve (11:13:59.055) ~1.00, -= (11:14:16.118) ~1.00, -&gt; (11:14:16.408) ~1.00, -setTimeout (11:14:18.857) ~1.00, -( (11:14:19.066) ~1.00, -resolve (11:14:23.324) ~1.00, -, (11:14:23.491) ~1.00, -100 (11:14:24.924) ~1.00, -) (11:14:31.103) ~1.00, -) (11:14:31.475) ~1.00, -; (11:14:32.118) ~1.00, -async (11:15:16.100), +1 (00:00:00), +arry (00:00:00), +cretaeElement (00:00:00), +function (00:00:00), +bubbleSort (00:00:00), +( (00:00:00), +arr (00:00:00), +) (00:00:00), +{ (00:00:00), +do (00:00:00), +{ (00:00:00), +var (00:00:00), +swapped (00:00:00), += (00:00:00), +false (00:00:00), +; (00:00:00), +for (00:00:00), +( (00:00:00), +i (00:00:00), += (00:00:00), +1 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +arr (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +if (00:00:00), +( (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +- (00:00:00), +1 (00:00:00), +] (00:00:00), +&gt; (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +aux (00:00:00), += (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +- (00:00:00), +1 (00:00:00), +] (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), += (00:00:00), +aux (00:00:00), +; (00:00:00), +swapped (00:00:00), += (00:00:00), +true (00:00:00), +; (00:00:00), +updateBars (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +await (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +100 (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +while (00:00:00), +( (00:00:00), +swapped (00:00:00), +) (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:17:21.139), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+          <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:17:21.139) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q5" t="n">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>-for (10:30:13.868), -( (10:30:14.352), -let (10:30:15.164), -i (10:30:15.672), -= (10:30:16.329), -0 (10:30:16.771), -; (10:30:17.011), -i (10:30:17.443), -&lt; (10:30:18.073), -count (10:30:20.284), -; (10:30:20.584), -i (10:30:47.713), -+ (10:30:48.171), -+ (10:30:48.660), -) (10:30:49.210), -{ (10:31:12.723), -array (10:31:16.948), -[ (10:31:17.188), -] (10:31:22.021), -Math (10:31:30.068), -. (10:31:30.292), -random (10:31:31.871), -( (10:31:32.250), -; (10:31:32.818), -var (10:59:12.196), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -} (11:10:03.305), +for (00:00:00), +( (00:00:00), +let (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +count (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +{ (00:00:00), +array (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), += (00:00:00), +Math (00:00:00), +. (00:00:00), +random (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +let (00:00:00)</t>
+          <t>-for (10:30:13.868) ~1.00, -( (10:30:14.352) ~1.00, -let (10:30:15.164) ~1.00, -i (10:30:15.672), -= (10:30:16.329), -0 (10:30:16.771) ~1.00, -; (10:30:17.011) ~1.00, -i (10:30:17.443) ~1.00, -&lt; (10:30:18.073) ~1.00, -count (10:30:20.284) ~1.00, -; (10:30:20.584) ~1.00, -i (10:30:47.713) ~1.00, -+ (10:30:48.171) ~1.00, -+ (10:30:48.660) ~1.00, -) (10:30:49.210), -{ (10:31:12.723) ~1.00, -array (10:31:16.948) ~1.00, -[ (10:31:17.188) ~1.00, -] (10:31:22.021) ~1.00, -Math (10:31:30.068) ~1.00, -. (10:31:30.292) ~1.00, -random (10:31:31.871) ~1.00, -( (10:31:32.250) ~1.00, -; (10:31:32.818) ~1.00, -var (10:59:12.196) ~0.00, +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -} (11:10:03.305), +for (00:00:00), +( (00:00:00), +let (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +count (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +{ (00:00:00), +array (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), += (00:00:00), +Math (00:00:00), +. (00:00:00), +random (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +let (00:00:00)</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>-&lt; (10:12:37.377), -/ (10:12:37.545), -head (10:12:38.381), -&gt; (10:12:38.657), -Visualizer (10:12:47.677), -&lt; (10:12:59.962), -body (10:13:00.878), -&gt; (10:13:01.096), -&lt; (10:13:08.462), -h1 (10:13:08.883), -&gt; (10:13:09.312), -Sorting (10:13:13.802), -Visualizer (10:13:16.993), -&lt; (10:13:17.335), -/ (10:13:17.789), -h1 (10:13:18.123), -&gt; (10:13:18.254), -&lt; (10:17:05.513), -/ (10:17:05.729), -style (10:17:06.766), -&gt; (10:17:06.867), -&lt; (10:18:29.900), -div (10:18:30.558), -id (10:18:31.498), -= (10:18:31.631), -" (10:18:33.349), -vis (10:18:34.420), -- (10:18:37.062), -123456 (10:18:40.665), -" (10:18:40.947), -&gt; (10:18:43.208), -&lt; (10:18:44.230), -/ (10:18:44.552), -div (10:18:45.086), -&gt; (10:18:45.251), -&lt; (10:27:13.253), -script (10:27:14.426), -&gt; (10:27:14.698), +visualizer (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +style (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +head (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +body (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +h1 (00:00:00), +&gt; (00:00:00), +Sorting (00:00:00), +visualizer (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +h1 (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +script (00:00:00), +&gt; (00:00:00)</t>
+          <t>-&lt; (10:12:37.377) ~1.00, -/ (10:12:37.545) ~1.00, -head (10:12:38.381) ~1.00, -&gt; (10:12:38.657) ~1.00, -Visualizer (10:12:47.677) ~0.90, -&lt; (10:12:59.962) ~1.00, -body (10:13:00.878) ~1.00, -&gt; (10:13:01.096) ~1.00, -&lt; (10:13:08.462) ~1.00, -h1 (10:13:08.883) ~1.00, -&gt; (10:13:09.312) ~1.00, -Sorting (10:13:13.802) ~1.00, -Visualizer (10:13:16.993) ~0.90, -&lt; (10:13:17.335) ~1.00, -/ (10:13:17.789) ~1.00, -h1 (10:13:18.123) ~1.00, -&gt; (10:13:18.254) ~1.00, -&lt; (10:17:05.513) ~1.00, -/ (10:17:05.729) ~1.00, -style (10:17:06.766) ~1.00, -&gt; (10:17:06.867) ~1.00, -&lt; (10:18:29.900) ~1.00, -div (10:18:30.558) ~1.00, -id (10:18:31.498) ~1.00, -= (10:18:31.631) ~1.00, -" (10:18:33.349) ~1.00, -vis (10:18:34.420) ~1.00, -- (10:18:37.062) ~1.00, -123456 (10:18:40.665) ~1.00, -" (10:18:40.947) ~1.00, -&gt; (10:18:43.208) ~1.00, -&lt; (10:18:44.230) ~1.00, -/ (10:18:44.552) ~1.00, -div (10:18:45.086) ~1.00, -&gt; (10:18:45.251) ~1.00, -&lt; (10:27:13.253) ~1.00, -script (10:27:14.426) ~1.00, -&gt; (10:27:14.698) ~1.00, +visualizer (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +style (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +head (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +body (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +h1 (00:00:00), +&gt; (00:00:00), +Sorting (00:00:00), +visualizer (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +h1 (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +script (00:00:00), +&gt; (00:00:00)</t>
         </is>
       </c>
       <c r="O9" t="n">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>-center (10:17:20.707), -# (10:19:53.296), -vis (10:19:54.003), -- (10:19:54.226), -123456 (10:19:55.544), -height (10:20:07.891), -: (10:20:07.983), -200px (10:20:09.051), -; (10:20:09.451), -flex (10:21:58.800), -direction (10:22:01.758), -column (10:22:03.223), -align (10:24:12.446), -items (10:24:13.500), -. (10:43:24.242), -bar (10:43:31.288), -{ (10:43:32.996), -width (10:43:37.644), -: (10:43:37.716), -7px (10:43:39.527), -; (10:43:40.239), -height (10:43:47.504), -: (10:43:47.683), -100 (10:43:48.485), -% (10:43:48.586), -; (10:43:48.809), -background (10:44:24.231), -- (10:44:24.311), -color (10:44:25.031), -: (10:44:25.154), -black (10:44:26.271), -; (10:44:26.592), -display (10:47:38.305), -: (10:47:38.437), -flex (10:47:39.551), -; (10:47:39.811), -margin (10:48:02.482), -: (10:48:02.549), -0px (10:48:03.827), -1px (10:48:07.241), +;* (10:50:09.333), -align (10:57:30.272), -- (10:57:30.282), -items (10:57:30.332), -: (10:57:30.342), -flex (10:57:30.392), -- (10:57:30.402), -end (10:57:30.432), +align (00:00:00), +items (00:00:00), +center (00:00:00), +flex (00:00:00), +direction (00:00:00), +column (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +{ (00:00:00), +height (00:00:00), +: (00:00:00), +200px (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +flex (00:00:00), +- (00:00:00), +end (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +bar (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +7px (00:00:00), +; (00:00:00), +height (00:00:00), +: (00:00:00), +100 (00:00:00), +% (00:00:00), +; (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +black (00:00:00), +; (00:00:00), +margin (00:00:00), +: (00:00:00), +0px (00:00:00), +1px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+          <t>-center (10:17:20.707) ~0.17, -# (10:19:53.296) ~1.00, -vis (10:19:54.003) ~1.00, -- (10:19:54.226) ~1.00, -123456 (10:19:55.544) ~1.00, -height (10:20:07.891) ~1.00, -: (10:20:07.983) ~1.00, -200px (10:20:09.051) ~1.00, -; (10:20:09.451), -flex (10:21:58.800) ~0.20, -direction (10:22:01.758) ~0.22, -column (10:22:03.223) ~1.00, -align (10:24:12.446) ~0.00, -items (10:24:13.500) ~0.14, -. (10:43:24.242) ~1.00, -bar (10:43:31.288) ~1.00, -{ (10:43:32.996) ~1.00, -width (10:43:37.644) ~1.00, -: (10:43:37.716) ~1.00, -7px (10:43:39.527) ~1.00, -; (10:43:40.239) ~1.00, -height (10:43:47.504) ~1.00, -: (10:43:47.683) ~1.00, -100 (10:43:48.485) ~1.00, -% (10:43:48.586) ~1.00, -; (10:43:48.809) ~1.00, -background (10:44:24.231) ~1.00, -- (10:44:24.311) ~1.00, -color (10:44:25.031) ~1.00, -: (10:44:25.154) ~1.00, -black (10:44:26.271) ~1.00, -; (10:44:26.592) ~1.00, -display (10:47:38.305) ~1.00, -: (10:47:38.437) ~1.00, -flex (10:47:39.551) ~1.00, -; (10:47:39.811) ~1.00, -margin (10:48:02.482) ~1.00, -: (10:48:02.549) ~1.00, -0px (10:48:03.827) ~1.00, -1px (10:48:07.241) ~1.00, +;* (10:50:09.333), -align (10:57:30.272) ~1.00, -- (10:57:30.282) ~1.00, -items (10:57:30.332) ~1.00, -: (10:57:30.342) ~1.00, -flex (10:57:30.392) ~1.00, -- (10:57:30.402) ~1.00, -end (10:57:30.432) ~1.00, +align (00:00:00), +items (00:00:00), +center (00:00:00), +flex (00:00:00), +direction (00:00:00), +column (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +} (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +{ (00:00:00), +height (00:00:00), +: (00:00:00), +200px (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +flex (00:00:00), +- (00:00:00), +end (00:00:00), +; (00:00:00), +} (00:00:00), +. (00:00:00), +bar (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +7px (00:00:00), +; (00:00:00), +height (00:00:00), +: (00:00:00), +100 (00:00:00), +% (00:00:00), +; (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +: (00:00:00), +black (00:00:00), +; (00:00:00), +margin (00:00:00), +: (00:00:00), +0px (00:00:00), +1px (00:00:00), +; (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="Q9" t="n">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>-const (10:27:46.114), -count (10:27:47.499), -= (10:27:48.489), -50 (10:27:50.527), -; (10:27:51.439), -const (10:28:42.502), -array (10:28:45.898), -= (10:28:48.193), -new (10:28:49.261), -Array (10:28:50.400), -( (10:28:50.634), -count (10:28:52.202), -) (10:28:52.450), -; (10:28:52.802), -for (10:30:13.868), -( (10:30:14.352), -let (10:30:15.164), -i (10:30:15.672), -= (10:30:16.329), -0 (10:30:16.771), -; (10:30:17.011), -i (10:30:17.443), -&lt; (10:30:18.073), -count (10:30:20.284), -; (10:30:20.584), -i (10:30:47.713), -+ (10:30:48.171), -+ (10:30:48.660), -) (10:30:49.210), -{ (10:31:12.723), -array (10:31:16.948), -[ (10:31:17.188), -i (10:31:18.211), -] (10:31:22.021), -= (10:31:23.399), -Math (10:31:30.068), -. (10:31:30.292), -random (10:31:31.871), -( (10:31:32.250), -) (10:31:32.537), -; (10:31:32.818), -const (10:37:42.386), -visualizer (10:37:44.631), -= (10:37:45.082), -document (10:37:47.323), -. (10:37:47.760), -getElementById (10:38:03.158), -( (10:38:03.433), -" (10:38:19.019), -vis (10:38:19.926), -- (10:38:20.217), -123456 (10:38:22.251), -" (10:38:22.629), -) (10:38:22.754), -; (10:38:23.727), -for (10:38:50.477), -( (10:38:50.999), -let (10:38:51.733), -i (10:38:52.267), -= (10:38:52.612), -0 (10:38:53.033), -; (10:38:53.257), -i (10:38:53.739), -&lt; (10:38:54.145), -array (10:38:55.446), -. (10:38:55.684), -length (10:38:57.372), -; (10:38:57.593), -i (10:38:58.029), -+ (10:38:58.280), -+ (10:38:58.511), -) (10:38:58.809), -{ (10:39:16.312), -const (10:39:36.638), -bar (10:39:37.346), -= (10:39:37.875), -document (10:39:42.722), -. (10:39:42.888), -createElement (10:39:45.021), -( (10:39:45.078), -" (10:39:45.883), -div (10:39:48.709), -" (10:39:48.892), -) (10:39:49.655), -; (10:39:49.907), -visualizer (10:40:27.992), -. (10:40:28.151), -appendChild (10:40:30.229), -( (10:40:30.435), -bar (10:40:31.317), -) (10:40:31.505), -; (10:40:32.101), -bar (10:42:30.607), -. (10:42:30.785), -classList (10:42:32.670), -. (10:42:32.869), -add (10:42:33.487), -( (10:42:33.684), -" (10:42:33.916), -bar (10:42:35.380), -" (10:42:35.625), -) (10:42:36.061), -; (10:42:36.565), -bar (10:50:10.577), -. (10:50:10.720), -style (10:50:11.842), -. (10:50:12.547), -height (10:50:14.172), -= (10:50:15.244), -array (10:50:17.753), -[ (10:50:17.905), -i (10:50:18.168), -] (10:50:18.460), -* (10:50:28.020), -100 (10:50:29.694), -+ (10:50:38.934), -" (10:50:40.368), -% (10:50:40.883), -" (10:50:41.432), -; (10:50:48.660), -function (10:57:37.492), -bubbleSort (10:57:42.836), -( (10:57:43.053), -arr (10:57:49.140), -) (10:57:49.861), -{ (10:57:54.715), -} (10:57:57.644), -do (10:58:33.576), -{ (10:58:34.903), -} (10:58:35.895), -var (10:59:12.196), -swapped (10:59:20.551), -= (10:59:21.101), -false (10:59:23.105), -; (10:59:24.221), -for (10:59:26.374), -( (10:59:26.727), -let (10:59:27.295), -i (10:59:27.677), -= (10:59:27.952), -1 (10:59:28.458), -; (10:59:28.738), -i (10:59:29.253), -&lt; (10:59:29.652), -arr (10:59:30.525), -. (10:59:30.766), -length (10:59:32.061), -; (10:59:32.305), -i (10:59:32.661), -+ (10:59:32.869), -+ (10:59:33.126), -) (10:59:33.350), -{ (10:59:35.506), -} (10:59:37.396), -if (10:59:41.288), -( (10:59:41.708), -arr (10:59:42.652), -[ (10:59:42.917), -i (10:59:43.246), -- (10:59:44.058), -1 (10:59:44.656), -] (10:59:44.854), -&gt; (10:59:45.546), -arr (10:59:46.616), -[ (10:59:46.969), -i (10:59:47.212), -] (10:59:47.751), -) (10:59:48.230), -{ (10:59:49.302), -} (10:59:50.413), -const (11:00:57.203), -aux (11:00:58.458), -= (11:01:01.660), -arr (11:01:02.684), -[ (11:01:02.941), -i (11:01:03.128), -- (11:01:03.607), -1 (11:01:04.198), -] (11:01:04.697), -; (11:01:05.017), -arr (11:01:06.389), -[ (11:01:06.650), -i (11:01:06.835), -- (11:01:07.252), -1 (11:01:07.757), -] (11:01:08.184), -= (11:01:08.961), -arr (11:01:09.861), -[ (11:01:10.052), -i (11:01:10.368), -] (11:01:10.513), -; (11:01:10.683), -arr (11:01:12.501), -[ (11:01:12.714), -i (11:01:12.894), -] (11:01:13.102), -= (11:01:13.537), -aux (11:01:14.449), -; (11:01:14.856), -swapped (11:02:15.877), -= (11:02:16.203), -true (11:02:17.158), -; (11:02:17.463), -while (11:02:23.923), -( (11:02:24.360), -swapped (11:02:25.916), -) (11:02:26.084), -; (11:02:26.436), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -function (11:08:36.630), -updateBars (11:08:38.342), -( (11:08:38.511), -) (11:08:38.687), -{ (11:08:39.319), -} (11:08:40.006), -const (11:09:21.850), -bars (11:09:22.876), -= (11:09:23.405), -document (11:09:24.920), -. (11:09:25.072), -getElementsByClassName (11:09:28.891), -( (11:09:28.949), -" (11:09:29.056), -bar (11:09:29.764), -" (11:09:29.897), -) (11:09:29.998), -; (11:09:30.476), -for (11:09:55.616), -( (11:09:55.956), -let (11:09:56.455), -i (11:09:56.677), -= (11:09:57.008), -0 (11:09:57.490), -; (11:09:57.512), -i (11:09:57.854), -&lt; (11:09:58.223), -bars (11:09:58.993), -. (11:09:59.214), -length (11:10:00.426), -; (11:10:00.634), -i (11:10:01.376), -+ (11:10:01.600), -+ (11:10:01.789), -) (11:10:01.880), -{ (11:10:02.609), -} (11:10:03.305), -bars (11:10:05.954), -[ (11:10:06.083), -i (11:10:06.207), -] (11:10:06.517), -. (11:10:06.753), -style (11:10:08.322), -. (11:10:08.474), -height (11:10:09.606), -= (11:10:12.868), -array (11:10:13.726), -[ (11:10:13.999), -i (11:10:14.138), -] (11:10:14.279), -* (11:10:14.846), -100 (11:10:15.517), -+ (11:10:16.137), -" (11:10:16.502), -% (11:10:16.625), -" (11:10:16.705), -; (11:10:17.104), -updateBars (11:12:30.664), -( (11:12:30.752), -) (11:12:30.906), -; (11:12:31.204), -await (11:13:47.348), -new (11:13:53.570), -Promise (11:13:54.982), -( (11:13:55.301), -resolve (11:13:59.055), -= (11:14:16.118), -&gt; (11:14:16.408), -setTimeout (11:14:18.857), -( (11:14:19.066), -resolve (11:14:23.324), -, (11:14:23.491), -100 (11:14:24.924), -) (11:14:31.103), -) (11:14:31.475), -; (11:14:32.118), -async (11:15:16.100), +const (00:00:00), +count (00:00:00), += (00:00:00), +50 (00:00:00), +; (00:00:00), +const (00:00:00), +array (00:00:00), += (00:00:00), +new (00:00:00), +Array (00:00:00), +( (00:00:00), +count (00:00:00), +) (00:00:00), +; (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +count (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +array (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), += (00:00:00), +Math (00:00:00), +. (00:00:00), +random (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +const (00:00:00), +visualizer (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +array (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bar (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +createElement (00:00:00), +( (00:00:00), +" (00:00:00), +div (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +visualizer (00:00:00), +. (00:00:00), +appendChild (00:00:00), +( (00:00:00), +bar (00:00:00), +) (00:00:00), +; (00:00:00), +bar (00:00:00), +. (00:00:00), +classList (00:00:00), +. (00:00:00), +add (00:00:00), +( (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +bar (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +height (00:00:00), += (00:00:00), +array (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +* (00:00:00), +100 (00:00:00), ++ (00:00:00), +" (00:00:00), +% (00:00:00), +" (00:00:00), +; (00:00:00), +function (00:00:00), +bubbleSort (00:00:00), +( (00:00:00), +array (00:00:00), +) (00:00:00), +function (00:00:00), +updatebars (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bars (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementByClassName (00:00:00), +( (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +) (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +bars (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +height (00:00:00), += (00:00:00), +array (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +* (00:00:00), +100 (00:00:00), ++ (00:00:00), +" (00:00:00), +% (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00), +async (00:00:00), +function (00:00:00), +bubbleSort (00:00:00), +( (00:00:00), +arr (00:00:00), +) (00:00:00), +{ (00:00:00), +do (00:00:00), +{ (00:00:00), +var (00:00:00), +swapped (00:00:00), += (00:00:00), +false (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +1 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +arr (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +if (00:00:00), +( (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +- (00:00:00), +1 (00:00:00), +] (00:00:00), +&gt; (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +aux (00:00:00), += (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +- (00:00:00), +1 (00:00:00), +] (00:00:00), +; (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +- (00:00:00), +1 (00:00:00), +] (00:00:00), += (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +; (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), += (00:00:00), +aux (00:00:00), +; (00:00:00), +swapped (00:00:00), += (00:00:00), +true (00:00:00), +; (00:00:00), +updateBars (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +await (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +100 (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +while (00:00:00), +( (00:00:00), +swapped (00:00:00), +) (00:00:00), +; (00:00:00)</t>
+          <t>-const (10:27:46.114) ~1.00, -count (10:27:47.499) ~1.00, -= (10:27:48.489) ~1.00, -50 (10:27:50.527) ~1.00, -; (10:27:51.439) ~1.00, -const (10:28:42.502) ~1.00, -array (10:28:45.898) ~1.00, -= (10:28:48.193) ~1.00, -new (10:28:49.261) ~1.00, -Array (10:28:50.400) ~1.00, -( (10:28:50.634) ~1.00, -count (10:28:52.202) ~1.00, -) (10:28:52.450) ~1.00, -; (10:28:52.802) ~1.00, -for (10:30:13.868) ~1.00, -( (10:30:14.352) ~1.00, -let (10:30:15.164) ~1.00, -i (10:30:15.672) ~1.00, -= (10:30:16.329) ~1.00, -0 (10:30:16.771) ~1.00, -; (10:30:17.011) ~1.00, -i (10:30:17.443) ~1.00, -&lt; (10:30:18.073) ~1.00, -count (10:30:20.284) ~1.00, -; (10:30:20.584) ~1.00, -i (10:30:47.713) ~1.00, -+ (10:30:48.171) ~1.00, -+ (10:30:48.660) ~1.00, -) (10:30:49.210) ~1.00, -{ (10:31:12.723) ~1.00, -array (10:31:16.948) ~1.00, -[ (10:31:17.188) ~1.00, -i (10:31:18.211) ~1.00, -] (10:31:22.021) ~1.00, -= (10:31:23.399) ~1.00, -Math (10:31:30.068) ~1.00, -. (10:31:30.292) ~1.00, -random (10:31:31.871) ~1.00, -( (10:31:32.250) ~1.00, -) (10:31:32.537) ~1.00, -; (10:31:32.818) ~1.00, -const (10:37:42.386) ~1.00, -visualizer (10:37:44.631) ~1.00, -= (10:37:45.082) ~1.00, -document (10:37:47.323) ~1.00, -. (10:37:47.760) ~1.00, -getElementById (10:38:03.158) ~1.00, -( (10:38:03.433) ~1.00, -" (10:38:19.019) ~1.00, -vis (10:38:19.926) ~1.00, -- (10:38:20.217) ~1.00, -123456 (10:38:22.251) ~1.00, -" (10:38:22.629) ~1.00, -) (10:38:22.754) ~1.00, -; (10:38:23.727) ~1.00, -for (10:38:50.477) ~1.00, -( (10:38:50.999) ~1.00, -let (10:38:51.733) ~1.00, -i (10:38:52.267) ~1.00, -= (10:38:52.612) ~1.00, -0 (10:38:53.033) ~1.00, -; (10:38:53.257) ~1.00, -i (10:38:53.739) ~1.00, -&lt; (10:38:54.145) ~1.00, -array (10:38:55.446) ~1.00, -. (10:38:55.684) ~1.00, -length (10:38:57.372) ~1.00, -; (10:38:57.593) ~1.00, -i (10:38:58.029) ~1.00, -+ (10:38:58.280) ~1.00, -+ (10:38:58.511) ~1.00, -) (10:38:58.809) ~1.00, -{ (10:39:16.312) ~1.00, -const (10:39:36.638) ~1.00, -bar (10:39:37.346) ~1.00, -= (10:39:37.875) ~1.00, -document (10:39:42.722) ~1.00, -. (10:39:42.888) ~1.00, -createElement (10:39:45.021) ~1.00, -( (10:39:45.078) ~1.00, -" (10:39:45.883) ~1.00, -div (10:39:48.709) ~1.00, -" (10:39:48.892) ~1.00, -) (10:39:49.655) ~1.00, -; (10:39:49.907) ~1.00, -visualizer (10:40:27.992) ~1.00, -. (10:40:28.151) ~1.00, -appendChild (10:40:30.229) ~1.00, -( (10:40:30.435) ~1.00, -bar (10:40:31.317) ~1.00, -) (10:40:31.505) ~1.00, -; (10:40:32.101) ~1.00, -bar (10:42:30.607) ~1.00, -. (10:42:30.785) ~1.00, -classList (10:42:32.670) ~1.00, -. (10:42:32.869) ~1.00, -add (10:42:33.487) ~1.00, -( (10:42:33.684) ~1.00, -" (10:42:33.916) ~1.00, -bar (10:42:35.380) ~1.00, -" (10:42:35.625) ~1.00, -) (10:42:36.061) ~1.00, -; (10:42:36.565) ~1.00, -bar (10:50:10.577) ~1.00, -. (10:50:10.720) ~1.00, -style (10:50:11.842) ~1.00, -. (10:50:12.547) ~1.00, -height (10:50:14.172) ~1.00, -= (10:50:15.244) ~1.00, -array (10:50:17.753) ~1.00, -[ (10:50:17.905) ~1.00, -i (10:50:18.168) ~1.00, -] (10:50:18.460) ~1.00, -* (10:50:28.020) ~1.00, -100 (10:50:29.694) ~1.00, -+ (10:50:38.934) ~1.00, -" (10:50:40.368) ~1.00, -% (10:50:40.883) ~1.00, -" (10:50:41.432) ~1.00, -; (10:50:48.660) ~1.00, -function (10:57:37.492) ~1.00, -bubbleSort (10:57:42.836) ~1.00, -( (10:57:43.053) ~1.00, -arr (10:57:49.140) ~1.00, -) (10:57:49.861) ~1.00, -{ (10:57:54.715) ~1.00, -} (10:57:57.644) ~1.00, -do (10:58:33.576) ~1.00, -{ (10:58:34.903) ~1.00, -} (10:58:35.895) ~1.00, -var (10:59:12.196) ~1.00, -swapped (10:59:20.551) ~1.00, -= (10:59:21.101) ~1.00, -false (10:59:23.105) ~1.00, -; (10:59:24.221), -for (10:59:26.374) ~1.00, -( (10:59:26.727) ~1.00, -let (10:59:27.295) ~1.00, -i (10:59:27.677) ~1.00, -= (10:59:27.952) ~1.00, -1 (10:59:28.458) ~1.00, -; (10:59:28.738) ~1.00, -i (10:59:29.253) ~1.00, -&lt; (10:59:29.652) ~1.00, -arr (10:59:30.525) ~1.00, -. (10:59:30.766) ~1.00, -length (10:59:32.061) ~1.00, -; (10:59:32.305) ~1.00, -i (10:59:32.661) ~1.00, -+ (10:59:32.869) ~1.00, -+ (10:59:33.126) ~1.00, -) (10:59:33.350) ~1.00, -{ (10:59:35.506) ~1.00, -} (10:59:37.396), -if (10:59:41.288) ~1.00, -( (10:59:41.708) ~1.00, -arr (10:59:42.652) ~1.00, -[ (10:59:42.917) ~1.00, -i (10:59:43.246) ~1.00, -- (10:59:44.058) ~1.00, -1 (10:59:44.656) ~1.00, -] (10:59:44.854) ~1.00, -&gt; (10:59:45.546) ~1.00, -arr (10:59:46.616) ~1.00, -[ (10:59:46.969) ~1.00, -i (10:59:47.212) ~1.00, -] (10:59:47.751) ~1.00, -) (10:59:48.230) ~1.00, -{ (10:59:49.302) ~1.00, -} (10:59:50.413), -const (11:00:57.203) ~1.00, -aux (11:00:58.458) ~1.00, -= (11:01:01.660) ~1.00, -arr (11:01:02.684) ~1.00, -[ (11:01:02.941) ~1.00, -i (11:01:03.128) ~1.00, -- (11:01:03.607) ~1.00, -1 (11:01:04.198) ~1.00, -] (11:01:04.697) ~1.00, -; (11:01:05.017) ~1.00, -arr (11:01:06.389) ~1.00, -[ (11:01:06.650) ~1.00, -i (11:01:06.835) ~1.00, -- (11:01:07.252) ~1.00, -1 (11:01:07.757) ~1.00, -] (11:01:08.184) ~1.00, -= (11:01:08.961) ~1.00, -arr (11:01:09.861) ~1.00, -[ (11:01:10.052) ~1.00, -i (11:01:10.368) ~1.00, -] (11:01:10.513) ~1.00, -; (11:01:10.683) ~1.00, -arr (11:01:12.501) ~1.00, -[ (11:01:12.714) ~1.00, -i (11:01:12.894) ~1.00, -] (11:01:13.102) ~1.00, -= (11:01:13.537) ~1.00, -aux (11:01:14.449) ~1.00, -; (11:01:14.856) ~1.00, -swapped (11:02:15.877) ~1.00, -= (11:02:16.203) ~1.00, -true (11:02:17.158) ~1.00, -; (11:02:17.463) ~1.00, -while (11:02:23.923) ~1.00, -( (11:02:24.360) ~1.00, -swapped (11:02:25.916) ~1.00, -) (11:02:26.084) ~1.00, -; (11:02:26.436) ~1.00, +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118) ~1.00, -( (11:08:34.128) ~1.00, -array (11:08:34.178) ~1.00, -) (11:08:34.188) ~1.00, -; (11:08:34.198), -function (11:08:36.630) ~1.00, -updateBars (11:08:38.342) ~0.90, -( (11:08:38.511) ~1.00, -) (11:08:38.687) ~1.00, -{ (11:08:39.319) ~1.00, -} (11:08:40.006) ~1.00, -const (11:09:21.850) ~1.00, -bars (11:09:22.876) ~1.00, -= (11:09:23.405) ~1.00, -document (11:09:24.920) ~1.00, -. (11:09:25.072) ~1.00, -getElementsByClassName (11:09:28.891) ~0.95, -( (11:09:28.949) ~1.00, -" (11:09:29.056) ~1.00, -bar (11:09:29.764) ~1.00, -" (11:09:29.897) ~1.00, -) (11:09:29.998) ~1.00, -; (11:09:30.476), -for (11:09:55.616) ~1.00, -( (11:09:55.956) ~1.00, -let (11:09:56.455) ~1.00, -i (11:09:56.677) ~1.00, -= (11:09:57.008) ~1.00, -0 (11:09:57.490) ~1.00, -; (11:09:57.512) ~1.00, -i (11:09:57.854) ~1.00, -&lt; (11:09:58.223) ~1.00, -bars (11:09:58.993) ~1.00, -. (11:09:59.214) ~1.00, -length (11:10:00.426) ~1.00, -; (11:10:00.634) ~1.00, -i (11:10:01.376) ~1.00, -+ (11:10:01.600) ~1.00, -+ (11:10:01.789) ~1.00, -) (11:10:01.880) ~1.00, -{ (11:10:02.609) ~1.00, -} (11:10:03.305) ~1.00, -bars (11:10:05.954) ~1.00, -[ (11:10:06.083) ~1.00, -i (11:10:06.207) ~1.00, -] (11:10:06.517) ~1.00, -. (11:10:06.753) ~1.00, -style (11:10:08.322) ~1.00, -. (11:10:08.474) ~1.00, -height (11:10:09.606) ~1.00, -= (11:10:12.868) ~1.00, -array (11:10:13.726) ~1.00, -[ (11:10:13.999) ~1.00, -i (11:10:14.138) ~1.00, -] (11:10:14.279) ~1.00, -* (11:10:14.846) ~1.00, -100 (11:10:15.517) ~1.00, -+ (11:10:16.137) ~1.00, -" (11:10:16.502) ~1.00, -% (11:10:16.625) ~1.00, -" (11:10:16.705) ~1.00, -; (11:10:17.104) ~1.00, -updateBars (11:12:30.664) ~1.00, -( (11:12:30.752) ~1.00, -) (11:12:30.906) ~1.00, -; (11:12:31.204) ~1.00, -await (11:13:47.348) ~1.00, -new (11:13:53.570) ~1.00, -Promise (11:13:54.982) ~1.00, -( (11:13:55.301) ~1.00, -resolve (11:13:59.055) ~1.00, -= (11:14:16.118) ~1.00, -&gt; (11:14:16.408) ~1.00, -setTimeout (11:14:18.857) ~1.00, -( (11:14:19.066) ~1.00, -resolve (11:14:23.324) ~1.00, -, (11:14:23.491) ~1.00, -100 (11:14:24.924) ~1.00, -) (11:14:31.103) ~1.00, -) (11:14:31.475) ~1.00, -; (11:14:32.118) ~1.00, -async (11:15:16.100) ~1.00, +const (00:00:00), +count (00:00:00), += (00:00:00), +50 (00:00:00), +; (00:00:00), +const (00:00:00), +array (00:00:00), += (00:00:00), +new (00:00:00), +Array (00:00:00), +( (00:00:00), +count (00:00:00), +) (00:00:00), +; (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +count (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +array (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), += (00:00:00), +Math (00:00:00), +. (00:00:00), +random (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +const (00:00:00), +visualizer (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +array (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bar (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +createElement (00:00:00), +( (00:00:00), +" (00:00:00), +div (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +visualizer (00:00:00), +. (00:00:00), +appendChild (00:00:00), +( (00:00:00), +bar (00:00:00), +) (00:00:00), +; (00:00:00), +bar (00:00:00), +. (00:00:00), +classList (00:00:00), +. (00:00:00), +add (00:00:00), +( (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +bar (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +height (00:00:00), += (00:00:00), +array (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +* (00:00:00), +100 (00:00:00), ++ (00:00:00), +" (00:00:00), +% (00:00:00), +" (00:00:00), +; (00:00:00), +function (00:00:00), +bubbleSort (00:00:00), +( (00:00:00), +array (00:00:00), +) (00:00:00), +function (00:00:00), +updatebars (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bars (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementByClassName (00:00:00), +( (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +) (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +bars (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +height (00:00:00), += (00:00:00), +array (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +* (00:00:00), +100 (00:00:00), ++ (00:00:00), +" (00:00:00), +% (00:00:00), +" (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00), +async (00:00:00), +function (00:00:00), +bubbleSort (00:00:00), +( (00:00:00), +arr (00:00:00), +) (00:00:00), +{ (00:00:00), +do (00:00:00), +{ (00:00:00), +var (00:00:00), +swapped (00:00:00), += (00:00:00), +false (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +1 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +arr (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +if (00:00:00), +( (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +- (00:00:00), +1 (00:00:00), +] (00:00:00), +&gt; (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +aux (00:00:00), += (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +- (00:00:00), +1 (00:00:00), +] (00:00:00), +; (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +- (00:00:00), +1 (00:00:00), +] (00:00:00), += (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +; (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), += (00:00:00), +aux (00:00:00), +; (00:00:00), +swapped (00:00:00), += (00:00:00), +true (00:00:00), +; (00:00:00), +updateBars (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +await (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +100 (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00), +while (00:00:00), +( (00:00:00), +swapped (00:00:00), +) (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:17:21.139), -# (10:19:53.296), -vis (10:19:54.003), -- (10:19:54.226), -123456 (10:19:55.544), -{ (10:20:02.452), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +{ (00:00:00)</t>
+          <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:17:21.139) ~1.00, -# (10:19:53.296) ~1.00, -vis (10:19:54.003) ~1.00, -- (10:19:54.226) ~1.00, -123456 (10:19:55.544) ~1.00, -{ (10:20:02.452) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +{ (00:00:00)</t>
         </is>
       </c>
       <c r="Q12" t="n">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>-&lt; (10:12:43.632), -title (10:12:44.512), -&gt; (10:12:44.622), -Sorting (10:12:45.778), -Visualizer (10:12:47.677), -&lt; (10:12:47.904), -/ (10:12:48.260), -title (10:12:49.434), -&gt; (10:12:49.841), +&lt; (00:00:00), +title (00:00:00), +&gt; (00:00:00), +Sorting (00:00:00), +Visualizer (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +title (00:00:00), +&gt; (00:00:00)</t>
+          <t>-&lt; (10:12:43.632) ~1.00, -title (10:12:44.512) ~1.00, -&gt; (10:12:44.622) ~1.00, -Sorting (10:12:45.778) ~1.00, -Visualizer (10:12:47.677) ~1.00, -&lt; (10:12:47.904) ~1.00, -/ (10:12:48.260) ~1.00, -title (10:12:49.434) ~1.00, -&gt; (10:12:49.841) ~1.00, +&lt; (00:00:00), +title (00:00:00), +&gt; (00:00:00), +Sorting (00:00:00), +Visualizer (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +title (00:00:00), +&gt; (00:00:00)</t>
         </is>
       </c>
       <c r="O19" t="n">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:17:21.139), -# (10:19:53.296), -vis (10:19:54.003), -- (10:19:54.226), -123456 (10:19:55.544), -{ (10:20:02.452), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +{ (00:00:00)</t>
+          <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:17:21.139) ~1.00, -# (10:19:53.296) ~1.00, -vis (10:19:54.003) ~1.00, -- (10:19:54.226) ~1.00, -123456 (10:19:55.544) ~1.00, -{ (10:20:02.452) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +{ (00:00:00)</t>
         </is>
       </c>
       <c r="Q19" t="n">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>+bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -updateBars (11:12:30.664), -( (11:12:30.752), -) (11:12:30.906), -; (11:12:31.204), -await (11:13:47.348), -new (11:13:53.570), -Promise (11:13:54.982), -( (11:13:55.301), -resolve (11:13:59.055), -= (11:14:16.118), -&gt; (11:14:16.408), -setTimeout (11:14:18.857), -( (11:14:19.066), -resolve (11:14:23.324), -, (11:14:23.491), -100 (11:14:24.924), -) (11:14:31.103), -) (11:14:31.475), -; (11:14:32.118), +bubbleSort (00:00:00), +( (00:00:00), +array (00:00:00), +) (00:00:00), +; (00:00:00), +updateBars (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +await (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +100 (00:00:00), +) (00:00:00), +) (00:00:00)</t>
+          <t>+bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118) ~1.00, -( (11:08:34.128) ~1.00, -array (11:08:34.178) ~1.00, -) (11:08:34.188) ~1.00, -; (11:08:34.198) ~1.00, -updateBars (11:12:30.664) ~1.00, -( (11:12:30.752) ~1.00, -) (11:12:30.906) ~1.00, -; (11:12:31.204) ~1.00, -await (11:13:47.348) ~1.00, -new (11:13:53.570) ~1.00, -Promise (11:13:54.982) ~1.00, -( (11:13:55.301) ~1.00, -resolve (11:13:59.055) ~1.00, -= (11:14:16.118) ~1.00, -&gt; (11:14:16.408) ~1.00, -setTimeout (11:14:18.857) ~1.00, -( (11:14:19.066) ~1.00, -resolve (11:14:23.324) ~1.00, -, (11:14:23.491) ~1.00, -100 (11:14:24.924) ~1.00, -) (11:14:31.103) ~1.00, -) (11:14:31.475) ~1.00, -; (11:14:32.118), +bubbleSort (00:00:00), +( (00:00:00), +array (00:00:00), +) (00:00:00), +; (00:00:00), +updateBars (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +await (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +100 (00:00:00), +) (00:00:00), +) (00:00:00)</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>-Visualizer (10:12:47.677), +Visualiser (00:00:00)</t>
+          <t>-Visualizer (10:12:47.677) ~0.90, +Visualiser (00:00:00)</t>
         </is>
       </c>
       <c r="O21" t="n">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:17:21.139), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), -0px (10:48:03.827), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +0 (00:00:00)</t>
+          <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:17:21.139) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, -0px (10:48:03.827) ~0.33, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +0 (00:00:00)</t>
         </is>
       </c>
       <c r="Q21" t="n">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>-getElementsByClassName (11:09:28.891), -bars (11:09:58.993), -100 (11:14:24.924), +querySelectorAll (00:00:00), +. (00:00:00), +array (00:00:00), +10 (00:00:00)</t>
+          <t>-getElementsByClassName (11:09:28.891) ~0.18, -bars (11:09:58.993) ~0.20, -100 (11:14:24.924) ~0.67, +querySelectorAll (00:00:00), +. (00:00:00), +array (00:00:00), +10 (00:00:00)</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:17:21.139), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), -. (10:43:24.242), -bar (10:43:31.288), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +. (00:00:00), +bar (00:00:00)</t>
+          <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:17:21.139) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, -. (10:43:24.242) ~1.00, -bar (10:43:31.288) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +. (00:00:00), +bar (00:00:00)</t>
         </is>
       </c>
       <c r="Q24" t="n">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:17:21.139), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+          <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:17:21.139) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q25" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>-length (10:38:57.372), -classList (10:42:32.670), -length (10:59:32.061), -getElementsByClassName (11:09:28.891), -length (11:10:00.426), -Promise (11:13:54.982), +lenght (00:00:00), +ClassList (00:00:00), +getElementByClassName (00:00:00), +lenght (00:00:00), +lenght (00:00:00), +promise (00:00:00)</t>
+          <t>-length (10:38:57.372) ~0.67, -classList (10:42:32.670) ~0.89, -length (10:59:32.061) ~0.67, -getElementsByClassName (11:09:28.891) ~0.95, -length (11:10:00.426) ~0.67, -Promise (11:13:54.982) ~0.86, +lenght (00:00:00), +ClassList (00:00:00), +getElementByClassName (00:00:00), +lenght (00:00:00), +lenght (00:00:00), +promise (00:00:00)</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:17:21.139), -# (10:19:53.296), -vis (10:19:54.003), -- (10:19:54.226), -123456 (10:19:55.544), -{ (10:20:02.452), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +{ (00:00:00)</t>
+          <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:17:21.139) ~1.00, -# (10:19:53.296) ~1.00, -vis (10:19:54.003) ~1.00, -- (10:19:54.226) ~1.00, -123456 (10:19:55.544) ~1.00, -{ (10:20:02.452) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +{ (00:00:00)</t>
         </is>
       </c>
       <c r="Q30" t="n">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>-function (10:57:37.492), -bubbleSort (10:57:42.836), -( (10:57:43.053), -arr (10:57:49.140), -) (10:57:49.861), -{ (10:57:54.715), -async (11:15:16.100), +async (00:00:00), +function (00:00:00), +bubbleSort (00:00:00), +( (00:00:00), +arr (00:00:00), +) (00:00:00), +{ (00:00:00)</t>
+          <t>-function (10:57:37.492) ~1.00, -bubbleSort (10:57:42.836) ~1.00, -( (10:57:43.053) ~1.00, -arr (10:57:49.140) ~1.00, -) (10:57:49.861) ~1.00, -{ (10:57:54.715) ~1.00, -async (11:15:16.100) ~1.00, +async (00:00:00), +function (00:00:00), +bubbleSort (00:00:00), +( (00:00:00), +arr (00:00:00), +) (00:00:00), +{ (00:00:00)</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>-Sorting (10:12:45.778), +sorting (00:00:00)</t>
+          <t>-Sorting (10:12:45.778) ~0.86, +sorting (00:00:00)</t>
         </is>
       </c>
       <c r="O31" t="n">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:17:21.139), -# (10:19:53.296), -vis (10:19:54.003), -- (10:19:54.226), -123456 (10:19:55.544), -{ (10:20:02.452), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), -. (10:43:24.242), -bar (10:43:31.288), -{ (10:43:32.996), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +{ (00:00:00), +. (00:00:00), +bar (00:00:00), +{ (00:00:00)</t>
+          <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:17:21.139) ~1.00, -# (10:19:53.296) ~1.00, -vis (10:19:54.003) ~1.00, -- (10:19:54.226) ~1.00, -123456 (10:19:55.544) ~1.00, -{ (10:20:02.452) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, -. (10:43:24.242) ~1.00, -bar (10:43:31.288) ~1.00, -{ (10:43:32.996) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +{ (00:00:00), +. (00:00:00), +bar (00:00:00), +{ (00:00:00)</t>
         </is>
       </c>
       <c r="Q31" t="n">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>-for (10:59:26.374), -( (10:59:26.727), -let (10:59:27.295), -i (10:59:27.677), -= (10:59:27.952), -1 (10:59:28.458), -; (10:59:28.738), -i (10:59:29.253), -&lt; (10:59:29.652), -arr (10:59:30.525), -. (10:59:30.766), -length (10:59:32.061), -; (10:59:32.305), -i (10:59:32.661), -+ (10:59:32.869), -+ (10:59:33.126), -) (10:59:33.350), -{ (10:59:35.506), -if (10:59:41.288), -( (10:59:41.708), -arr (10:59:42.652), -[ (10:59:42.917), -i (10:59:43.246), -- (10:59:44.058), -1 (10:59:44.656), -] (10:59:44.854), -&gt; (10:59:45.546), -arr (10:59:46.616), -[ (10:59:46.969), -i (10:59:47.212), -] (10:59:47.751), -) (10:59:48.230), -{ (10:59:49.302), -const (11:00:57.203), -aux (11:00:58.458), -= (11:01:01.660), -arr (11:01:02.684), -[ (11:01:02.941), -i (11:01:03.128), -- (11:01:03.607), -1 (11:01:04.198), -] (11:01:04.697), -; (11:01:05.017), -arr (11:01:06.389), -[ (11:01:06.650), -i (11:01:06.835), -- (11:01:07.252), -1 (11:01:07.757), -] (11:01:08.184), -= (11:01:08.961), -arr (11:01:09.861), -[ (11:01:10.052), -i (11:01:10.368), -] (11:01:10.513), -; (11:01:10.683), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +arr (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +if (00:00:00), +( (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +- (00:00:00), +1 (00:00:00), +] (00:00:00), +&gt; (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +aux (00:00:00), += (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +- (00:00:00), +1 (00:00:00), +] (00:00:00), +; (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +- (00:00:00), +1 (00:00:00), +] (00:00:00), += (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +; (00:00:00)</t>
+          <t>-for (10:59:26.374) ~1.00, -( (10:59:26.727) ~1.00, -let (10:59:27.295) ~1.00, -i (10:59:27.677) ~1.00, -= (10:59:27.952) ~1.00, -1 (10:59:28.458) ~0.00, -; (10:59:28.738) ~1.00, -i (10:59:29.253) ~1.00, -&lt; (10:59:29.652) ~1.00, -arr (10:59:30.525) ~1.00, -. (10:59:30.766) ~1.00, -length (10:59:32.061) ~1.00, -; (10:59:32.305) ~1.00, -i (10:59:32.661) ~1.00, -+ (10:59:32.869) ~1.00, -+ (10:59:33.126) ~1.00, -) (10:59:33.350) ~1.00, -{ (10:59:35.506) ~1.00, -if (10:59:41.288) ~1.00, -( (10:59:41.708) ~1.00, -arr (10:59:42.652) ~1.00, -[ (10:59:42.917) ~1.00, -i (10:59:43.246) ~1.00, -- (10:59:44.058) ~1.00, -1 (10:59:44.656) ~1.00, -] (10:59:44.854) ~1.00, -&gt; (10:59:45.546) ~1.00, -arr (10:59:46.616) ~1.00, -[ (10:59:46.969) ~1.00, -i (10:59:47.212) ~1.00, -] (10:59:47.751) ~1.00, -) (10:59:48.230) ~1.00, -{ (10:59:49.302) ~1.00, -const (11:00:57.203) ~1.00, -aux (11:00:58.458) ~1.00, -= (11:01:01.660) ~1.00, -arr (11:01:02.684) ~1.00, -[ (11:01:02.941) ~1.00, -i (11:01:03.128) ~1.00, -- (11:01:03.607) ~1.00, -1 (11:01:04.198) ~1.00, -] (11:01:04.697) ~1.00, -; (11:01:05.017) ~1.00, -arr (11:01:06.389) ~1.00, -[ (11:01:06.650) ~1.00, -i (11:01:06.835) ~1.00, -- (11:01:07.252) ~1.00, -1 (11:01:07.757) ~1.00, -] (11:01:08.184) ~1.00, -= (11:01:08.961) ~1.00, -arr (11:01:09.861) ~1.00, -[ (11:01:10.052) ~1.00, -i (11:01:10.368) ~1.00, -] (11:01:10.513) ~1.00, -; (11:01:10.683) ~1.00, +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +arr (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +if (00:00:00), +( (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +- (00:00:00), +1 (00:00:00), +] (00:00:00), +&gt; (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +aux (00:00:00), += (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +- (00:00:00), +1 (00:00:00), +] (00:00:00), +; (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +- (00:00:00), +1 (00:00:00), +] (00:00:00), += (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>-Sorting (10:13:13.802), +/ (00:00:00), +sorting (00:00:00)</t>
+          <t>-Sorting (10:13:13.802) ~0.86, +/ (00:00:00), +sorting (00:00:00)</t>
         </is>
       </c>
       <c r="O36" t="n">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>-center (10:17:20.707), -# (10:19:53.296), -vis (10:19:54.003), -- (10:19:54.226), -123456 (10:19:55.544), -{ (10:20:02.452), -height (10:20:07.891), -200px (10:20:09.051), -flex (10:21:58.800), -direction (10:22:01.758), -column (10:22:03.223), -align (10:24:12.446), -items (10:24:13.500), -. (10:43:24.242), -bar (10:43:31.288), -{ (10:43:32.996), -width (10:43:37.644), -7px (10:43:39.527), -height (10:43:47.504), -100 (10:43:48.485), -% (10:43:48.586), -background (10:44:24.231), -- (10:44:24.311), -color (10:44:25.031), -: (10:44:25.154), -black (10:44:26.271), -; (10:44:26.592), +200px* (10:50:08.740), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +red* (10:50:09.332), +align (00:00:00), +items (00:00:00), +center (00:00:00), +flex (00:00:00), +direction (00:00:00), +column (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +{ (00:00:00), +height (00:00:00), +: (00:00:00), +; (00:00:00), +. (00:00:00), +bar (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +7px (00:00:00), +; (00:00:00), +height (00:00:00), +100 (00:00:00), +% (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +black (00:00:00)</t>
+          <t>-center (10:17:20.707) ~0.17, -# (10:19:53.296) ~1.00, -vis (10:19:54.003) ~1.00, -- (10:19:54.226) ~1.00, -123456 (10:19:55.544) ~1.00, -{ (10:20:02.452) ~1.00, -height (10:20:07.891) ~1.00, -200px (10:20:09.051) ~0.00, -flex (10:21:58.800) ~0.20, -direction (10:22:01.758) ~0.22, -column (10:22:03.223) ~0.17, -align (10:24:12.446) ~0.20, -items (10:24:13.500) ~0.22, -. (10:43:24.242) ~1.00, -bar (10:43:31.288) ~1.00, -{ (10:43:32.996) ~1.00, -width (10:43:37.644) ~1.00, -7px (10:43:39.527) ~1.00, -height (10:43:47.504) ~1.00, -100 (10:43:48.485) ~1.00, -% (10:43:48.586) ~1.00, -background (10:44:24.231) ~1.00, -- (10:44:24.311) ~1.00, -color (10:44:25.031) ~1.00, -: (10:44:25.154), -black (10:44:26.271) ~1.00, -; (10:44:26.592), +200px* (10:50:08.740), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +red* (10:50:09.332), +align (00:00:00), +items (00:00:00), +center (00:00:00), +flex (00:00:00), +direction (00:00:00), +column (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +{ (00:00:00), +height (00:00:00), +: (00:00:00), +; (00:00:00), +. (00:00:00), +bar (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +7px (00:00:00), +; (00:00:00), +height (00:00:00), +100 (00:00:00), +% (00:00:00), +background (00:00:00), +- (00:00:00), +color (00:00:00), +black (00:00:00)</t>
         </is>
       </c>
       <c r="Q36" t="n">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>-50 (10:27:50.527), -. (10:31:30.292), -. (10:38:55.684), -. (10:40:28.151), -arr (11:01:09.861), -; (11:01:10.683), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -array (11:08:34.178), -function (11:08:36.630), -updateBars (11:08:38.342), -( (11:08:38.511), -) (11:08:38.687), -{ (11:08:39.319), -const (11:09:21.850), -bars (11:09:22.876), -= (11:09:23.405), -document (11:09:24.920), -. (11:09:25.072), -getElementsByClassName (11:09:28.891), -( (11:09:28.949), -" (11:09:29.056), -bar (11:09:29.764), -" (11:09:29.897), -) (11:09:29.998), -; (11:09:30.476), -for (11:09:55.616), -( (11:09:55.956), -let (11:09:56.455), -i (11:09:56.677), -= (11:09:57.008), -0 (11:09:57.490), -; (11:09:57.512), -i (11:09:57.854), -&lt; (11:09:58.223), -bars (11:09:58.993), -. (11:09:59.214), -length (11:10:00.426), -; (11:10:00.634), -i (11:10:01.376), -+ (11:10:01.600), -+ (11:10:01.789), -) (11:10:01.880), -{ (11:10:02.609), -bars (11:10:05.954), -[ (11:10:06.083), -i (11:10:06.207), -] (11:10:06.517), -. (11:10:06.753), -style (11:10:08.322), -. (11:10:08.474), -height (11:10:09.606), -= (11:10:12.868), -array (11:10:13.726), -[ (11:10:13.999), -i (11:10:14.138), -] (11:10:14.279), -* (11:10:14.846), -100 (11:10:15.517), -+ (11:10:16.137), -" (11:10:16.502), -% (11:10:16.625), -" (11:10:16.705), -; (11:10:17.104), -Promise (11:13:54.982), +20 (00:00:00), +, (00:00:00), +bubblesort (00:00:00), +, (00:00:00), +, (00:00:00), +function (00:00:00), +updateBars (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bars (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementsByClassName (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +bars (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +height (00:00:00), += (00:00:00), +array (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +* (00:00:00), +100 (00:00:00), ++ (00:00:00), +" (00:00:00), +% (00:00:00), +" (00:00:00), +aee (00:00:00), +promise (00:00:00)</t>
+          <t>-50 (10:27:50.527) ~0.50, -. (10:31:30.292) ~0.00, -. (10:38:55.684) ~0.00, -. (10:40:28.151) ~0.00, -arr (11:01:09.861) ~0.33, -; (11:01:10.683), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -array (11:08:34.178), -function (11:08:36.630) ~1.00, -updateBars (11:08:38.342) ~1.00, -( (11:08:38.511) ~1.00, -) (11:08:38.687) ~1.00, -{ (11:08:39.319) ~1.00, -const (11:09:21.850) ~1.00, -bars (11:09:22.876) ~1.00, -= (11:09:23.405) ~1.00, -document (11:09:24.920) ~1.00, -. (11:09:25.072) ~1.00, -getElementsByClassName (11:09:28.891) ~1.00, -( (11:09:28.949), -" (11:09:29.056) ~1.00, -bar (11:09:29.764) ~1.00, -" (11:09:29.897) ~1.00, -) (11:09:29.998), -; (11:09:30.476), -for (11:09:55.616) ~1.00, -( (11:09:55.956) ~1.00, -let (11:09:56.455) ~1.00, -i (11:09:56.677) ~1.00, -= (11:09:57.008) ~1.00, -0 (11:09:57.490) ~1.00, -; (11:09:57.512) ~1.00, -i (11:09:57.854) ~1.00, -&lt; (11:09:58.223) ~1.00, -bars (11:09:58.993) ~1.00, -. (11:09:59.214) ~1.00, -length (11:10:00.426) ~1.00, -; (11:10:00.634) ~1.00, -i (11:10:01.376) ~1.00, -+ (11:10:01.600) ~1.00, -+ (11:10:01.789) ~1.00, -) (11:10:01.880) ~1.00, -{ (11:10:02.609) ~1.00, -bars (11:10:05.954) ~1.00, -[ (11:10:06.083) ~1.00, -i (11:10:06.207) ~1.00, -] (11:10:06.517) ~1.00, -. (11:10:06.753) ~1.00, -style (11:10:08.322) ~1.00, -. (11:10:08.474) ~1.00, -height (11:10:09.606) ~1.00, -= (11:10:12.868) ~1.00, -array (11:10:13.726) ~1.00, -[ (11:10:13.999) ~1.00, -i (11:10:14.138) ~1.00, -] (11:10:14.279) ~1.00, -* (11:10:14.846) ~1.00, -100 (11:10:15.517) ~1.00, -+ (11:10:16.137) ~1.00, -" (11:10:16.502) ~1.00, -% (11:10:16.625) ~1.00, -" (11:10:16.705) ~1.00, -; (11:10:17.104), -Promise (11:13:54.982) ~0.86, +20 (00:00:00), +, (00:00:00), +bubblesort (00:00:00), +, (00:00:00), +, (00:00:00), +function (00:00:00), +updateBars (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bars (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementsByClassName (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +bars (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +height (00:00:00), += (00:00:00), +array (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +* (00:00:00), +100 (00:00:00), ++ (00:00:00), +" (00:00:00), +% (00:00:00), +" (00:00:00), +aee (00:00:00), +promise (00:00:00)</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -3373,7 +3373,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>-# (10:19:53.296), -vis (10:19:54.003), -- (10:19:54.226), -123456 (10:19:55.544), -{ (10:20:02.452), -height (10:20:07.891), -: (10:20:07.983), -200px (10:20:09.051), -; (10:20:09.451), -flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223), -; (10:22:03.455), +;* (10:50:09.333), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +coloumn (00:00:00), +; (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +{ (00:00:00), +height (00:00:00), +: (00:00:00), +200px (00:00:00)</t>
+          <t>-# (10:19:53.296) ~1.00, -vis (10:19:54.003) ~1.00, -- (10:19:54.226) ~1.00, -123456 (10:19:55.544) ~1.00, -{ (10:20:02.452) ~1.00, -height (10:20:07.891) ~1.00, -: (10:20:07.983) ~1.00, -200px (10:20:09.051) ~1.00, -; (10:20:09.451), -flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758) ~1.00, -: (10:22:01.952), -column (10:22:03.223) ~0.86, -; (10:22:03.455) ~1.00, +;* (10:50:09.333), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +coloumn (00:00:00), +; (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +{ (00:00:00), +height (00:00:00), +: (00:00:00), +200px (00:00:00)</t>
         </is>
       </c>
       <c r="Q42" t="n">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>-let (10:38:51.733), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -let (11:09:56.455), -bars (11:09:58.993), -bars (11:10:05.954), -[ (11:10:06.083), -i (11:10:06.207), -] (11:10:06.517), -. (11:10:06.753), -style (11:10:08.322), -. (11:10:08.474), -height (11:10:09.606), -= (11:10:12.868), -array (11:10:13.726), -[ (11:10:13.999), -i (11:10:14.138), -] (11:10:14.279), -* (11:10:14.846), -100 (11:10:15.517), -+ (11:10:16.137), -" (11:10:16.502), -% (11:10:16.625), -" (11:10:16.705), -; (11:10:17.104), -updateBars (11:12:30.664), -( (11:12:30.752), -) (11:12:30.906), -; (11:12:31.204), -await (11:13:47.348), -new (11:13:53.570), -Promise (11:13:54.982), -( (11:13:55.301), -resolve (11:13:59.055), -= (11:14:16.118), -&gt; (11:14:16.408), -setTimeout (11:14:18.857), -( (11:14:19.066), -resolve (11:14:23.324), -, (11:14:23.491), -100 (11:14:24.924), -) (11:14:31.103), -) (11:14:31.475), -; (11:14:32.118), -async (11:15:16.100), +array (00:00:00)</t>
+          <t>-let (10:38:51.733), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -let (11:09:56.455), -bars (11:09:58.993) ~0.20, -bars (11:10:05.954), -[ (11:10:06.083), -i (11:10:06.207), -] (11:10:06.517), -. (11:10:06.753), -style (11:10:08.322), -. (11:10:08.474), -height (11:10:09.606), -= (11:10:12.868), -array (11:10:13.726), -[ (11:10:13.999), -i (11:10:14.138), -] (11:10:14.279), -* (11:10:14.846), -100 (11:10:15.517), -+ (11:10:16.137), -" (11:10:16.502), -% (11:10:16.625), -" (11:10:16.705), -; (11:10:17.104), -updateBars (11:12:30.664), -( (11:12:30.752), -) (11:12:30.906), -; (11:12:31.204), -await (11:13:47.348), -new (11:13:53.570), -Promise (11:13:54.982), -( (11:13:55.301), -resolve (11:13:59.055), -= (11:14:16.118), -&gt; (11:14:16.408), -setTimeout (11:14:18.857), -( (11:14:19.066), -resolve (11:14:23.324), -, (11:14:23.491), -100 (11:14:24.924), -) (11:14:31.103), -) (11:14:31.475), -; (11:14:32.118), -async (11:15:16.100), +array (00:00:00)</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:17:21.139), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), -. (10:43:24.242), -bar (10:43:31.288), -{ (10:43:32.996), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +. (00:00:00), +bar (00:00:00), +{ (00:00:00)</t>
+          <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:17:21.139) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, -. (10:43:24.242) ~1.00, -bar (10:43:31.288) ~1.00, -{ (10:43:32.996) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +. (00:00:00), +bar (00:00:00), +{ (00:00:00)</t>
         </is>
       </c>
       <c r="Q45" t="n">
@@ -3597,7 +3597,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:17:21.139), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), -display (10:47:38.305), -flex (10:47:39.551), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +red* (10:50:09.332), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+          <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:17:21.139) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, -display (10:47:38.305), -flex (10:47:39.551), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +red* (10:50:09.332), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q46" t="n">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>-title (10:12:49.434), -Visualizer (10:13:16.993), +tittle (00:00:00), +visualizer (00:00:00)</t>
+          <t>-title (10:12:49.434) ~0.83, -Visualizer (10:13:16.993) ~0.90, +tittle (00:00:00), +visualizer (00:00:00)</t>
         </is>
       </c>
       <c r="O48" t="n">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:17:21.139), -# (10:19:53.296), -vis (10:19:54.003), -- (10:19:54.226), -123456 (10:19:55.544), -{ (10:20:02.452), -height (10:20:07.891), -: (10:20:07.983), -200px (10:20:09.051), -; (10:20:09.451), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), -display (10:47:38.305), -: (10:47:38.437), -flex (10:47:39.551), -; (10:47:39.811), -margin (10:48:02.482), -: (10:48:02.549), -0px (10:48:03.827), -1px (10:48:07.241), -; (10:48:07.569), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), -align (10:57:30.272), -- (10:57:30.282), -items (10:57:30.332), -: (10:57:30.342), -flex (10:57:30.392), -- (10:57:30.402), -end (10:57:30.432), -; (10:57:30.442), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +{ (00:00:00), +height (00:00:00), +: (00:00:00), +200px (00:00:00), +; (00:00:00)</t>
+          <t>-: (10:17:19.374), -center (10:17:20.707) ~1.00, -; (10:17:21.139) ~1.00, -# (10:19:53.296) ~1.00, -vis (10:19:54.003) ~1.00, -- (10:19:54.226) ~1.00, -123456 (10:19:55.544) ~1.00, -{ (10:20:02.452) ~1.00, -height (10:20:07.891) ~1.00, -: (10:20:07.983), -200px (10:20:09.051), -; (10:20:09.451), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), -display (10:47:38.305), -: (10:47:38.437) ~1.00, -flex (10:47:39.551) ~0.20, -; (10:47:39.811) ~1.00, -margin (10:48:02.482), -: (10:48:02.549), -0px (10:48:03.827), -1px (10:48:07.241), -; (10:48:07.569), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), -align (10:57:30.272) ~1.00, -- (10:57:30.282) ~1.00, -items (10:57:30.332) ~1.00, -: (10:57:30.342) ~1.00, -flex (10:57:30.392), -- (10:57:30.402), -end (10:57:30.432), -; (10:57:30.442), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +{ (00:00:00), +height (00:00:00), +: (00:00:00), +200px (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q48" t="n">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>-array (10:28:45.898), -const (10:37:42.386), -visualizer (10:37:44.631), -= (10:37:45.082), -document (10:37:47.323), -. (10:37:47.760), -getElementById (10:38:03.158), -" (10:38:19.019), -vis (10:38:19.926), -- (10:38:20.217), -123456 (10:38:22.251), -" (10:38:22.629), +bubbleSort* (11:08:31.581), -array (11:08:34.178), -getElementsByClassName (11:09:28.891), +arry (00:00:00), +arry (00:00:00), +const (00:00:00), +visualizer (00:00:00), += (00:00:00), +documnet (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +arry (00:00:00), +getElementByClassName (00:00:00)</t>
+          <t>-array (10:28:45.898) ~0.80, -const (10:37:42.386) ~1.00, -visualizer (10:37:44.631) ~1.00, -= (10:37:45.082) ~1.00, -document (10:37:47.323) ~0.75, -. (10:37:47.760) ~1.00, -getElementById (10:38:03.158) ~1.00, -" (10:38:19.019) ~1.00, -vis (10:38:19.926) ~1.00, -- (10:38:20.217) ~1.00, -123456 (10:38:22.251) ~1.00, -" (10:38:22.629) ~1.00, +bubbleSort* (11:08:31.581), -array (11:08:34.178) ~0.80, -getElementsByClassName (11:09:28.891) ~0.95, +arry (00:00:00), +arry (00:00:00), +const (00:00:00), +visualizer (00:00:00), += (00:00:00), +documnet (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +arry (00:00:00), +getElementByClassName (00:00:00)</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>-html (10:12:23.484), +htm (00:00:00)</t>
+          <t>-html (10:12:23.484) ~0.75, +htm (00:00:00)</t>
         </is>
       </c>
       <c r="O50" t="n">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:17:21.139), -# (10:19:53.296), -vis (10:19:54.003), -- (10:19:54.226), -123456 (10:19:55.544), -{ (10:20:02.452), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), -. (10:43:24.242), -bar (10:43:31.288), -{ (10:43:32.996), -- (10:57:30.402), -end (10:57:30.432), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +{ (00:00:00), +. (00:00:00), +bar (00:00:00), +{ (00:00:00)</t>
+          <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:17:21.139) ~1.00, -# (10:19:53.296) ~1.00, -vis (10:19:54.003) ~1.00, -- (10:19:54.226) ~1.00, -123456 (10:19:55.544) ~1.00, -{ (10:20:02.452) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, -. (10:43:24.242) ~1.00, -bar (10:43:31.288) ~1.00, -{ (10:43:32.996) ~1.00, -- (10:57:30.402), -end (10:57:30.432), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +{ (00:00:00), +. (00:00:00), +bar (00:00:00), +{ (00:00:00)</t>
         </is>
       </c>
       <c r="Q50" t="n">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>-for (10:30:13.868), -( (10:30:14.352), -let (10:30:15.164), -i (10:30:15.672), -= (10:30:16.329), -0 (10:30:16.771), -; (10:30:17.011), -i (10:30:17.443), -&lt; (10:30:18.073), -count (10:30:20.284), -; (10:30:20.584), -i (10:30:47.713), -+ (10:30:48.171), -+ (10:30:48.660), -) (10:30:49.210), -{ (10:31:12.723), -function (10:57:37.492), -bubbleSort (10:57:42.836), -( (10:57:43.053), -arr (10:57:49.140), -) (10:57:49.861), -{ (10:57:54.715), -bubbleSort (11:08:34.118), -array (11:08:34.178), -function (11:08:36.630), -updateBars (11:08:38.342), -( (11:08:38.511), -) (11:08:38.687), -{ (11:08:39.319), -const (11:09:21.850), -bars (11:09:22.876), -= (11:09:23.405), -document (11:09:24.920), -. (11:09:25.072), -getElementsByClassName (11:09:28.891), -( (11:09:28.949), -" (11:09:29.056), -bar (11:09:29.764), -" (11:09:29.897), -) (11:09:29.998), -; (11:09:30.476), -for (11:09:55.616), -( (11:09:55.956), -let (11:09:56.455), -i (11:09:56.677), -= (11:09:57.008), -0 (11:09:57.490), -; (11:09:57.512), -i (11:09:57.854), -&lt; (11:09:58.223), -bars (11:09:58.993), -. (11:09:59.214), -length (11:10:00.426), -; (11:10:00.634), -i (11:10:01.376), -+ (11:10:01.600), -+ (11:10:01.789), -) (11:10:01.880), -{ (11:10:02.609), -bars (11:10:05.954), -[ (11:10:06.083), -i (11:10:06.207), -] (11:10:06.517), -. (11:10:06.753), -style (11:10:08.322), -. (11:10:08.474), -height (11:10:09.606), -= (11:10:12.868), -array (11:10:13.726), -[ (11:10:13.999), -i (11:10:14.138), -] (11:10:14.279), -* (11:10:14.846), -100 (11:10:15.517), -+ (11:10:16.137), -" (11:10:16.502), -% (11:10:16.625), -" (11:10:16.705), -; (11:10:17.104), -100 (11:14:24.924), -async (11:15:16.100), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +count (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +function (00:00:00), +updateBars (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bars (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementsByClassname (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +bars (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +height (00:00:00), += (00:00:00), +array (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +* (00:00:00), +100 (00:00:00), ++ (00:00:00), +" (00:00:00), +% (00:00:00), +" (00:00:00), +; (00:00:00), +async (00:00:00), +function (00:00:00), +bubbleSort (00:00:00), +( (00:00:00), +arr (00:00:00), +) (00:00:00), +{ (00:00:00), +10 (00:00:00)</t>
+          <t>-for (10:30:13.868) ~1.00, -( (10:30:14.352) ~1.00, -let (10:30:15.164) ~1.00, -i (10:30:15.672) ~1.00, -= (10:30:16.329) ~1.00, -0 (10:30:16.771) ~1.00, -; (10:30:17.011) ~1.00, -i (10:30:17.443) ~1.00, -&lt; (10:30:18.073) ~1.00, -count (10:30:20.284) ~1.00, -; (10:30:20.584) ~1.00, -i (10:30:47.713) ~1.00, -+ (10:30:48.171) ~1.00, -+ (10:30:48.660) ~1.00, -) (10:30:49.210) ~1.00, -{ (10:31:12.723) ~1.00, -function (10:57:37.492) ~1.00, -bubbleSort (10:57:42.836) ~1.00, -( (10:57:43.053) ~1.00, -arr (10:57:49.140) ~1.00, -) (10:57:49.861) ~1.00, -{ (10:57:54.715) ~1.00, -bubbleSort (11:08:34.118), -array (11:08:34.178), -function (11:08:36.630) ~1.00, -updateBars (11:08:38.342) ~1.00, -( (11:08:38.511) ~1.00, -) (11:08:38.687) ~1.00, -{ (11:08:39.319) ~1.00, -const (11:09:21.850) ~1.00, -bars (11:09:22.876) ~1.00, -= (11:09:23.405) ~1.00, -document (11:09:24.920) ~1.00, -. (11:09:25.072) ~1.00, -getElementsByClassName (11:09:28.891) ~0.95, -( (11:09:28.949), -" (11:09:29.056) ~1.00, -bar (11:09:29.764) ~1.00, -" (11:09:29.897) ~1.00, -) (11:09:29.998), -; (11:09:30.476), -for (11:09:55.616) ~1.00, -( (11:09:55.956) ~1.00, -let (11:09:56.455) ~1.00, -i (11:09:56.677) ~1.00, -= (11:09:57.008) ~1.00, -0 (11:09:57.490) ~1.00, -; (11:09:57.512) ~1.00, -i (11:09:57.854) ~1.00, -&lt; (11:09:58.223) ~1.00, -bars (11:09:58.993) ~1.00, -. (11:09:59.214) ~1.00, -length (11:10:00.426) ~1.00, -; (11:10:00.634) ~1.00, -i (11:10:01.376) ~1.00, -+ (11:10:01.600) ~1.00, -+ (11:10:01.789) ~1.00, -) (11:10:01.880) ~1.00, -{ (11:10:02.609) ~1.00, -bars (11:10:05.954) ~1.00, -[ (11:10:06.083) ~1.00, -i (11:10:06.207) ~1.00, -] (11:10:06.517) ~1.00, -. (11:10:06.753) ~1.00, -style (11:10:08.322) ~1.00, -. (11:10:08.474) ~1.00, -height (11:10:09.606) ~1.00, -= (11:10:12.868) ~1.00, -array (11:10:13.726) ~1.00, -[ (11:10:13.999) ~1.00, -i (11:10:14.138) ~1.00, -] (11:10:14.279) ~1.00, -* (11:10:14.846) ~1.00, -100 (11:10:15.517) ~1.00, -+ (11:10:16.137) ~1.00, -" (11:10:16.502) ~1.00, -% (11:10:16.625) ~1.00, -" (11:10:16.705) ~1.00, -; (11:10:17.104) ~1.00, -100 (11:14:24.924) ~0.67, -async (11:15:16.100) ~1.00, +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +count (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +function (00:00:00), +updateBars (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bars (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +getElementsByClassname (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +bars (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +height (00:00:00), += (00:00:00), +array (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +* (00:00:00), +100 (00:00:00), ++ (00:00:00), +" (00:00:00), +% (00:00:00), +" (00:00:00), +; (00:00:00), +async (00:00:00), +function (00:00:00), +bubbleSort (00:00:00), +( (00:00:00), +arr (00:00:00), +) (00:00:00), +{ (00:00:00), +10 (00:00:00)</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:17:21.139), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+          <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:17:21.139) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q51" t="n">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>-&lt; (10:12:43.632), -title (10:12:44.512), -&gt; (10:12:44.622), -&lt; (10:12:47.904), -/ (10:12:48.260), -title (10:12:49.434), -&gt; (10:12:49.841), -Sorting (10:13:13.802), -Visualizer (10:13:16.993), -&lt; (10:13:17.335), -/ (10:13:17.789), -h1 (10:13:18.123), -&gt; (10:13:18.254), -&lt; (10:18:29.900), -div (10:18:30.558), -id (10:18:31.498), -= (10:18:31.631), -" (10:18:33.349), -vis (10:18:34.420), -- (10:18:37.062), -123456 (10:18:40.665), -" (10:18:40.947), -&gt; (10:18:43.208), -&lt; (10:18:44.230), -/ (10:18:44.552), -div (10:18:45.086), -&gt; (10:18:45.251), +Sorting (00:00:00), +Visualizer (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +h1 (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
+          <t>-&lt; (10:12:43.632), -title (10:12:44.512), -&gt; (10:12:44.622), -&lt; (10:12:47.904), -/ (10:12:48.260), -title (10:12:49.434), -&gt; (10:12:49.841), -Sorting (10:13:13.802) ~1.00, -Visualizer (10:13:16.993) ~1.00, -&lt; (10:13:17.335) ~1.00, -/ (10:13:17.789) ~1.00, -h1 (10:13:18.123) ~1.00, -&gt; (10:13:18.254) ~1.00, -&lt; (10:18:29.900) ~1.00, -div (10:18:30.558) ~1.00, -id (10:18:31.498) ~1.00, -= (10:18:31.631) ~1.00, -" (10:18:33.349) ~1.00, -vis (10:18:34.420) ~1.00, -- (10:18:37.062) ~1.00, -123456 (10:18:40.665) ~1.00, -" (10:18:40.947) ~1.00, -&gt; (10:18:43.208) ~1.00, -&lt; (10:18:44.230) ~1.00, -/ (10:18:44.552) ~1.00, -div (10:18:45.086) ~1.00, -&gt; (10:18:45.251) ~1.00, +Sorting (00:00:00), +Visualizer (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +h1 (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +div (00:00:00), +id (00:00:00), += (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +" (00:00:00), +&gt; (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +div (00:00:00), +&gt; (00:00:00)</t>
         </is>
       </c>
       <c r="O56" t="n">
@@ -4115,7 +4115,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:17:21.139), -# (10:19:53.296), -vis (10:19:54.003), -- (10:19:54.226), -123456 (10:19:55.544), -{ (10:20:02.452), -height (10:20:07.891), -: (10:20:07.983), -200px (10:20:09.051), -; (10:20:09.451), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), -. (10:43:24.242), -bar (10:43:31.288), -{ (10:43:32.996), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +{ (00:00:00), +height (00:00:00), +: (00:00:00), +200px (00:00:00), +; (00:00:00), +. (00:00:00), +bar (00:00:00), +{ (00:00:00)</t>
+          <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:17:21.139) ~1.00, -# (10:19:53.296) ~1.00, -vis (10:19:54.003) ~1.00, -- (10:19:54.226) ~1.00, -123456 (10:19:55.544) ~1.00, -{ (10:20:02.452) ~1.00, -height (10:20:07.891) ~1.00, -: (10:20:07.983) ~1.00, -200px (10:20:09.051) ~1.00, -; (10:20:09.451) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, -. (10:43:24.242) ~1.00, -bar (10:43:31.288) ~1.00, -{ (10:43:32.996) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +{ (00:00:00), +height (00:00:00), +: (00:00:00), +200px (00:00:00), +; (00:00:00), +. (00:00:00), +bar (00:00:00), +{ (00:00:00)</t>
         </is>
       </c>
       <c r="Q56" t="n">
@@ -4123,7 +4123,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>-; (10:50:48.660), -100 (11:14:24.924), +10 (00:00:00)</t>
+          <t>-; (10:50:48.660), -100 (11:14:24.924) ~0.67, +10 (00:00:00)</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:17:21.139), -# (10:19:53.296), -vis (10:19:54.003), -- (10:19:54.226), -123456 (10:19:55.544), -{ (10:20:02.452), -height (10:20:07.891), -: (10:20:07.983), -200px (10:20:09.051), -; (10:20:09.451), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), -align (10:57:30.272), -- (10:57:30.282), -items (10:57:30.332), -: (10:57:30.342), -flex (10:57:30.392), -- (10:57:30.402), -end (10:57:30.432), -; (10:57:30.442), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +{ (00:00:00), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +flex (00:00:00), +- (00:00:00), +end (00:00:00), +; (00:00:00), +height (00:00:00), +: (00:00:00), +200px (00:00:00), +; (00:00:00)</t>
+          <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:17:21.139) ~1.00, -# (10:19:53.296) ~1.00, -vis (10:19:54.003) ~1.00, -- (10:19:54.226) ~1.00, -123456 (10:19:55.544) ~1.00, -{ (10:20:02.452) ~1.00, -height (10:20:07.891) ~1.00, -: (10:20:07.983) ~1.00, -200px (10:20:09.051) ~0.20, -; (10:20:09.451), -align (10:24:12.446) ~1.00, -- (10:24:12.596) ~1.00, -items (10:24:13.500), -align (10:57:30.272) ~1.00, -- (10:57:30.282) ~1.00, -items (10:57:30.332) ~1.00, -: (10:57:30.342) ~1.00, -flex (10:57:30.392), -- (10:57:30.402) ~0.00, -end (10:57:30.432) ~1.00, -; (10:57:30.442) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +{ (00:00:00), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +flex (00:00:00), +- (00:00:00), +end (00:00:00), +; (00:00:00), +height (00:00:00), +: (00:00:00), +200px (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q59" t="n">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>-length (10:38:57.372), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -getElementsByClassName (11:09:28.891), -; (11:14:32.118), +lenght (00:00:00), +getElementsByClassname (00:00:00)</t>
+          <t>-length (10:38:57.372) ~0.67, +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -getElementsByClassName (11:09:28.891) ~0.95, -; (11:14:32.118), +lenght (00:00:00), +getElementsByClassname (00:00:00)</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:17:21.139), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+          <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:17:21.139) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q62" t="n">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:17:21.139), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), -7px (10:43:39.527), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +700px (00:00:00)</t>
+          <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:17:21.139) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, -7px (10:43:39.527) ~0.60, +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +700px (00:00:00)</t>
         </is>
       </c>
       <c r="Q66" t="n">
@@ -4605,7 +4605,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>-for (10:30:13.868), -( (10:30:14.352), -let (10:30:15.164), -i (10:30:15.672), -= (10:30:16.329), -0 (10:30:16.771), -; (10:30:17.011), -i (10:30:17.443), -&lt; (10:30:18.073), -count (10:30:20.284), -; (10:30:20.584), -i (10:30:47.713), -+ (10:30:48.171), -+ (10:30:48.660), -) (10:30:49.210), -{ (10:31:12.723), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +count (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00)</t>
+          <t>-for (10:30:13.868) ~1.00, -( (10:30:14.352) ~1.00, -let (10:30:15.164) ~1.00, -i (10:30:15.672) ~1.00, -= (10:30:16.329) ~1.00, -0 (10:30:16.771) ~1.00, -; (10:30:17.011) ~1.00, -i (10:30:17.443) ~1.00, -&lt; (10:30:18.073) ~1.00, -count (10:30:20.284) ~1.00, -; (10:30:20.584) ~1.00, -i (10:30:47.713) ~1.00, -+ (10:30:48.171) ~1.00, -+ (10:30:48.660) ~1.00, -) (10:30:49.210) ~1.00, -{ (10:31:12.723) ~1.00, -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +count (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00)</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
@@ -4713,7 +4713,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>-# (10:19:53.296), -vis (10:19:54.003), -- (10:19:54.226), -123456 (10:19:55.544), -height (10:20:07.891), -200px (10:20:09.051), -. (10:43:24.242), -bar (10:43:31.288), -{ (10:43:32.996), -} (10:43:33.966), -width (10:43:37.644), -: (10:43:37.716), -7px (10:43:39.527), -; (10:43:40.239), -height (10:43:47.504), -: (10:43:47.683), -100 (10:43:48.485), -% (10:43:48.586), -; (10:43:48.809), -background (10:44:24.231), -- (10:44:24.311), -color (10:44:25.031), -: (10:44:25.154), -black (10:44:26.271), -; (10:44:26.592), -display (10:47:38.305), -flex (10:47:39.551), -margin (10:48:02.482), -: (10:48:02.549), -0px (10:48:03.827), -1px (10:48:07.241), -; (10:48:07.569), +:* (10:50:08.734), +;* (10:50:09.333), -align (10:57:30.272), -items (10:57:30.332), -flex (10:57:30.392), -- (10:57:30.402), -end (10:57:30.432), +} (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +{ (00:00:00), +display (00:00:00), +flex (00:00:00), +; (00:00:00), +height (00:00:00), +: (00:00:00), +200px (00:00:00), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +flex (00:00:00), +- (00:00:00), +end (00:00:00), +; (00:00:00), +background (00:00:00), +: (00:00:00), +red (00:00:00), +; (00:00:00), +. (00:00:00), +bar (00:00:00), +width (00:00:00), +7px (00:00:00), +height (00:00:00), +100 (00:00:00), +% (00:00:00), +background (00:00:00), +color (00:00:00), +black (00:00:00), +margin (00:00:00), +: (00:00:00), +0 (00:00:00), +1px (00:00:00), +; (00:00:00)</t>
+          <t>-# (10:19:53.296) ~1.00, -vis (10:19:54.003) ~1.00, -- (10:19:54.226) ~1.00, -123456 (10:19:55.544) ~1.00, -height (10:20:07.891) ~1.00, -200px (10:20:09.051) ~1.00, -. (10:43:24.242) ~1.00, -bar (10:43:31.288) ~1.00, -{ (10:43:32.996) ~1.00, -} (10:43:33.966), -width (10:43:37.644) ~1.00, -: (10:43:37.716), -7px (10:43:39.527) ~1.00, -; (10:43:40.239), -height (10:43:47.504) ~1.00, -: (10:43:47.683), -100 (10:43:48.485) ~1.00, -% (10:43:48.586) ~1.00, -; (10:43:48.809), -background (10:44:24.231) ~1.00, -- (10:44:24.311) ~1.00, -color (10:44:25.031) ~1.00, -: (10:44:25.154), -black (10:44:26.271) ~1.00, -; (10:44:26.592), -display (10:47:38.305) ~1.00, -flex (10:47:39.551) ~1.00, -margin (10:48:02.482) ~1.00, -: (10:48:02.549) ~1.00, -0px (10:48:03.827) ~0.33, -1px (10:48:07.241) ~1.00, -; (10:48:07.569) ~1.00, +:* (10:50:08.734), +;* (10:50:09.333), -align (10:57:30.272) ~1.00, -items (10:57:30.332) ~1.00, -flex (10:57:30.392) ~1.00, -- (10:57:30.402) ~1.00, -end (10:57:30.432) ~0.33, +} (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +{ (00:00:00), +display (00:00:00), +flex (00:00:00), +; (00:00:00), +height (00:00:00), +: (00:00:00), +200px (00:00:00), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +flex (00:00:00), +- (00:00:00), +end (00:00:00), +; (00:00:00), +background (00:00:00), +: (00:00:00), +red (00:00:00), +; (00:00:00), +. (00:00:00), +bar (00:00:00), +width (00:00:00), +7px (00:00:00), +height (00:00:00), +100 (00:00:00), +% (00:00:00), +background (00:00:00), +color (00:00:00), +black (00:00:00), +margin (00:00:00), +: (00:00:00), +0 (00:00:00), +1px (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q68" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>-function (10:57:37.492), -bubbleSort (10:57:42.836), -( (10:57:43.053), -arr (10:57:49.140), -) (10:57:49.861), -{ (10:57:54.715), -do (10:58:33.576), -{ (10:58:34.903), -var (10:59:12.196), -swapped (10:59:20.551), -= (10:59:21.101), -false (10:59:23.105), -; (10:59:24.221), -for (10:59:26.374), -( (10:59:26.727), -let (10:59:27.295), -i (10:59:27.677), -= (10:59:27.952), -1 (10:59:28.458), -; (10:59:28.738), -i (10:59:29.253), -&lt; (10:59:29.652), -arr (10:59:30.525), -. (10:59:30.766), -length (10:59:32.061), -; (10:59:32.305), -i (10:59:32.661), -+ (10:59:32.869), -+ (10:59:33.126), -) (10:59:33.350), -{ (10:59:35.506), -if (10:59:41.288), -( (10:59:41.708), -arr (10:59:42.652), -[ (10:59:42.917), -i (10:59:43.246), -- (10:59:44.058), -1 (10:59:44.656), -] (10:59:44.854), -&gt; (10:59:45.546), -arr (10:59:46.616), -[ (10:59:46.969), -i (10:59:47.212), -] (10:59:47.751), -) (10:59:48.230), -{ (10:59:49.302), -const (11:00:57.203), -aux (11:00:58.458), -= (11:01:01.660), -arr (11:01:02.684), -[ (11:01:02.941), -i (11:01:03.128), -- (11:01:03.607), -1 (11:01:04.198), -] (11:01:04.697), -; (11:01:05.017), -arr (11:01:06.389), -[ (11:01:06.650), -i (11:01:06.835), -- (11:01:07.252), -1 (11:01:07.757), -] (11:01:08.184), -= (11:01:08.961), -arr (11:01:09.861), -[ (11:01:10.052), -i (11:01:10.368), -] (11:01:10.513), -; (11:01:10.683), -arr (11:01:12.501), -[ (11:01:12.714), -i (11:01:12.894), -] (11:01:13.102), -= (11:01:13.537), -aux (11:01:14.449), -; (11:01:14.856), -swapped (11:02:15.877), -= (11:02:16.203), -true (11:02:17.158), -; (11:02:17.463), -bubbleSort (11:08:34.118), -array (11:08:34.178), -function (11:08:36.630), -updateBars (11:08:38.342), -( (11:08:38.511), -) (11:08:38.687), -{ (11:08:39.319), -const (11:09:21.850), -bars (11:09:22.876), -= (11:09:23.405), -document (11:09:24.920), -. (11:09:25.072), -getElementsByClassName (11:09:28.891), -( (11:09:28.949), -" (11:09:29.056), -bar (11:09:29.764), -" (11:09:29.897), -) (11:09:29.998), -; (11:09:30.476), -for (11:09:55.616), -( (11:09:55.956), -let (11:09:56.455), -i (11:09:56.677), -= (11:09:57.008), -0 (11:09:57.490), -; (11:09:57.512), -i (11:09:57.854), -&lt; (11:09:58.223), -bars (11:09:58.993), -. (11:09:59.214), -length (11:10:00.426), -; (11:10:00.634), -i (11:10:01.376), -+ (11:10:01.600), -+ (11:10:01.789), -) (11:10:01.880), -{ (11:10:02.609), -bars (11:10:05.954), -[ (11:10:06.083), -i (11:10:06.207), -] (11:10:06.517), -. (11:10:06.753), -style (11:10:08.322), -. (11:10:08.474), -height (11:10:09.606), -= (11:10:12.868), -array (11:10:13.726), -[ (11:10:13.999), -i (11:10:14.138), -] (11:10:14.279), -* (11:10:14.846), -100 (11:10:15.517), -+ (11:10:16.137), -" (11:10:16.502), -% (11:10:16.625), -" (11:10:16.705), -; (11:10:17.104), -updateBars (11:12:30.664), -; (11:12:31.204), -await (11:13:47.348), -new (11:13:53.570), -Promise (11:13:54.982), -( (11:13:55.301), -resolve (11:13:59.055), -= (11:14:16.118), -&gt; (11:14:16.408), -setTimeout (11:14:18.857), -( (11:14:19.066), -resolve (11:14:23.324), -, (11:14:23.491), -100 (11:14:24.924), -) (11:14:31.103), -) (11:14:31.475), -; (11:14:32.118), -async (11:15:16.100), +function (00:00:00), +updataBars (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bars (00:00:00), += (00:00:00), +visualizer (00:00:00), +. (00:00:00), +querySelectorAll (00:00:00), +" (00:00:00), +. (00:00:00), +bar (00:00:00), +" (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +array (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +height (00:00:00), += (00:00:00), +array (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +* (00:00:00), +100 (00:00:00), ++ (00:00:00), +" (00:00:00), +% (00:00:00), +" (00:00:00), +; (00:00:00), +async (00:00:00), +function (00:00:00), +bubblesort (00:00:00), +arr (00:00:00), +{ (00:00:00), +do (00:00:00), +{ (00:00:00), +var (00:00:00), +swapped (00:00:00), += (00:00:00), +false (00:00:00), +; (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +arr (00:00:00), +. (00:00:00), +length (00:00:00), +- (00:00:00), +1 (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +if (00:00:00), +( (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +&gt; (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), ++ (00:00:00), +1 (00:00:00), +] (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +aux (00:00:00), += (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +- (00:00:00), +1 (00:00:00), +] (00:00:00), +; (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), += (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), ++ (00:00:00), +1 (00:00:00), +] (00:00:00), +; (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), ++ (00:00:00), +1 (00:00:00), +] (00:00:00), += (00:00:00), +aux (00:00:00), +; (00:00:00), +swapped (00:00:00), += (00:00:00), +true (00:00:00), +; (00:00:00), +updataBars (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +await (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +10 (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00)</t>
+          <t>-function (10:57:37.492) ~1.00, -bubbleSort (10:57:42.836) ~0.90, -( (10:57:43.053), -arr (10:57:49.140) ~1.00, -) (10:57:49.861), -{ (10:57:54.715) ~1.00, -do (10:58:33.576) ~1.00, -{ (10:58:34.903) ~1.00, -var (10:59:12.196) ~1.00, -swapped (10:59:20.551) ~1.00, -= (10:59:21.101) ~1.00, -false (10:59:23.105) ~1.00, -; (10:59:24.221) ~1.00, -for (10:59:26.374) ~1.00, -( (10:59:26.727) ~1.00, -let (10:59:27.295) ~1.00, -i (10:59:27.677) ~1.00, -= (10:59:27.952) ~1.00, -1 (10:59:28.458) ~0.00, -; (10:59:28.738) ~1.00, -i (10:59:29.253) ~1.00, -&lt; (10:59:29.652) ~1.00, -arr (10:59:30.525) ~1.00, -. (10:59:30.766) ~1.00, -length (10:59:32.061) ~1.00, -; (10:59:32.305) ~1.00, -i (10:59:32.661) ~1.00, -+ (10:59:32.869) ~1.00, -+ (10:59:33.126) ~1.00, -) (10:59:33.350) ~1.00, -{ (10:59:35.506) ~1.00, -if (10:59:41.288) ~1.00, -( (10:59:41.708) ~1.00, -arr (10:59:42.652) ~1.00, -[ (10:59:42.917) ~1.00, -i (10:59:43.246) ~1.00, -- (10:59:44.058), -1 (10:59:44.656) ~1.00, -] (10:59:44.854) ~1.00, -&gt; (10:59:45.546) ~1.00, -arr (10:59:46.616) ~1.00, -[ (10:59:46.969) ~1.00, -i (10:59:47.212) ~1.00, -] (10:59:47.751) ~1.00, -) (10:59:48.230) ~1.00, -{ (10:59:49.302) ~1.00, -const (11:00:57.203) ~1.00, -aux (11:00:58.458) ~1.00, -= (11:01:01.660) ~1.00, -arr (11:01:02.684) ~1.00, -[ (11:01:02.941) ~1.00, -i (11:01:03.128) ~1.00, -- (11:01:03.607) ~1.00, -1 (11:01:04.198) ~1.00, -] (11:01:04.697) ~1.00, -; (11:01:05.017) ~1.00, -arr (11:01:06.389) ~1.00, -[ (11:01:06.650) ~1.00, -i (11:01:06.835) ~1.00, -- (11:01:07.252) ~0.00, -1 (11:01:07.757) ~1.00, -] (11:01:08.184) ~1.00, -= (11:01:08.961) ~1.00, -arr (11:01:09.861) ~1.00, -[ (11:01:10.052) ~1.00, -i (11:01:10.368) ~1.00, -] (11:01:10.513) ~1.00, -; (11:01:10.683) ~1.00, -arr (11:01:12.501) ~1.00, -[ (11:01:12.714) ~1.00, -i (11:01:12.894) ~1.00, -] (11:01:13.102) ~1.00, -= (11:01:13.537) ~1.00, -aux (11:01:14.449) ~1.00, -; (11:01:14.856) ~1.00, -swapped (11:02:15.877) ~1.00, -= (11:02:16.203) ~1.00, -true (11:02:17.158) ~1.00, -; (11:02:17.463) ~1.00, -bubbleSort (11:08:34.118) ~0.20, -array (11:08:34.178), -function (11:08:36.630), -updateBars (11:08:38.342) ~0.90, -( (11:08:38.511) ~1.00, -) (11:08:38.687) ~1.00, -{ (11:08:39.319) ~1.00, -const (11:09:21.850) ~1.00, -bars (11:09:22.876) ~1.00, -= (11:09:23.405) ~1.00, -document (11:09:24.920) ~0.10, -. (11:09:25.072) ~1.00, -getElementsByClassName (11:09:28.891) ~0.18, -( (11:09:28.949) ~0.00, -" (11:09:29.056) ~1.00, -bar (11:09:29.764) ~1.00, -" (11:09:29.897) ~1.00, -) (11:09:29.998), -; (11:09:30.476), -for (11:09:55.616) ~1.00, -( (11:09:55.956) ~1.00, -let (11:09:56.455) ~1.00, -i (11:09:56.677) ~1.00, -= (11:09:57.008) ~1.00, -0 (11:09:57.490) ~1.00, -; (11:09:57.512) ~1.00, -i (11:09:57.854) ~1.00, -&lt; (11:09:58.223) ~1.00, -bars (11:09:58.993) ~0.20, -. (11:09:59.214) ~1.00, -length (11:10:00.426) ~1.00, -; (11:10:00.634) ~1.00, -i (11:10:01.376) ~1.00, -+ (11:10:01.600) ~1.00, -+ (11:10:01.789) ~1.00, -) (11:10:01.880) ~1.00, -{ (11:10:02.609) ~1.00, -bars (11:10:05.954) ~1.00, -[ (11:10:06.083) ~1.00, -i (11:10:06.207) ~1.00, -] (11:10:06.517) ~1.00, -. (11:10:06.753) ~1.00, -style (11:10:08.322) ~1.00, -. (11:10:08.474) ~1.00, -height (11:10:09.606) ~1.00, -= (11:10:12.868) ~1.00, -array (11:10:13.726) ~1.00, -[ (11:10:13.999) ~1.00, -i (11:10:14.138) ~1.00, -] (11:10:14.279) ~1.00, -* (11:10:14.846) ~1.00, -100 (11:10:15.517) ~1.00, -+ (11:10:16.137) ~1.00, -" (11:10:16.502) ~1.00, -% (11:10:16.625) ~1.00, -" (11:10:16.705) ~1.00, -; (11:10:17.104) ~1.00, -updateBars (11:12:30.664) ~0.90, -; (11:12:31.204) ~1.00, -await (11:13:47.348) ~1.00, -new (11:13:53.570) ~1.00, -Promise (11:13:54.982) ~1.00, -( (11:13:55.301) ~1.00, -resolve (11:13:59.055) ~1.00, -= (11:14:16.118) ~1.00, -&gt; (11:14:16.408) ~1.00, -setTimeout (11:14:18.857) ~1.00, -( (11:14:19.066) ~1.00, -resolve (11:14:23.324) ~1.00, -, (11:14:23.491) ~1.00, -100 (11:14:24.924) ~0.67, -) (11:14:31.103) ~1.00, -) (11:14:31.475) ~1.00, -; (11:14:32.118) ~1.00, -async (11:15:16.100) ~1.00, +function (00:00:00), +updataBars (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bars (00:00:00), += (00:00:00), +visualizer (00:00:00), +. (00:00:00), +querySelectorAll (00:00:00), +" (00:00:00), +. (00:00:00), +bar (00:00:00), +" (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +array (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +height (00:00:00), += (00:00:00), +array (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +* (00:00:00), +100 (00:00:00), ++ (00:00:00), +" (00:00:00), +% (00:00:00), +" (00:00:00), +; (00:00:00), +async (00:00:00), +function (00:00:00), +bubblesort (00:00:00), +arr (00:00:00), +{ (00:00:00), +do (00:00:00), +{ (00:00:00), +var (00:00:00), +swapped (00:00:00), += (00:00:00), +false (00:00:00), +; (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +arr (00:00:00), +. (00:00:00), +length (00:00:00), +- (00:00:00), +1 (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +if (00:00:00), +( (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +&gt; (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), ++ (00:00:00), +1 (00:00:00), +] (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +aux (00:00:00), += (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +- (00:00:00), +1 (00:00:00), +] (00:00:00), +; (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), += (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), ++ (00:00:00), +1 (00:00:00), +] (00:00:00), +; (00:00:00), +arr (00:00:00), +[ (00:00:00), +i (00:00:00), ++ (00:00:00), +1 (00:00:00), +] (00:00:00), += (00:00:00), +aux (00:00:00), +; (00:00:00), +swapped (00:00:00), += (00:00:00), +true (00:00:00), +; (00:00:00), +updataBars (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +await (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +10 (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -4821,7 +4821,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>-DOCTYPE (10:12:14.338), -Visualizer (10:12:47.677), -Sorting (10:13:13.802), -Visualizer (10:13:16.993), -&lt; (10:27:15.917), +Doctype (00:00:00), +visualizer (00:00:00), +sorting (00:00:00), +visualizer (00:00:00)</t>
+          <t>-DOCTYPE (10:12:14.338) ~0.14, -Visualizer (10:12:47.677) ~0.90, -Sorting (10:13:13.802) ~0.86, -Visualizer (10:13:16.993) ~0.90, -&lt; (10:27:15.917), +Doctype (00:00:00), +visualizer (00:00:00), +sorting (00:00:00), +visualizer (00:00:00)</t>
         </is>
       </c>
       <c r="O70" t="n">
@@ -4829,7 +4829,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:17:21.139), -# (10:19:53.296), -vis (10:19:54.003), -- (10:19:54.226), -123456 (10:19:55.544), -{ (10:20:02.452), -height (10:20:07.891), -200px (10:20:09.051), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), -. (10:43:24.242), -bar (10:43:31.288), -{ (10:43:32.996), -width (10:43:37.644), -7px (10:43:39.527), -height (10:43:47.504), -100 (10:43:48.485), -% (10:43:48.586), -background (10:44:24.231), -- (10:44:24.311), -color (10:44:25.031), -black (10:44:26.271), -margin (10:48:02.482), -: (10:48:02.549), -0px (10:48:03.827), -1px (10:48:07.241), -; (10:48:07.569), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +red* (10:50:09.332), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +{ (00:00:00), +height (00:00:00), +: (00:00:00), +500px (00:00:00), +. (00:00:00), +bar (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +7px (00:00:00), +; (00:00:00), +height (00:00:00), +100 (00:00:00), +% (00:00:00), +Background (00:00:00), +- (00:00:00), +color (00:00:00), +black (00:00:00), +margin (00:00:00), +0px (00:00:00), +1px (00:00:00)</t>
+          <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:17:21.139) ~1.00, -# (10:19:53.296) ~1.00, -vis (10:19:54.003) ~1.00, -- (10:19:54.226) ~1.00, -123456 (10:19:55.544) ~1.00, -{ (10:20:02.452) ~1.00, -height (10:20:07.891) ~1.00, -200px (10:20:09.051) ~0.80, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, -. (10:43:24.242) ~1.00, -bar (10:43:31.288) ~1.00, -{ (10:43:32.996) ~1.00, -width (10:43:37.644) ~1.00, -7px (10:43:39.527) ~1.00, -height (10:43:47.504) ~1.00, -100 (10:43:48.485) ~1.00, -% (10:43:48.586) ~1.00, -background (10:44:24.231) ~0.90, -- (10:44:24.311) ~1.00, -color (10:44:25.031) ~1.00, -black (10:44:26.271) ~1.00, -margin (10:48:02.482) ~1.00, -: (10:48:02.549), -0px (10:48:03.827) ~1.00, -1px (10:48:07.241) ~1.00, -; (10:48:07.569), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +red* (10:50:09.332), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +{ (00:00:00), +height (00:00:00), +: (00:00:00), +500px (00:00:00), +. (00:00:00), +bar (00:00:00), +{ (00:00:00), +width (00:00:00), +: (00:00:00), +7px (00:00:00), +; (00:00:00), +height (00:00:00), +100 (00:00:00), +% (00:00:00), +Background (00:00:00), +- (00:00:00), +color (00:00:00), +black (00:00:00), +margin (00:00:00), +0px (00:00:00), +1px (00:00:00)</t>
         </is>
       </c>
       <c r="Q70" t="n">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>-bubbleSort (10:57:42.836), -i (10:59:29.253), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -&lt; (11:09:58.223), -bars (11:09:58.993), -i (11:10:01.376), -Promise (11:13:54.982), +&gt; (00:00:00), +bats (00:00:00), +bubblesort (00:00:00), +promise (00:00:00)</t>
+          <t>-bubbleSort (10:57:42.836) ~0.90, -i (10:59:29.253), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -&lt; (11:09:58.223) ~0.00, -bars (11:09:58.993) ~0.75, -i (11:10:01.376), -Promise (11:13:54.982) ~0.86, +&gt; (00:00:00), +bats (00:00:00), +bubblesort (00:00:00), +promise (00:00:00)</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:17:21.139), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+          <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:17:21.139) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q71" t="n">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>-title (10:12:49.434), -Visualizer (10:13:16.993), -123456 (10:18:40.665), +tittle (00:00:00), +visualizer (00:00:00), +654321 (00:00:00)</t>
+          <t>-title (10:12:49.434) ~0.83, -Visualizer (10:13:16.993) ~0.90, -123456 (10:18:40.665) ~0.00, +tittle (00:00:00), +visualizer (00:00:00), +654321 (00:00:00)</t>
         </is>
       </c>
       <c r="O72" t="n">
@@ -4973,7 +4973,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:17:21.139), -# (10:19:53.296), -vis (10:19:54.003), -- (10:19:54.226), -123456 (10:19:55.544), -{ (10:20:02.452), -height (10:20:07.891), -: (10:20:07.983), -200px (10:20:09.051), -; (10:20:09.451), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), -display (10:47:38.305), -: (10:47:38.437), -flex (10:47:39.551), -; (10:47:39.811), -margin (10:48:02.482), -: (10:48:02.549), -0px (10:48:03.827), -1px (10:48:07.241), -; (10:48:07.569), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), -align (10:57:30.272), -- (10:57:30.282), -items (10:57:30.332), -: (10:57:30.342), -flex (10:57:30.392), -- (10:57:30.402), -end (10:57:30.432), -; (10:57:30.442), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +654321 (00:00:00), +{ (00:00:00), +height (00:00:00), +: (00:00:00), +200px (00:00:00), +; (00:00:00)</t>
+          <t>-: (10:17:19.374), -center (10:17:20.707) ~1.00, -; (10:17:21.139) ~1.00, -# (10:19:53.296) ~1.00, -vis (10:19:54.003) ~1.00, -- (10:19:54.226) ~1.00, -123456 (10:19:55.544) ~0.00, -{ (10:20:02.452) ~1.00, -height (10:20:07.891) ~1.00, -: (10:20:07.983), -200px (10:20:09.051), -; (10:20:09.451), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), -display (10:47:38.305), -: (10:47:38.437) ~1.00, -flex (10:47:39.551), -; (10:47:39.811) ~1.00, -margin (10:48:02.482), -: (10:48:02.549), -0px (10:48:03.827), -1px (10:48:07.241), -; (10:48:07.569), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), -align (10:57:30.272) ~1.00, -- (10:57:30.282) ~1.00, -items (10:57:30.332) ~1.00, -: (10:57:30.342) ~1.00, -flex (10:57:30.392), -- (10:57:30.402), -end (10:57:30.432), -; (10:57:30.442), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +654321 (00:00:00), +{ (00:00:00), +height (00:00:00), +: (00:00:00), +200px (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q72" t="n">
@@ -4981,7 +4981,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>-array (10:28:45.898), -const (10:37:42.386), -visualizer (10:37:44.631), -= (10:37:45.082), -document (10:37:47.323), -. (10:37:47.760), -getElementById (10:38:03.158), -" (10:38:19.019), -vis (10:38:19.926), -- (10:38:20.217), -123456 (10:38:22.251), -" (10:38:22.629), +bubbleSort* (11:08:31.581), -array (11:08:34.178), -getElementsByClassName (11:09:28.891), +arry (00:00:00), +arry (00:00:00), +const (00:00:00), +visualizer (00:00:00), += (00:00:00), +documnet (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +654321 (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +arry (00:00:00), +getElementByClassName (00:00:00)</t>
+          <t>-array (10:28:45.898) ~0.80, -const (10:37:42.386) ~1.00, -visualizer (10:37:44.631) ~1.00, -= (10:37:45.082) ~1.00, -document (10:37:47.323) ~0.75, -. (10:37:47.760) ~1.00, -getElementById (10:38:03.158) ~1.00, -" (10:38:19.019) ~1.00, -vis (10:38:19.926) ~1.00, -- (10:38:20.217) ~1.00, -123456 (10:38:22.251) ~0.00, -" (10:38:22.629) ~1.00, +bubbleSort* (11:08:31.581), -array (11:08:34.178) ~0.80, -getElementsByClassName (11:09:28.891) ~0.95, +arry (00:00:00), +arry (00:00:00), +const (00:00:00), +visualizer (00:00:00), += (00:00:00), +documnet (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +654321 (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +arry (00:00:00), +getElementByClassName (00:00:00)</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -5047,7 +5047,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:17:21.139), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+          <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:17:21.139) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q73" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:17:21.139), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), -align (10:57:30.272), -- (10:57:30.282), -items (10:57:30.332), -: (10:57:30.342), -flex (10:57:30.392), -- (10:57:30.402), -end (10:57:30.432), -; (10:57:30.442), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+          <t>-: (10:17:19.374), -center (10:17:20.707) ~1.00, -; (10:17:21.139) ~1.00, -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), -align (10:57:30.272) ~1.00, -- (10:57:30.282) ~1.00, -items (10:57:30.332) ~1.00, -: (10:57:30.342) ~1.00, -flex (10:57:30.392), -- (10:57:30.402), -end (10:57:30.432), -; (10:57:30.442), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q75" t="n">
@@ -5159,7 +5159,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>-createElement (10:39:45.021), -visualizer (10:40:27.992), -. (10:40:28.151), -appendChild (10:40:30.229), -( (10:40:30.435), -bar (10:40:31.317), -) (10:40:31.505), -; (10:40:32.101), -bubbleSort (10:57:42.836), -} (10:59:37.396), -&gt; (10:59:45.546), -arr (10:59:46.616), -[ (10:59:46.969), -i (10:59:47.212), -] (10:59:47.751), -- (11:01:03.607), -1 (11:01:04.198), -arr (11:01:06.389), -[ (11:01:06.650), -i (11:01:06.835), -- (11:01:07.252), -1 (11:01:07.757), -] (11:01:08.184), -= (11:01:08.961), -arr (11:01:09.861), -[ (11:01:10.052), -i (11:01:10.368), -] (11:01:10.513), -; (11:01:10.683), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -function (11:08:36.630), -updateBars (11:08:38.342), -( (11:08:38.511), -) (11:08:38.687), -{ (11:08:39.319), -const (11:09:21.850), -bars (11:09:22.876), -= (11:09:23.405), -document (11:09:24.920), -. (11:09:25.072), -getElementsByClassName (11:09:28.891), -( (11:09:28.949), -" (11:09:29.056), -bar (11:09:29.764), -" (11:09:29.897), -) (11:09:29.998), -; (11:09:30.476), -for (11:09:55.616), -( (11:09:55.956), -let (11:09:56.455), -i (11:09:56.677), -= (11:09:57.008), -0 (11:09:57.490), -; (11:09:57.512), -i (11:09:57.854), -&lt; (11:09:58.223), -bars (11:09:58.993), -. (11:09:59.214), -length (11:10:00.426), -; (11:10:00.634), -i (11:10:01.376), -+ (11:10:01.600), -+ (11:10:01.789), -) (11:10:01.880), -{ (11:10:02.609), -} (11:10:03.305), -bars (11:10:05.954), -[ (11:10:06.083), -i (11:10:06.207), -] (11:10:06.517), -. (11:10:06.753), -style (11:10:08.322), -. (11:10:08.474), -height (11:10:09.606), -= (11:10:12.868), -array (11:10:13.726), -[ (11:10:13.999), -i (11:10:14.138), -] (11:10:14.279), -* (11:10:14.846), -100 (11:10:15.517), -+ (11:10:16.137), -" (11:10:16.502), -% (11:10:16.625), -" (11:10:16.705), -; (11:10:17.104), -updateBars (11:12:30.664), -( (11:12:30.752), -) (11:12:30.906), -; (11:12:31.204), -await (11:13:47.348), -new (11:13:53.570), -Promise (11:13:54.982), -( (11:13:55.301), -resolve (11:13:59.055), -= (11:14:16.118), -&gt; (11:14:16.408), -setTimeout (11:14:18.857), -( (11:14:19.066), -resolve (11:14:23.324), -, (11:14:23.491), -100 (11:14:24.924), -) (11:14:31.103), -) (11:14:31.475), -; (11:14:32.118), +createrElement (00:00:00), +function (00:00:00), +updatebars (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bars (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +get (00:00:00), +ElementsByClassName (00:00:00), +( (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +&lt; (00:00:00), +array (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +height (00:00:00), += (00:00:00), +array (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +* (00:00:00), +100 (00:00:00), ++ (00:00:00), +" (00:00:00), +% (00:00:00), +" (00:00:00), +; (00:00:00), +bubblesort (00:00:00), +updateBars (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +await (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeOut (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +100 (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+          <t>-createElement (10:39:45.021) ~0.93, -visualizer (10:40:27.992), -. (10:40:28.151), -appendChild (10:40:30.229), -( (10:40:30.435), -bar (10:40:31.317), -) (10:40:31.505), -; (10:40:32.101), -bubbleSort (10:57:42.836) ~0.90, -} (10:59:37.396) ~1.00, -&gt; (10:59:45.546), -arr (10:59:46.616), -[ (10:59:46.969), -i (10:59:47.212), -] (10:59:47.751), -- (11:01:03.607), -1 (11:01:04.198), -arr (11:01:06.389), -[ (11:01:06.650), -i (11:01:06.835), -- (11:01:07.252), -1 (11:01:07.757), -] (11:01:08.184), -= (11:01:08.961), -arr (11:01:09.861), -[ (11:01:10.052), -i (11:01:10.368), -] (11:01:10.513), -; (11:01:10.683), -bubbleSort (11:08:34.118), -( (11:08:34.128) ~1.00, -array (11:08:34.178), -) (11:08:34.188) ~1.00, -; (11:08:34.198), -function (11:08:36.630) ~1.00, -updateBars (11:08:38.342) ~0.90, -( (11:08:38.511), -) (11:08:38.687), -{ (11:08:39.319) ~1.00, -const (11:09:21.850) ~1.00, -bars (11:09:22.876) ~1.00, -= (11:09:23.405) ~1.00, -document (11:09:24.920) ~1.00, -. (11:09:25.072) ~1.00, -getElementsByClassName (11:09:28.891) ~0.86, -( (11:09:28.949) ~1.00, -" (11:09:29.056) ~1.00, -bar (11:09:29.764) ~1.00, -" (11:09:29.897) ~1.00, -) (11:09:29.998) ~1.00, -; (11:09:30.476) ~1.00, -for (11:09:55.616) ~1.00, -( (11:09:55.956) ~1.00, -let (11:09:56.455) ~1.00, -i (11:09:56.677) ~1.00, -= (11:09:57.008) ~1.00, -0 (11:09:57.490) ~1.00, -; (11:09:57.512), -i (11:09:57.854), -&lt; (11:09:58.223) ~1.00, -bars (11:09:58.993) ~0.20, -. (11:09:59.214) ~1.00, -length (11:10:00.426) ~1.00, -; (11:10:00.634) ~1.00, -i (11:10:01.376) ~1.00, -+ (11:10:01.600) ~1.00, -+ (11:10:01.789) ~1.00, -) (11:10:01.880) ~1.00, -{ (11:10:02.609) ~1.00, -} (11:10:03.305), -bars (11:10:05.954) ~1.00, -[ (11:10:06.083) ~1.00, -i (11:10:06.207) ~1.00, -] (11:10:06.517) ~1.00, -. (11:10:06.753) ~1.00, -style (11:10:08.322) ~1.00, -. (11:10:08.474) ~1.00, -height (11:10:09.606) ~1.00, -= (11:10:12.868) ~1.00, -array (11:10:13.726) ~1.00, -[ (11:10:13.999) ~1.00, -i (11:10:14.138) ~1.00, -] (11:10:14.279) ~1.00, -* (11:10:14.846) ~1.00, -100 (11:10:15.517) ~1.00, -+ (11:10:16.137) ~1.00, -" (11:10:16.502) ~1.00, -% (11:10:16.625) ~1.00, -" (11:10:16.705) ~1.00, -; (11:10:17.104) ~1.00, -updateBars (11:12:30.664) ~1.00, -( (11:12:30.752) ~1.00, -) (11:12:30.906) ~1.00, -; (11:12:31.204) ~1.00, -await (11:13:47.348) ~1.00, -new (11:13:53.570) ~1.00, -Promise (11:13:54.982) ~1.00, -( (11:13:55.301) ~1.00, -resolve (11:13:59.055) ~1.00, -= (11:14:16.118) ~1.00, -&gt; (11:14:16.408) ~1.00, -setTimeout (11:14:18.857) ~0.90, -( (11:14:19.066) ~1.00, -resolve (11:14:23.324) ~1.00, -, (11:14:23.491) ~1.00, -100 (11:14:24.924) ~1.00, -) (11:14:31.103) ~1.00, -) (11:14:31.475) ~1.00, -; (11:14:32.118) ~1.00, +createrElement (00:00:00), +function (00:00:00), +updatebars (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bars (00:00:00), += (00:00:00), +document (00:00:00), +. (00:00:00), +get (00:00:00), +ElementsByClassName (00:00:00), +( (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +&lt; (00:00:00), +array (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +bars (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +height (00:00:00), += (00:00:00), +array (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +* (00:00:00), +100 (00:00:00), ++ (00:00:00), +" (00:00:00), +% (00:00:00), +" (00:00:00), +; (00:00:00), +bubblesort (00:00:00), +updateBars (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +await (00:00:00), +new (00:00:00), +Promise (00:00:00), +( (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeOut (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +100 (00:00:00), +) (00:00:00), +) (00:00:00), +; (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -5301,7 +5301,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>-center (10:17:20.707), -flex (10:21:58.800), -direction (10:22:01.758), -column (10:22:03.223), -align (10:24:12.446), -items (10:24:13.500), +align (00:00:00), +items (00:00:00), +center (00:00:00), +flex (00:00:00), +direction (00:00:00), +column (00:00:00)</t>
+          <t>-center (10:17:20.707) ~0.17, -flex (10:21:58.800) ~0.20, -direction (10:22:01.758) ~0.22, -column (10:22:03.223) ~0.17, -align (10:24:12.446) ~0.20, -items (10:24:13.500) ~0.22, +align (00:00:00), +items (00:00:00), +center (00:00:00), +flex (00:00:00), +direction (00:00:00), +column (00:00:00)</t>
         </is>
       </c>
       <c r="Q78" t="n">
@@ -5375,7 +5375,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:17:21.139), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+          <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:17:21.139) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q79" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>-; (10:50:48.660), -; (11:10:17.104), -100 (11:14:24.924), +10 (00:00:00)</t>
+          <t>-; (10:50:48.660), -; (11:10:17.104), -100 (11:14:24.924) ~0.67, +10 (00:00:00)</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:17:21.139), -# (10:19:53.296), -vis (10:19:54.003), -- (10:19:54.226), -123456 (10:19:55.544), -{ (10:20:02.452), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), -. (10:43:24.242), -bar (10:43:31.288), -{ (10:43:32.996), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +{ (00:00:00), +. (00:00:00), +bar (00:00:00), +{ (00:00:00)</t>
+          <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:17:21.139) ~1.00, -# (10:19:53.296) ~1.00, -vis (10:19:54.003) ~1.00, -- (10:19:54.226) ~1.00, -123456 (10:19:55.544) ~1.00, -{ (10:20:02.452) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, -. (10:43:24.242) ~1.00, -bar (10:43:31.288) ~1.00, -{ (10:43:32.996) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +{ (00:00:00), +. (00:00:00), +bar (00:00:00), +{ (00:00:00)</t>
         </is>
       </c>
       <c r="Q81" t="n">
@@ -5565,7 +5565,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>-&lt; (10:12:37.377), -/ (10:12:37.545), -head (10:12:38.381), -&gt; (10:12:38.657), +&lt; (00:00:00), +/ (00:00:00), +head (00:00:00), +&gt; (00:00:00)</t>
+          <t>-&lt; (10:12:37.377) ~1.00, -/ (10:12:37.545) ~1.00, -head (10:12:38.381) ~1.00, -&gt; (10:12:38.657) ~1.00, +&lt; (00:00:00), +/ (00:00:00), +head (00:00:00), +&gt; (00:00:00)</t>
         </is>
       </c>
       <c r="O82" t="n">
@@ -5573,7 +5573,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:17:21.139), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+          <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:17:21.139) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q82" t="n">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>-: (10:17:19.374), -center (10:17:20.707), -; (10:17:21.139), -align (10:24:12.446), -- (10:24:12.596), -items (10:24:13.500), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
+          <t>-: (10:17:19.374) ~1.00, -center (10:17:20.707) ~1.00, -; (10:17:21.139) ~1.00, -align (10:24:12.446) ~1.00, -- (10:24:12.596), -items (10:24:13.500) ~1.00, +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +center (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q83" t="n">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>-; (10:50:48.660), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -array (11:08:34.178), -; (11:08:34.198), -function (11:08:36.630), -updateBars (11:08:38.342), -( (11:08:38.511), -) (11:08:38.687), -{ (11:08:39.319), -; (11:10:17.104), +function (00:00:00), +updateBars (00:00:00), +{ (00:00:00)</t>
+          <t>-; (10:50:48.660), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -array (11:08:34.178), -; (11:08:34.198), -function (11:08:36.630) ~1.00, -updateBars (11:08:38.342) ~1.00, -( (11:08:38.511), -) (11:08:38.687), -{ (11:08:39.319) ~1.00, -; (11:10:17.104), +function (00:00:00), +updateBars (00:00:00), +{ (00:00:00)</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
